--- a/AIDS_Data.xlsx
+++ b/AIDS_Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V93"/>
+  <dimension ref="A1:Z93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,100 +441,120 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Basic Materials_w</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Communication Services_w</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Consumer Cyclical_w</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Consumer Defensive_w</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Energy_w</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Financial Services_w</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Healthcare_w</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Industrials_w</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Real Estate_w</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Technology_w</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Utilities_w</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Basic Materials_logp</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Communication Services_logp</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Consumer Cyclical_logp</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Consumer Defensive_logp</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Energy_logp</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Financial Services_logp</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Healthcare_logp</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Industrials_logp</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Real Estate_logp</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Technology_logp</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Utilities_logp</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>portfolio_value</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>PPI</t>
         </is>
@@ -552,63 +572,75 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.585525361101453</v>
+        <v>0.1445538969840306</v>
       </c>
       <c r="D2" t="n">
-        <v>7.816681278180012</v>
+        <v>2.135966505940736</v>
       </c>
       <c r="E2" t="n">
-        <v>65.88675959715189</v>
+        <v>5.547781591706151</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>47.62022507899552</v>
       </c>
       <c r="G2" t="n">
-        <v>12.0410442308068</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>41.50549992630928</v>
       </c>
       <c r="I2" t="n">
-        <v>12.66998953275984</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2.942094345785439</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.1038786542788318</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4.98449666990073</v>
+      </c>
+      <c r="O2" t="n">
         <v>4.94556331906551</v>
       </c>
-      <c r="M2" t="n">
+      <c r="P2" t="n">
         <v>5.494665092567373</v>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>5.466666758038366</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
         <v>5.41498867335173</v>
       </c>
-      <c r="P2" t="n">
+      <c r="S2" t="n">
         <v>5.898005146840249</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="T2" t="n">
         <v>5.91886694593901</v>
       </c>
-      <c r="R2" t="n">
+      <c r="U2" t="n">
         <v>5.562526124991417</v>
       </c>
-      <c r="S2" t="n">
+      <c r="V2" t="n">
+        <v>4.572853581359557</v>
+      </c>
+      <c r="W2" t="n">
         <v>5.754475608311122</v>
       </c>
-      <c r="T2" t="n">
+      <c r="X2" t="n">
         <v>5.005823728921762</v>
       </c>
-      <c r="U2" t="n">
-        <v>17455413000</v>
-      </c>
-      <c r="V2" t="n">
+      <c r="Y2" t="n">
+        <v>31476149000</v>
+      </c>
+      <c r="Z2" t="n">
         <v>129.8</v>
       </c>
     </row>
@@ -624,63 +656,75 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.535885428632459</v>
+        <v>0.1492439585258826</v>
       </c>
       <c r="D3" t="n">
-        <v>7.003740602381262</v>
+        <v>1.677675502626196</v>
       </c>
       <c r="E3" t="n">
-        <v>67.55770942062367</v>
+        <v>5.114573599493569</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>50.1260697998018</v>
       </c>
       <c r="G3" t="n">
-        <v>12.24272056475546</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>39.96080447422951</v>
       </c>
       <c r="I3" t="n">
-        <v>11.65994398360716</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2.759309651878953</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.2123230134440948</v>
       </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4.959061305678293</v>
+      </c>
+      <c r="O3" t="n">
         <v>4.642851217688932</v>
       </c>
-      <c r="M3" t="n">
+      <c r="P3" t="n">
         <v>5.35242666906693</v>
       </c>
-      <c r="N3" t="n">
+      <c r="Q3" t="n">
         <v>5.440684634302936</v>
       </c>
-      <c r="O3" t="n">
+      <c r="R3" t="n">
         <v>5.358612487853522</v>
       </c>
-      <c r="P3" t="n">
+      <c r="S3" t="n">
         <v>5.803869067315105</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="T3" t="n">
         <v>5.708239183220393</v>
       </c>
-      <c r="R3" t="n">
+      <c r="U3" t="n">
         <v>5.391215554476817</v>
       </c>
-      <c r="S3" t="n">
+      <c r="V3" t="n">
+        <v>4.565597439442779</v>
+      </c>
+      <c r="W3" t="n">
         <v>5.444579873526289</v>
       </c>
-      <c r="T3" t="n">
+      <c r="X3" t="n">
         <v>4.762515764534214</v>
       </c>
-      <c r="U3" t="n">
-        <v>17972239000</v>
-      </c>
-      <c r="V3" t="n">
+      <c r="Y3" t="n">
+        <v>31140289000</v>
+      </c>
+      <c r="Z3" t="n">
         <v>130.9</v>
       </c>
     </row>
@@ -696,63 +740,75 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.801661909840159</v>
+        <v>0.0933152440536386</v>
       </c>
       <c r="D4" t="n">
-        <v>7.077948256412469</v>
+        <v>1.698997826580294</v>
       </c>
       <c r="E4" t="n">
-        <v>66.04069090079705</v>
+        <v>4.865722414497485</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>49.30058968415051</v>
       </c>
       <c r="G4" t="n">
-        <v>12.50477429217805</v>
+        <v>0.0069160952035139</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>40.91621859497893</v>
       </c>
       <c r="I4" t="n">
-        <v>12.49034970380279</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.08457493696948019</v>
+        <v>2.470621579659832</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.5983768243982611</v>
       </c>
       <c r="L4" t="n">
+        <v>0.0492417364775354</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.695650550267494</v>
+      </c>
+      <c r="O4" t="n">
         <v>4.369447852467021</v>
       </c>
-      <c r="M4" t="n">
+      <c r="P4" t="n">
         <v>5.19028664613369</v>
       </c>
-      <c r="N4" t="n">
+      <c r="Q4" t="n">
         <v>5.315813408167131</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>5.15109261850503</v>
       </c>
-      <c r="P4" t="n">
+      <c r="S4" t="n">
         <v>5.627657119393593</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="T4" t="n">
         <v>5.687212641149006</v>
       </c>
-      <c r="R4" t="n">
+      <c r="U4" t="n">
         <v>5.211724103929734</v>
       </c>
-      <c r="S4" t="n">
+      <c r="V4" t="n">
+        <v>4.42328856536701</v>
+      </c>
+      <c r="W4" t="n">
         <v>5.193623268324707</v>
       </c>
-      <c r="T4" t="n">
+      <c r="X4" t="n">
         <v>4.547752895725483</v>
       </c>
-      <c r="U4" t="n">
-        <v>16222300000</v>
-      </c>
-      <c r="V4" t="n">
+      <c r="Y4" t="n">
+        <v>27862543000</v>
+      </c>
+      <c r="Z4" t="n">
         <v>132.3</v>
       </c>
     </row>
@@ -768,63 +824,75 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.688769110991986</v>
+        <v>0.1944070584716614</v>
       </c>
       <c r="D5" t="n">
-        <v>7.846569704839128</v>
+        <v>1.724734825055769</v>
       </c>
       <c r="E5" t="n">
-        <v>63.88651243587314</v>
+        <v>5.141113686097639</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>46.38543212432849</v>
       </c>
       <c r="G5" t="n">
-        <v>13.09593442376427</v>
+        <v>0.0154180636632236</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>42.4265965137691</v>
       </c>
       <c r="I5" t="n">
-        <v>13.48221432453148</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3.17758646778214</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.9347112608319772</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4.809660868702075</v>
+      </c>
+      <c r="O5" t="n">
         <v>4.680092101179473</v>
       </c>
-      <c r="M5" t="n">
+      <c r="P5" t="n">
         <v>5.208119098629888</v>
       </c>
-      <c r="N5" t="n">
+      <c r="Q5" t="n">
         <v>5.321154576587962</v>
       </c>
-      <c r="O5" t="n">
+      <c r="R5" t="n">
         <v>5.210196309815951</v>
       </c>
-      <c r="P5" t="n">
+      <c r="S5" t="n">
         <v>5.693429074910782</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="T5" t="n">
         <v>5.731981085500282</v>
       </c>
-      <c r="R5" t="n">
+      <c r="U5" t="n">
         <v>5.260096153727839</v>
       </c>
-      <c r="S5" t="n">
+      <c r="V5" t="n">
+        <v>4.412555880408674</v>
+      </c>
+      <c r="W5" t="n">
         <v>5.394399966908532</v>
       </c>
-      <c r="T5" t="n">
+      <c r="X5" t="n">
         <v>4.58251551727507</v>
       </c>
-      <c r="U5" t="n">
-        <v>15720207000</v>
-      </c>
-      <c r="V5" t="n">
+      <c r="Y5" t="n">
+        <v>28252575000</v>
+      </c>
+      <c r="Z5" t="n">
         <v>132.9</v>
       </c>
     </row>
@@ -840,63 +908,75 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.804293507034864</v>
+        <v>0.0989028151823136</v>
       </c>
       <c r="D6" t="n">
-        <v>8.52673652952029</v>
+        <v>1.855828664040231</v>
       </c>
       <c r="E6" t="n">
-        <v>61.70981388627362</v>
+        <v>5.412686992707014</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>45.35940602714633</v>
       </c>
       <c r="G6" t="n">
-        <v>13.62955172622151</v>
+        <v>0.0548427814661098</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>41.95844399244037</v>
       </c>
       <c r="I6" t="n">
-        <v>13.15452504785336</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.175079303096341</v>
+        <v>3.209619469223997</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.111895879915011</v>
       </c>
       <c r="L6" t="n">
+        <v>0.6823599294366454</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.2560134484419697</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.727918629653245</v>
+      </c>
+      <c r="O6" t="n">
         <v>4.516666774060043</v>
       </c>
-      <c r="M6" t="n">
+      <c r="P6" t="n">
         <v>5.192067546342173</v>
       </c>
-      <c r="N6" t="n">
+      <c r="Q6" t="n">
         <v>5.248338996741795</v>
       </c>
-      <c r="O6" t="n">
+      <c r="R6" t="n">
         <v>5.210087068486874</v>
       </c>
-      <c r="P6" t="n">
+      <c r="S6" t="n">
         <v>5.635039598075843</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="T6" t="n">
         <v>5.74046789800696</v>
       </c>
-      <c r="R6" t="n">
+      <c r="U6" t="n">
         <v>5.20367697581266</v>
       </c>
-      <c r="S6" t="n">
+      <c r="V6" t="n">
+        <v>4.409763389645481</v>
+      </c>
+      <c r="W6" t="n">
         <v>5.388934739706401</v>
       </c>
-      <c r="T6" t="n">
+      <c r="X6" t="n">
         <v>4.539030367181421</v>
       </c>
-      <c r="U6" t="n">
-        <v>15027156000</v>
-      </c>
-      <c r="V6" t="n">
+      <c r="Y6" t="n">
+        <v>27339970000</v>
+      </c>
+      <c r="Z6" t="n">
         <v>141.2</v>
       </c>
     </row>
@@ -912,63 +992,75 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.794305531596105</v>
+        <v>0.3948875523321931</v>
       </c>
       <c r="D7" t="n">
-        <v>8.323228391238654</v>
+        <v>1.839322269362168</v>
       </c>
       <c r="E7" t="n">
-        <v>63.1286987370936</v>
+        <v>5.025265449168124</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>44.05836840904697</v>
       </c>
       <c r="G7" t="n">
-        <v>13.48995528881666</v>
+        <v>0.0636360491215814</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>42.85534268149943</v>
       </c>
       <c r="I7" t="n">
-        <v>12.09944570172849</v>
+        <v>1.701540087033856</v>
       </c>
       <c r="J7" t="n">
-        <v>1.164366349526484</v>
+        <v>2.329229039448659</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.5951642869708914</v>
       </c>
       <c r="L7" t="n">
+        <v>1.046739785985655</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0905043900304674</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.850153520627408</v>
+      </c>
+      <c r="O7" t="n">
         <v>4.702750514326955</v>
       </c>
-      <c r="M7" t="n">
+      <c r="P7" t="n">
         <v>5.36480710781687</v>
       </c>
-      <c r="N7" t="n">
+      <c r="Q7" t="n">
         <v>5.330155129309042</v>
       </c>
-      <c r="O7" t="n">
+      <c r="R7" t="n">
         <v>5.272076092937608</v>
       </c>
-      <c r="P7" t="n">
+      <c r="S7" t="n">
         <v>5.798880488548207</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="T7" t="n">
         <v>5.831941094373923</v>
       </c>
-      <c r="R7" t="n">
+      <c r="U7" t="n">
         <v>5.345916345347316</v>
       </c>
-      <c r="S7" t="n">
+      <c r="V7" t="n">
+        <v>4.483341463834376</v>
+      </c>
+      <c r="W7" t="n">
         <v>5.554973017897679</v>
       </c>
-      <c r="T7" t="n">
+      <c r="X7" t="n">
         <v>4.722508651266526</v>
       </c>
-      <c r="U7" t="n">
-        <v>16677483000</v>
-      </c>
-      <c r="V7" t="n">
+      <c r="Y7" t="n">
+        <v>31274726000</v>
+      </c>
+      <c r="Z7" t="n">
         <v>138</v>
       </c>
     </row>
@@ -984,63 +1076,75 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.91023467036363</v>
+        <v>0.3610530066152669</v>
       </c>
       <c r="D8" t="n">
-        <v>8.777389523463707</v>
+        <v>1.770757825322903</v>
       </c>
       <c r="E8" t="n">
-        <v>61.17275019910576</v>
+        <v>4.902162883428725</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>41.8040033129497</v>
       </c>
       <c r="G8" t="n">
-        <v>14.50072715521231</v>
+        <v>0.0712375689475598</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>46.19043648363627</v>
       </c>
       <c r="I8" t="n">
-        <v>13.26764674888961</v>
+        <v>2.12591464237806</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3712517029649771</v>
+        <v>1.893340572866045</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.5804814731735941</v>
       </c>
       <c r="L8" t="n">
+        <v>0.2191964853297326</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0814157453521433</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.905348809082064</v>
+      </c>
+      <c r="O8" t="n">
         <v>4.596331265030552</v>
       </c>
-      <c r="M8" t="n">
+      <c r="P8" t="n">
         <v>5.384953701192524</v>
       </c>
-      <c r="N8" t="n">
+      <c r="Q8" t="n">
         <v>5.337345785799931</v>
       </c>
-      <c r="O8" t="n">
+      <c r="R8" t="n">
         <v>5.276327317460328</v>
       </c>
-      <c r="P8" t="n">
+      <c r="S8" t="n">
         <v>5.83422573496753</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="T8" t="n">
         <v>5.780280464475663</v>
       </c>
-      <c r="R8" t="n">
+      <c r="U8" t="n">
         <v>5.38582442322963</v>
       </c>
-      <c r="S8" t="n">
+      <c r="V8" t="n">
+        <v>4.557973744758631</v>
+      </c>
+      <c r="W8" t="n">
         <v>5.657110092038305</v>
       </c>
-      <c r="T8" t="n">
+      <c r="X8" t="n">
         <v>4.707365717589783</v>
       </c>
-      <c r="U8" t="n">
-        <v>15923698000</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="Y8" t="n">
+        <v>31036994000</v>
+      </c>
+      <c r="Z8" t="n">
         <v>138.5</v>
       </c>
     </row>
@@ -1056,63 +1160,75 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.902385725697662</v>
+        <v>0.3092151897135169</v>
       </c>
       <c r="D9" t="n">
-        <v>8.626089597302883</v>
+        <v>1.86505235312745</v>
       </c>
       <c r="E9" t="n">
-        <v>63.36417912418494</v>
+        <v>4.94712148951545</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>43.81985333487599</v>
       </c>
       <c r="G9" t="n">
-        <v>13.91721921344334</v>
+        <v>0.1079360686362693</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>44.73629934545313</v>
       </c>
       <c r="I9" t="n">
-        <v>11.88161708233296</v>
+        <v>1.908805563203436</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3085092570382319</v>
+        <v>1.575040918151352</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.5696845950516957</v>
       </c>
       <c r="L9" t="n">
+        <v>0.160991142271716</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5.108003937675567</v>
+      </c>
+      <c r="O9" t="n">
         <v>4.712408933916262</v>
       </c>
-      <c r="M9" t="n">
+      <c r="P9" t="n">
         <v>5.516247338538519</v>
       </c>
-      <c r="N9" t="n">
+      <c r="Q9" t="n">
         <v>5.409411414053624</v>
       </c>
-      <c r="O9" t="n">
+      <c r="R9" t="n">
         <v>5.4122708539008</v>
       </c>
-      <c r="P9" t="n">
+      <c r="S9" t="n">
         <v>5.939697475569493</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="T9" t="n">
         <v>5.856961264242846</v>
       </c>
-      <c r="R9" t="n">
+      <c r="U9" t="n">
         <v>5.52042039868253</v>
       </c>
-      <c r="S9" t="n">
+      <c r="V9" t="n">
+        <v>4.601463296488943</v>
+      </c>
+      <c r="W9" t="n">
         <v>5.776599148587745</v>
       </c>
-      <c r="T9" t="n">
+      <c r="X9" t="n">
         <v>4.773984254268113</v>
       </c>
-      <c r="U9" t="n">
-        <v>54529320000</v>
-      </c>
-      <c r="V9" t="n">
+      <c r="Y9" t="n">
+        <v>104495190000</v>
+      </c>
+      <c r="Z9" t="n">
         <v>139.5</v>
       </c>
     </row>
@@ -1128,63 +1244,75 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.829996629256753</v>
+        <v>0.3173541155777533</v>
       </c>
       <c r="D10" t="n">
-        <v>8.266385425235054</v>
+        <v>1.853358084451284</v>
       </c>
       <c r="E10" t="n">
-        <v>62.67707760454822</v>
+        <v>4.727114960631592</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>43.37816916893532</v>
       </c>
       <c r="G10" t="n">
-        <v>14.83903186542297</v>
+        <v>0.0940044846908637</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>45.83757772537844</v>
       </c>
       <c r="I10" t="n">
-        <v>12.38750847553702</v>
+        <v>1.754903914575647</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1.412283738391004</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.6252338073681035</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5.084938530620289</v>
+      </c>
+      <c r="O10" t="n">
         <v>4.753159037381939</v>
       </c>
-      <c r="M10" t="n">
+      <c r="P10" t="n">
         <v>5.526448459373285</v>
       </c>
-      <c r="N10" t="n">
+      <c r="Q10" t="n">
         <v>5.459542983423417</v>
       </c>
-      <c r="O10" t="n">
+      <c r="R10" t="n">
         <v>5.457242332518927</v>
       </c>
-      <c r="P10" t="n">
+      <c r="S10" t="n">
         <v>5.981616177151595</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="T10" t="n">
         <v>5.84805595676794</v>
       </c>
-      <c r="R10" t="n">
+      <c r="U10" t="n">
         <v>5.505981745890733</v>
       </c>
-      <c r="S10" t="n">
+      <c r="V10" t="n">
+        <v>4.673949727023152</v>
+      </c>
+      <c r="W10" t="n">
         <v>5.750252454082805</v>
       </c>
-      <c r="T10" t="n">
+      <c r="X10" t="n">
         <v>4.814701490083507</v>
       </c>
-      <c r="U10" t="n">
-        <v>36977008000</v>
-      </c>
-      <c r="V10" t="n">
+      <c r="Y10" t="n">
+        <v>71645518000</v>
+      </c>
+      <c r="Z10" t="n">
         <v>143.1</v>
       </c>
     </row>
@@ -1200,63 +1328,75 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.769120662583443</v>
+        <v>0.3156541939384671</v>
       </c>
       <c r="D11" t="n">
-        <v>8.22833332393205</v>
+        <v>2.210985395765775</v>
       </c>
       <c r="E11" t="n">
-        <v>64.09031168210549</v>
+        <v>5.039937009488797</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>44.16893308606213</v>
       </c>
       <c r="G11" t="n">
-        <v>14.22760418597695</v>
+        <v>0.0842821835237295</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>44.37096613442366</v>
       </c>
       <c r="I11" t="n">
-        <v>11.68463014540207</v>
+        <v>1.673445115119446</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1.466774074357267</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.6690228073207244</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5.104429173382616</v>
+      </c>
+      <c r="O11" t="n">
         <v>4.73532088384979</v>
       </c>
-      <c r="M11" t="n">
+      <c r="P11" t="n">
         <v>5.52142093903576</v>
       </c>
-      <c r="N11" t="n">
+      <c r="Q11" t="n">
         <v>5.459372712559857</v>
       </c>
-      <c r="O11" t="n">
+      <c r="R11" t="n">
         <v>5.524735579596999</v>
       </c>
-      <c r="P11" t="n">
+      <c r="S11" t="n">
         <v>5.951657700297862</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="T11" t="n">
         <v>5.871159594390024</v>
       </c>
-      <c r="R11" t="n">
+      <c r="U11" t="n">
         <v>5.582668894310453</v>
       </c>
-      <c r="S11" t="n">
+      <c r="V11" t="n">
+        <v>4.616209039139818</v>
+      </c>
+      <c r="W11" t="n">
         <v>5.77743555878909</v>
       </c>
-      <c r="T11" t="n">
+      <c r="X11" t="n">
         <v>4.791732754765883</v>
       </c>
-      <c r="U11" t="n">
-        <v>18259919000</v>
-      </c>
-      <c r="V11" t="n">
+      <c r="Y11" t="n">
+        <v>36201008000</v>
+      </c>
+      <c r="Z11" t="n">
         <v>147.2</v>
       </c>
     </row>
@@ -1272,63 +1412,75 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.988392340581134</v>
+        <v>0.3464345194319228</v>
       </c>
       <c r="D12" t="n">
-        <v>8.965315817108802</v>
+        <v>2.325246742683747</v>
       </c>
       <c r="E12" t="n">
-        <v>58.87636841159775</v>
+        <v>5.27917733971209</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>40.41812464012048</v>
       </c>
       <c r="G12" t="n">
-        <v>17.51624497633456</v>
+        <v>0.1035780594492101</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>47.87750494055474</v>
       </c>
       <c r="I12" t="n">
-        <v>12.65367845437775</v>
+        <v>1.505761507629702</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1.457779032985905</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.6863932174322096</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5.133796455964578</v>
+      </c>
+      <c r="O12" t="n">
         <v>4.788990621445104</v>
       </c>
-      <c r="M12" t="n">
+      <c r="P12" t="n">
         <v>5.507645958532938</v>
       </c>
-      <c r="N12" t="n">
+      <c r="Q12" t="n">
         <v>5.39698556322996</v>
       </c>
-      <c r="O12" t="n">
+      <c r="R12" t="n">
         <v>5.623837028555773</v>
       </c>
-      <c r="P12" t="n">
+      <c r="S12" t="n">
         <v>5.949287496857821</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="T12" t="n">
         <v>5.812038756910852</v>
       </c>
-      <c r="R12" t="n">
+      <c r="U12" t="n">
         <v>5.577765675612066</v>
       </c>
-      <c r="S12" t="n">
+      <c r="V12" t="n">
+        <v>4.660888706494492</v>
+      </c>
+      <c r="W12" t="n">
         <v>5.67205099729549</v>
       </c>
-      <c r="T12" t="n">
+      <c r="X12" t="n">
         <v>4.847410261736004</v>
       </c>
-      <c r="U12" t="n">
-        <v>16304579000</v>
-      </c>
-      <c r="V12" t="n">
+      <c r="Y12" t="n">
+        <v>34204155000</v>
+      </c>
+      <c r="Z12" t="n">
         <v>147.7</v>
       </c>
     </row>
@@ -1344,63 +1496,75 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.848772346354218</v>
+        <v>0.7175750609611891</v>
       </c>
       <c r="D13" t="n">
-        <v>7.323220219137688</v>
+        <v>2.775524575729342</v>
       </c>
       <c r="E13" t="n">
-        <v>58.46580293048931</v>
+        <v>4.477881661289274</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>41.32282182023617</v>
       </c>
       <c r="G13" t="n">
-        <v>19.03701381602357</v>
+        <v>0.0969962018182223</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>48.78959119069869</v>
       </c>
       <c r="I13" t="n">
-        <v>13.32519068799522</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1.401683115201535</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>0.41792637406557</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5.210305455899594</v>
+      </c>
+      <c r="O13" t="n">
         <v>4.860587345130021</v>
       </c>
-      <c r="M13" t="n">
+      <c r="P13" t="n">
         <v>5.630853272749199</v>
       </c>
-      <c r="N13" t="n">
+      <c r="Q13" t="n">
         <v>5.468017969330994</v>
       </c>
-      <c r="O13" t="n">
+      <c r="R13" t="n">
         <v>5.665145607958486</v>
       </c>
-      <c r="P13" t="n">
+      <c r="S13" t="n">
         <v>6.018739183303569</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="T13" t="n">
         <v>5.859303674852162</v>
       </c>
-      <c r="R13" t="n">
+      <c r="U13" t="n">
         <v>5.668397089278836</v>
       </c>
-      <c r="S13" t="n">
+      <c r="V13" t="n">
+        <v>4.799090891194417</v>
+      </c>
+      <c r="W13" t="n">
         <v>5.797728050457213</v>
       </c>
-      <c r="T13" t="n">
+      <c r="X13" t="n">
         <v>4.953006224363542</v>
       </c>
-      <c r="U13" t="n">
-        <v>17149218000</v>
-      </c>
-      <c r="V13" t="n">
+      <c r="Y13" t="n">
+        <v>36477717000</v>
+      </c>
+      <c r="Z13" t="n">
         <v>150.2</v>
       </c>
     </row>
@@ -1416,63 +1580,75 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.879704037131179</v>
+        <v>0.5764188477463719</v>
       </c>
       <c r="D14" t="n">
-        <v>7.335999862684443</v>
+        <v>2.822446628171708</v>
       </c>
       <c r="E14" t="n">
-        <v>59.2802081215812</v>
+        <v>4.250344209287805</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>45.93145745021227</v>
       </c>
       <c r="G14" t="n">
-        <v>18.22974052802257</v>
+        <v>0.1114167302348025</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>44.49638204508508</v>
       </c>
       <c r="I14" t="n">
-        <v>13.2743474505806</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1.425899878233725</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>0.3856342110282398</v>
       </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5.22321658745924</v>
+      </c>
+      <c r="O14" t="n">
         <v>4.770515147028341</v>
       </c>
-      <c r="M14" t="n">
+      <c r="P14" t="n">
         <v>5.570022493779399</v>
       </c>
-      <c r="N14" t="n">
+      <c r="Q14" t="n">
         <v>5.46873503428068</v>
       </c>
-      <c r="O14" t="n">
+      <c r="R14" t="n">
         <v>5.822779598674465</v>
       </c>
-      <c r="P14" t="n">
+      <c r="S14" t="n">
         <v>5.946624050292827</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="T14" t="n">
         <v>5.849036536381251</v>
       </c>
-      <c r="R14" t="n">
+      <c r="U14" t="n">
         <v>5.647776350776669</v>
       </c>
-      <c r="S14" t="n">
+      <c r="V14" t="n">
+        <v>4.741360508479988</v>
+      </c>
+      <c r="W14" t="n">
         <v>5.720082218050309</v>
       </c>
-      <c r="T14" t="n">
+      <c r="X14" t="n">
         <v>4.996401167087179</v>
       </c>
-      <c r="U14" t="n">
-        <v>16720611000</v>
-      </c>
-      <c r="V14" t="n">
+      <c r="Y14" t="n">
+        <v>37392948000</v>
+      </c>
+      <c r="Z14" t="n">
         <v>153.7</v>
       </c>
     </row>
@@ -1488,63 +1664,75 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.66406392210672</v>
+        <v>0.7091471797300092</v>
       </c>
       <c r="D15" t="n">
-        <v>6.889142576828192</v>
+        <v>2.571330451496104</v>
       </c>
       <c r="E15" t="n">
-        <v>59.95966331540163</v>
+        <v>3.95851988289535</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>46.38708700615953</v>
       </c>
       <c r="G15" t="n">
-        <v>18.89356229324729</v>
+        <v>0.1242554211317696</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>44.06286835543211</v>
       </c>
       <c r="I15" t="n">
-        <v>12.59356789241616</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1.622220701388532</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.398149240094568</v>
       </c>
       <c r="L15" t="n">
+        <v>0.1664217616720235</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5.118532567489065</v>
+      </c>
+      <c r="O15" t="n">
         <v>4.796534040523403</v>
       </c>
-      <c r="M15" t="n">
+      <c r="P15" t="n">
         <v>5.558332777110733</v>
       </c>
-      <c r="N15" t="n">
+      <c r="Q15" t="n">
         <v>5.456346254223955</v>
       </c>
-      <c r="O15" t="n">
+      <c r="R15" t="n">
         <v>5.837934529325819</v>
       </c>
-      <c r="P15" t="n">
+      <c r="S15" t="n">
         <v>5.982398612048843</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="T15" t="n">
         <v>5.885770656116809</v>
       </c>
-      <c r="R15" t="n">
+      <c r="U15" t="n">
         <v>5.60906883726267</v>
       </c>
-      <c r="S15" t="n">
+      <c r="V15" t="n">
+        <v>4.84363575580437</v>
+      </c>
+      <c r="W15" t="n">
         <v>5.736314242985138</v>
       </c>
-      <c r="T15" t="n">
+      <c r="X15" t="n">
         <v>5.076672725638416</v>
       </c>
-      <c r="U15" t="n">
-        <v>17645476000</v>
-      </c>
-      <c r="V15" t="n">
+      <c r="Y15" t="n">
+        <v>38955242000</v>
+      </c>
+      <c r="Z15" t="n">
         <v>154.3</v>
       </c>
     </row>
@@ -1560,63 +1748,75 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.510354392350833</v>
+        <v>1.061057154798091</v>
       </c>
       <c r="D16" t="n">
-        <v>5.875528159414668</v>
+        <v>1.676977696468386</v>
       </c>
       <c r="E16" t="n">
-        <v>56.51935613326453</v>
+        <v>3.25272881105586</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>45.04704515726037</v>
       </c>
       <c r="G16" t="n">
-        <v>24.44983948811917</v>
+        <v>0.1305085097648471</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>46.30906370566444</v>
       </c>
       <c r="I16" t="n">
-        <v>11.6449218268508</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1.941707513376404</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.4358914388498471</v>
       </c>
       <c r="L16" t="n">
+        <v>0.1450200127617611</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5.130963193583406</v>
+      </c>
+      <c r="O16" t="n">
         <v>4.776767789701273</v>
       </c>
-      <c r="M16" t="n">
+      <c r="P16" t="n">
         <v>5.546777740128277</v>
       </c>
-      <c r="N16" t="n">
+      <c r="Q16" t="n">
         <v>5.482595346716701</v>
       </c>
-      <c r="O16" t="n">
+      <c r="R16" t="n">
         <v>6.001315842005465</v>
       </c>
-      <c r="P16" t="n">
+      <c r="S16" t="n">
         <v>5.983180358291727</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="T16" t="n">
         <v>5.896521769590768</v>
       </c>
-      <c r="R16" t="n">
+      <c r="U16" t="n">
         <v>5.628232485857152</v>
       </c>
-      <c r="S16" t="n">
+      <c r="V16" t="n">
+        <v>4.868687584544564</v>
+      </c>
+      <c r="W16" t="n">
         <v>5.792403629070463</v>
       </c>
-      <c r="T16" t="n">
+      <c r="X16" t="n">
         <v>5.138324612262206</v>
       </c>
-      <c r="U16" t="n">
-        <v>19349035000</v>
-      </c>
-      <c r="V16" t="n">
+      <c r="Y16" t="n">
+        <v>42097638000</v>
+      </c>
+      <c r="Z16" t="n">
         <v>162.2</v>
       </c>
     </row>
@@ -1632,63 +1832,75 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.0323974183878</v>
+        <v>0.9838295103794886</v>
       </c>
       <c r="D17" t="n">
-        <v>4.221291819513397</v>
+        <v>1.150887254127761</v>
       </c>
       <c r="E17" t="n">
-        <v>63.26031649142075</v>
+        <v>3.026736934991515</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>42.49450729148651</v>
       </c>
       <c r="G17" t="n">
-        <v>21.64331691053404</v>
+        <v>0.7769307464943215</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>49.10333836638777</v>
       </c>
       <c r="I17" t="n">
-        <v>9.842677360144014</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1.762379791606281</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.3882179605004676</v>
       </c>
       <c r="L17" t="n">
+        <v>0.3131721440258874</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5.231750096181371</v>
+      </c>
+      <c r="O17" t="n">
         <v>4.765842413975779</v>
       </c>
-      <c r="M17" t="n">
+      <c r="P17" t="n">
         <v>5.554470128160384</v>
       </c>
-      <c r="N17" t="n">
+      <c r="Q17" t="n">
         <v>5.481346998301677</v>
       </c>
-      <c r="O17" t="n">
-        <v>5.9682982597063</v>
-      </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
+        <v>5.920854326415729</v>
+      </c>
+      <c r="S17" t="n">
         <v>6.055377858537573</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="T17" t="n">
         <v>5.927832272106348</v>
       </c>
-      <c r="R17" t="n">
+      <c r="U17" t="n">
         <v>5.671947772139333</v>
       </c>
-      <c r="S17" t="n">
-        <v>5.832673920647911</v>
-      </c>
-      <c r="T17" t="n">
+      <c r="V17" t="n">
+        <v>4.870069709592</v>
+      </c>
+      <c r="W17" t="n">
+        <v>5.801544185058611</v>
+      </c>
+      <c r="X17" t="n">
         <v>5.093197923557418</v>
       </c>
-      <c r="U17" t="n">
-        <v>50917020000</v>
-      </c>
-      <c r="V17" t="n">
+      <c r="Y17" t="n">
+        <v>85888865000</v>
+      </c>
+      <c r="Z17" t="n">
         <v>163</v>
       </c>
     </row>
@@ -1704,63 +1916,75 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.034096549355026</v>
+        <v>1.340074929476397</v>
       </c>
       <c r="D18" t="n">
-        <v>3.551841242166937</v>
+        <v>1.07854277641667</v>
       </c>
       <c r="E18" t="n">
-        <v>61.58334431838873</v>
+        <v>2.530493250439627</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>40.34165050101595</v>
       </c>
       <c r="G18" t="n">
-        <v>22.8368744589118</v>
+        <v>2.609531270994983</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4375133484830216</v>
+        <v>48.80234656837887</v>
       </c>
       <c r="I18" t="n">
-        <v>10.5563300826945</v>
+        <v>0.2532842354635228</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2.487590618268375</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.3080973903862281</v>
       </c>
       <c r="L18" t="n">
+        <v>0.2483884591593798</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>5.297617124487539</v>
+      </c>
+      <c r="O18" t="n">
         <v>4.891401201588273</v>
       </c>
-      <c r="M18" t="n">
+      <c r="P18" t="n">
         <v>5.581012008687198</v>
       </c>
-      <c r="N18" t="n">
+      <c r="Q18" t="n">
         <v>5.491084198820473</v>
       </c>
-      <c r="O18" t="n">
+      <c r="R18" t="n">
         <v>6.003343706622339</v>
       </c>
-      <c r="P18" t="n">
+      <c r="S18" t="n">
         <v>6.080962441457248</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="T18" t="n">
         <v>5.915285210249134</v>
       </c>
-      <c r="R18" t="n">
+      <c r="U18" t="n">
         <v>5.735055014016577</v>
       </c>
-      <c r="S18" t="n">
+      <c r="V18" t="n">
+        <v>5.000382925853788</v>
+      </c>
+      <c r="W18" t="n">
         <v>5.84081605367302</v>
       </c>
-      <c r="T18" t="n">
+      <c r="X18" t="n">
         <v>5.052416789086174</v>
       </c>
-      <c r="U18" t="n">
-        <v>26665015000</v>
-      </c>
-      <c r="V18" t="n">
+      <c r="Y18" t="n">
+        <v>46060111000</v>
+      </c>
+      <c r="Z18" t="n">
         <v>162.2</v>
       </c>
     </row>
@@ -1776,63 +2000,75 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9553576514710695</v>
+        <v>0.9956737879919824</v>
       </c>
       <c r="D19" t="n">
-        <v>2.335859157056186</v>
+        <v>1.16994426835457</v>
       </c>
       <c r="E19" t="n">
-        <v>60.58812748727721</v>
+        <v>1.696920759430388</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>39.97394018748774</v>
       </c>
       <c r="G19" t="n">
-        <v>20.91538243222732</v>
+        <v>2.618407088709243</v>
       </c>
       <c r="H19" t="n">
-        <v>5.418351150322618</v>
+        <v>47.5930033293305</v>
       </c>
       <c r="I19" t="n">
-        <v>9.786922121645604</v>
+        <v>3.144583335687507</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>2.413027906696075</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.3944993363119917</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>5.287205827848895</v>
+      </c>
+      <c r="O19" t="n">
         <v>4.877103901471733</v>
       </c>
-      <c r="M19" t="n">
+      <c r="P19" t="n">
         <v>5.573711767563356</v>
       </c>
-      <c r="N19" t="n">
+      <c r="Q19" t="n">
         <v>5.513912480425678</v>
       </c>
-      <c r="O19" t="n">
+      <c r="R19" t="n">
         <v>6.041087712101386</v>
       </c>
-      <c r="P19" t="n">
+      <c r="S19" t="n">
         <v>6.073344039665362</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="T19" t="n">
         <v>5.85990264930154</v>
       </c>
-      <c r="R19" t="n">
+      <c r="U19" t="n">
         <v>5.730424425412799</v>
       </c>
-      <c r="S19" t="n">
+      <c r="V19" t="n">
+        <v>4.986274289013967</v>
+      </c>
+      <c r="W19" t="n">
         <v>5.737926262479704</v>
       </c>
-      <c r="T19" t="n">
+      <c r="X19" t="n">
         <v>5.098646190049969</v>
       </c>
-      <c r="U19" t="n">
-        <v>27631118000</v>
-      </c>
-      <c r="V19" t="n">
+      <c r="Y19" t="n">
+        <v>47610473000</v>
+      </c>
+      <c r="Z19" t="n">
         <v>166.1</v>
       </c>
     </row>
@@ -1848,63 +2084,75 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.8913587378149982</v>
+        <v>1.542699349091882</v>
       </c>
       <c r="D20" t="n">
-        <v>3.129820856162511</v>
+        <v>1.187818508264526</v>
       </c>
       <c r="E20" t="n">
-        <v>58.22465804706033</v>
+        <v>2.161300943575533</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>38.14146059066545</v>
       </c>
       <c r="G20" t="n">
-        <v>20.77062354897313</v>
+        <v>2.236237076236818</v>
       </c>
       <c r="H20" t="n">
-        <v>5.405958862539556</v>
+        <v>47.97575926761982</v>
       </c>
       <c r="I20" t="n">
-        <v>11.57757994744948</v>
+        <v>3.17826326278335</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>3.067847293510758</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.5086137082518642</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5.275867225226265</v>
+      </c>
+      <c r="O20" t="n">
         <v>4.969049114533534</v>
       </c>
-      <c r="M20" t="n">
+      <c r="P20" t="n">
         <v>5.619820974199119</v>
       </c>
-      <c r="N20" t="n">
+      <c r="Q20" t="n">
         <v>5.563562093880882</v>
       </c>
-      <c r="O20" t="n">
-        <v>5.991314541961288</v>
-      </c>
-      <c r="P20" t="n">
+      <c r="R20" t="n">
+        <v>6.019517373419365</v>
+      </c>
+      <c r="S20" t="n">
         <v>6.143820731875084</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="T20" t="n">
         <v>5.95303555537268</v>
       </c>
-      <c r="R20" t="n">
+      <c r="U20" t="n">
         <v>5.72453239347294</v>
       </c>
-      <c r="S20" t="n">
+      <c r="V20" t="n">
+        <v>5.079228047569239</v>
+      </c>
+      <c r="W20" t="n">
         <v>5.834576830842404</v>
       </c>
-      <c r="T20" t="n">
+      <c r="X20" t="n">
         <v>5.165128758358181</v>
       </c>
-      <c r="U20" t="n">
-        <v>29939573000</v>
-      </c>
-      <c r="V20" t="n">
+      <c r="Y20" t="n">
+        <v>50924699000</v>
+      </c>
+      <c r="Z20" t="n">
         <v>165.4</v>
       </c>
     </row>
@@ -1920,63 +2168,75 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.751163734758536</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7962072933203036</v>
+        <v>2.050520925023454</v>
       </c>
       <c r="E21" t="n">
-        <v>81.07160883725994</v>
+        <v>0.3575721360178402</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>44.21693577359567</v>
       </c>
       <c r="G21" t="n">
-        <v>5.930821462992361</v>
+        <v>4.869520296528352</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>41.84405549199003</v>
       </c>
       <c r="I21" t="n">
-        <v>10.45019867166886</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>6.661395376844653</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>5.365181315364676</v>
+      </c>
+      <c r="O21" t="n">
         <v>5.044392351554939</v>
       </c>
-      <c r="M21" t="n">
+      <c r="P21" t="n">
         <v>5.713468788573279</v>
       </c>
-      <c r="N21" t="n">
+      <c r="Q21" t="n">
         <v>5.592515675871328</v>
       </c>
-      <c r="O21" t="n">
-        <v>6.064436156726807</v>
-      </c>
-      <c r="P21" t="n">
+      <c r="R21" t="n">
+        <v>6.121461573541935</v>
+      </c>
+      <c r="S21" t="n">
         <v>6.205183824245303</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="T21" t="n">
         <v>5.973529711755427</v>
       </c>
-      <c r="R21" t="n">
+      <c r="U21" t="n">
         <v>5.776506170922134</v>
       </c>
-      <c r="S21" t="n">
+      <c r="V21" t="n">
+        <v>5.182401340377518</v>
+      </c>
+      <c r="W21" t="n">
         <v>5.896576801564275</v>
       </c>
-      <c r="T21" t="n">
+      <c r="X21" t="n">
         <v>5.229984955227814</v>
       </c>
-      <c r="U21" t="n">
-        <v>11903056000</v>
-      </c>
-      <c r="V21" t="n">
+      <c r="Y21" t="n">
+        <v>26504582000</v>
+      </c>
+      <c r="Z21" t="n">
         <v>165.6</v>
       </c>
     </row>
@@ -1992,63 +2252,75 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.8355664231360345</v>
+        <v>1.385872086787072</v>
       </c>
       <c r="D22" t="n">
-        <v>2.542533860484649</v>
+        <v>0.8689937775311934</v>
       </c>
       <c r="E22" t="n">
-        <v>55.98087088407436</v>
+        <v>1.56005516429296</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>35.21316063212726</v>
       </c>
       <c r="G22" t="n">
-        <v>16.90213718585584</v>
+        <v>2.266336397846239</v>
       </c>
       <c r="H22" t="n">
-        <v>9.556902447103312</v>
+        <v>48.18758788105091</v>
       </c>
       <c r="I22" t="n">
-        <v>14.18198919934581</v>
+        <v>5.394759211311435</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>4.712097260107599</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>0.4111375889453272</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5.458350738138398</v>
+      </c>
+      <c r="O22" t="n">
         <v>5.106066704566762</v>
       </c>
-      <c r="M22" t="n">
+      <c r="P22" t="n">
         <v>5.70354908967665</v>
       </c>
-      <c r="N22" t="n">
+      <c r="Q22" t="n">
         <v>5.60829891963446</v>
       </c>
-      <c r="O22" t="n">
-        <v>6.158164717832639</v>
-      </c>
-      <c r="P22" t="n">
+      <c r="R22" t="n">
+        <v>6.138525860478522</v>
+      </c>
+      <c r="S22" t="n">
         <v>6.170175403607245</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="T22" t="n">
         <v>5.969091102527061</v>
       </c>
-      <c r="R22" t="n">
+      <c r="U22" t="n">
         <v>5.782316382403756</v>
       </c>
-      <c r="S22" t="n">
+      <c r="V22" t="n">
+        <v>5.20318220499646</v>
+      </c>
+      <c r="W22" t="n">
         <v>5.884602881552337</v>
       </c>
-      <c r="T22" t="n">
+      <c r="X22" t="n">
         <v>5.326953401221941</v>
       </c>
-      <c r="U22" t="n">
-        <v>32460256000</v>
-      </c>
-      <c r="V22" t="n">
+      <c r="Y22" t="n">
+        <v>57503864000</v>
+      </c>
+      <c r="Z22" t="n">
         <v>169.3</v>
       </c>
     </row>
@@ -2064,63 +2336,75 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.7845363904884359</v>
+        <v>1.296382323434801</v>
       </c>
       <c r="D23" t="n">
-        <v>2.308282682906684</v>
+        <v>1.06033860567316</v>
       </c>
       <c r="E23" t="n">
-        <v>59.10868623768691</v>
+        <v>1.405177046956519</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>36.88027317275661</v>
       </c>
       <c r="G23" t="n">
-        <v>16.63009103456468</v>
+        <v>2.332133299913936</v>
       </c>
       <c r="H23" t="n">
-        <v>10.91205323752483</v>
+        <v>46.79980756645848</v>
       </c>
       <c r="I23" t="n">
-        <v>10.25635041682846</v>
+        <v>6.190317726395446</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>3.669488811591264</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>0.3660814468197793</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5.521860862287873</v>
+      </c>
+      <c r="O23" t="n">
         <v>5.171676503682149</v>
       </c>
-      <c r="M23" t="n">
+      <c r="P23" t="n">
         <v>5.737249459943504</v>
       </c>
-      <c r="N23" t="n">
+      <c r="Q23" t="n">
         <v>5.629202605068625</v>
       </c>
-      <c r="O23" t="n">
-        <v>6.294065974658426</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="R23" t="n">
+        <v>6.272329728463355</v>
+      </c>
+      <c r="S23" t="n">
         <v>6.184993902190373</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="T23" t="n">
         <v>6.013739629497909</v>
       </c>
-      <c r="R23" t="n">
+      <c r="U23" t="n">
         <v>5.870708345972182</v>
       </c>
-      <c r="S23" t="n">
+      <c r="V23" t="n">
+        <v>5.097057567680466</v>
+      </c>
+      <c r="W23" t="n">
         <v>5.977061313701207</v>
       </c>
-      <c r="T23" t="n">
+      <c r="X23" t="n">
         <v>5.318267035872698</v>
       </c>
-      <c r="U23" t="n">
-        <v>36636414000</v>
-      </c>
-      <c r="V23" t="n">
+      <c r="Y23" t="n">
+        <v>64581257000</v>
+      </c>
+      <c r="Z23" t="n">
         <v>173.8</v>
       </c>
     </row>
@@ -2136,63 +2420,75 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.3755391458181911</v>
+        <v>0.9223191151827536</v>
       </c>
       <c r="D24" t="n">
-        <v>2.652760567921075</v>
+        <v>1.175397526313663</v>
       </c>
       <c r="E24" t="n">
-        <v>62.05694151557339</v>
+        <v>1.531167333684999</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>38.84082367431473</v>
       </c>
       <c r="G24" t="n">
-        <v>14.87721532513786</v>
+        <v>2.210965500548044</v>
       </c>
       <c r="H24" t="n">
-        <v>12.07202564633749</v>
+        <v>45.67165318069968</v>
       </c>
       <c r="I24" t="n">
-        <v>7.965517799211987</v>
+        <v>6.967945597730798</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2.282955656814607</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>0.3967724147107209</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5.580748133801471</v>
+      </c>
+      <c r="O24" t="n">
         <v>5.191121824753271</v>
       </c>
-      <c r="M24" t="n">
+      <c r="P24" t="n">
         <v>5.683069453829514</v>
       </c>
-      <c r="N24" t="n">
+      <c r="Q24" t="n">
         <v>5.668120720368221</v>
       </c>
-      <c r="O24" t="n">
-        <v>6.356853897254239</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="R24" t="n">
+        <v>6.375535741743472</v>
+      </c>
+      <c r="S24" t="n">
         <v>6.155027902469199</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="T24" t="n">
         <v>6.031598316574446</v>
       </c>
-      <c r="R24" t="n">
+      <c r="U24" t="n">
         <v>5.937483462230671</v>
       </c>
-      <c r="S24" t="n">
+      <c r="V24" t="n">
+        <v>5.137502826612432</v>
+      </c>
+      <c r="W24" t="n">
         <v>6.024826804424126</v>
       </c>
-      <c r="T24" t="n">
+      <c r="X24" t="n">
         <v>5.331268451923534</v>
       </c>
-      <c r="U24" t="n">
-        <v>40118321000</v>
-      </c>
-      <c r="V24" t="n">
+      <c r="Y24" t="n">
+        <v>69505336000</v>
+      </c>
+      <c r="Z24" t="n">
         <v>173.5</v>
       </c>
     </row>
@@ -2208,63 +2504,75 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.3254920720617215</v>
+        <v>0.8885132368788761</v>
       </c>
       <c r="D25" t="n">
-        <v>2.848283186430271</v>
+        <v>0.5117137316079975</v>
       </c>
       <c r="E25" t="n">
-        <v>64.58870374312252</v>
+        <v>1.71094354351929</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>42.05232868239545</v>
       </c>
       <c r="G25" t="n">
-        <v>12.07679778897014</v>
+        <v>2.248160365315699</v>
       </c>
       <c r="H25" t="n">
-        <v>12.35012872522004</v>
+        <v>42.58921250113261</v>
       </c>
       <c r="I25" t="n">
-        <v>7.810594484195311</v>
+        <v>7.418634883187253</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>2.329420382582125</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>0.2510726733806966</v>
       </c>
       <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>5.560066042879604</v>
+      </c>
+      <c r="O25" t="n">
         <v>5.125510369475787</v>
       </c>
-      <c r="M25" t="n">
+      <c r="P25" t="n">
         <v>5.558872298156878</v>
       </c>
-      <c r="N25" t="n">
+      <c r="Q25" t="n">
         <v>5.702281307778702</v>
       </c>
-      <c r="O25" t="n">
+      <c r="R25" t="n">
         <v>6.401983493082342</v>
       </c>
-      <c r="P25" t="n">
+      <c r="S25" t="n">
         <v>5.971465866353856</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="T25" t="n">
         <v>6.015425214347873</v>
       </c>
-      <c r="R25" t="n">
+      <c r="U25" t="n">
         <v>5.870285142480805</v>
       </c>
-      <c r="S25" t="n">
+      <c r="V25" t="n">
+        <v>4.953782763214289</v>
+      </c>
+      <c r="W25" t="n">
         <v>6.020100581781886</v>
       </c>
-      <c r="T25" t="n">
+      <c r="X25" t="n">
         <v>5.375787540139199</v>
       </c>
-      <c r="U25" t="n">
-        <v>41308533000</v>
-      </c>
-      <c r="V25" t="n">
+      <c r="Y25" t="n">
+        <v>68768137000</v>
+      </c>
+      <c r="Z25" t="n">
         <v>178.6</v>
       </c>
     </row>
@@ -2280,63 +2588,75 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.2489967459598722</v>
+        <v>0.9458116510162377</v>
       </c>
       <c r="D26" t="n">
-        <v>3.01014001725497</v>
+        <v>0.4932093937962984</v>
       </c>
       <c r="E26" t="n">
-        <v>64.81953659202756</v>
+        <v>1.821749476055391</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>42.28170399028462</v>
       </c>
       <c r="G26" t="n">
-        <v>12.3012666456735</v>
+        <v>2.007693990107675</v>
       </c>
       <c r="H26" t="n">
-        <v>11.52703799907186</v>
+        <v>42.91311727873083</v>
       </c>
       <c r="I26" t="n">
-        <v>8.093022000012231</v>
+        <v>6.976212174485381</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2.426347128364653</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>0.1341549171589136</v>
       </c>
       <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>5.523937828254207</v>
+      </c>
+      <c r="O26" t="n">
         <v>4.968353855147478</v>
       </c>
-      <c r="M26" t="n">
+      <c r="P26" t="n">
         <v>5.494377479553683</v>
       </c>
-      <c r="N26" t="n">
+      <c r="Q26" t="n">
         <v>5.674078999474445</v>
       </c>
-      <c r="O26" t="n">
+      <c r="R26" t="n">
         <v>6.323731569220806</v>
       </c>
-      <c r="P26" t="n">
+      <c r="S26" t="n">
         <v>5.812816228382959</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="T26" t="n">
         <v>5.888296095302036</v>
       </c>
-      <c r="R26" t="n">
+      <c r="U26" t="n">
         <v>5.824553662862312</v>
       </c>
-      <c r="S26" t="n">
+      <c r="V26" t="n">
+        <v>4.972794910401873</v>
+      </c>
+      <c r="W26" t="n">
         <v>5.853236385774826</v>
       </c>
-      <c r="T26" t="n">
+      <c r="X26" t="n">
         <v>5.262897386537107</v>
       </c>
-      <c r="U26" t="n">
-        <v>40222614000</v>
-      </c>
-      <c r="V26" t="n">
+      <c r="Y26" t="n">
+        <v>66461224000</v>
+      </c>
+      <c r="Z26" t="n">
         <v>187.9</v>
       </c>
     </row>
@@ -2352,63 +2672,75 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.2058739197571476</v>
+        <v>0.7948564752071696</v>
       </c>
       <c r="D27" t="n">
-        <v>2.758146713103509</v>
+        <v>0.4720864103499043</v>
       </c>
       <c r="E27" t="n">
-        <v>63.10860552653904</v>
+        <v>1.575929612457694</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>37.99293343346854</v>
       </c>
       <c r="G27" t="n">
-        <v>12.1904481875426</v>
+        <v>8.870760438752901</v>
       </c>
       <c r="H27" t="n">
-        <v>12.58399477633749</v>
+        <v>40.67368087519819</v>
       </c>
       <c r="I27" t="n">
-        <v>8.770128674988904</v>
+        <v>7.190150515499044</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2.069909707327493</v>
       </c>
       <c r="K27" t="n">
-        <v>0.3828022017313096</v>
+        <v>0.140969821102854</v>
       </c>
       <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.218722710636218</v>
+      </c>
+      <c r="N27" t="n">
+        <v>5.561988454971673</v>
+      </c>
+      <c r="O27" t="n">
         <v>4.916031580587534</v>
       </c>
-      <c r="M27" t="n">
+      <c r="P27" t="n">
         <v>5.409724596882461</v>
       </c>
-      <c r="N27" t="n">
+      <c r="Q27" t="n">
         <v>5.613018615798221</v>
       </c>
-      <c r="O27" t="n">
+      <c r="R27" t="n">
         <v>6.480044561926653</v>
       </c>
-      <c r="P27" t="n">
+      <c r="S27" t="n">
         <v>5.60193434706483</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="T27" t="n">
         <v>5.870821198687071</v>
       </c>
-      <c r="R27" t="n">
+      <c r="U27" t="n">
         <v>5.712577002170785</v>
       </c>
-      <c r="S27" t="n">
+      <c r="V27" t="n">
+        <v>4.90808567514792</v>
+      </c>
+      <c r="W27" t="n">
         <v>5.875913411075747</v>
       </c>
-      <c r="T27" t="n">
+      <c r="X27" t="n">
         <v>5.331461991710737</v>
       </c>
-      <c r="U27" t="n">
-        <v>36288715000</v>
-      </c>
-      <c r="V27" t="n">
+      <c r="Y27" t="n">
+        <v>63511466000</v>
+      </c>
+      <c r="Z27" t="n">
         <v>200.5</v>
       </c>
     </row>
@@ -2424,63 +2756,75 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.1498892201963119</v>
+        <v>0.6253380407197443</v>
       </c>
       <c r="D28" t="n">
-        <v>2.620350188875227</v>
+        <v>0.4220053092379799</v>
       </c>
       <c r="E28" t="n">
-        <v>63.34359222233863</v>
+        <v>1.458262647729008</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>37.02499184467038</v>
       </c>
       <c r="G28" t="n">
-        <v>13.3755464269255</v>
+        <v>8.799216836532226</v>
       </c>
       <c r="H28" t="n">
-        <v>12.48942369434416</v>
+        <v>42.41639908977379</v>
       </c>
       <c r="I28" t="n">
-        <v>7.703031709312767</v>
+        <v>6.950544298409788</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>2.008399528063284</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3181665380074033</v>
+        <v>0.1177781406661185</v>
       </c>
       <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.1770642641976816</v>
+      </c>
+      <c r="N28" t="n">
+        <v>5.301611951747788</v>
+      </c>
+      <c r="O28" t="n">
         <v>4.744845149483041</v>
       </c>
-      <c r="M28" t="n">
+      <c r="P28" t="n">
         <v>5.399293283888039</v>
       </c>
-      <c r="N28" t="n">
+      <c r="Q28" t="n">
         <v>5.653541215432804</v>
       </c>
-      <c r="O28" t="n">
+      <c r="R28" t="n">
         <v>6.193077992344528</v>
       </c>
-      <c r="P28" t="n">
+      <c r="S28" t="n">
         <v>5.600937284305436</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="T28" t="n">
         <v>5.870764730880892</v>
       </c>
-      <c r="R28" t="n">
+      <c r="U28" t="n">
         <v>5.61695285494033</v>
       </c>
-      <c r="S28" t="n">
+      <c r="V28" t="n">
+        <v>4.916617562818702</v>
+      </c>
+      <c r="W28" t="n">
         <v>5.738087282279983</v>
       </c>
-      <c r="T28" t="n">
+      <c r="X28" t="n">
         <v>5.123963979403259</v>
       </c>
-      <c r="U28" t="n">
-        <v>38894725000</v>
-      </c>
-      <c r="V28" t="n">
+      <c r="Y28" t="n">
+        <v>69889879000</v>
+      </c>
+      <c r="Z28" t="n">
         <v>196.9</v>
       </c>
     </row>
@@ -2496,63 +2840,75 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0943085164238755</v>
+        <v>0.2646232951669272</v>
       </c>
       <c r="D29" t="n">
-        <v>2.577220162703305</v>
+        <v>0.4268000124387986</v>
       </c>
       <c r="E29" t="n">
-        <v>70.14141285243069</v>
+        <v>1.453097294597928</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>40.07915872541334</v>
       </c>
       <c r="G29" t="n">
-        <v>11.0646754819023</v>
+        <v>7.978851189034055</v>
       </c>
       <c r="H29" t="n">
-        <v>7.736300517724041</v>
+        <v>41.81297340863626</v>
       </c>
       <c r="I29" t="n">
-        <v>7.811717240766897</v>
+        <v>4.361908041534869</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>2.175517348085147</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5743652280489072</v>
+        <v>0.1607770632408997</v>
       </c>
       <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.286293621851769</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4.924278221823624</v>
+      </c>
+      <c r="O29" t="n">
         <v>4.715816678754136</v>
       </c>
-      <c r="M29" t="n">
+      <c r="P29" t="n">
         <v>5.132321833969698</v>
       </c>
-      <c r="N29" t="n">
+      <c r="Q29" t="n">
         <v>5.508010884984633</v>
       </c>
-      <c r="O29" t="n">
+      <c r="R29" t="n">
         <v>5.956743710177485</v>
       </c>
-      <c r="P29" t="n">
+      <c r="S29" t="n">
         <v>5.128655298924384</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="T29" t="n">
         <v>5.734667270073004</v>
       </c>
-      <c r="R29" t="n">
+      <c r="U29" t="n">
         <v>5.333732804170261</v>
       </c>
-      <c r="S29" t="n">
+      <c r="V29" t="n">
+        <v>4.35632415297757</v>
+      </c>
+      <c r="W29" t="n">
         <v>5.445918060081674</v>
       </c>
-      <c r="T29" t="n">
+      <c r="X29" t="n">
         <v>4.996739139392761</v>
       </c>
-      <c r="U29" t="n">
-        <v>29245503000</v>
-      </c>
-      <c r="V29" t="n">
+      <c r="Y29" t="n">
+        <v>51869961000</v>
+      </c>
+      <c r="Z29" t="n">
         <v>170.9</v>
       </c>
     </row>
@@ -2568,63 +2924,75 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0295317180580206</v>
+        <v>0.317874005489192</v>
       </c>
       <c r="D30" t="n">
-        <v>2.777433749376904</v>
+        <v>0.3964280493183162</v>
       </c>
       <c r="E30" t="n">
-        <v>70.3298624771937</v>
+        <v>1.745391776243555</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>44.79205602474602</v>
       </c>
       <c r="G30" t="n">
-        <v>9.814509273757626</v>
+        <v>6.824586246191544</v>
       </c>
       <c r="H30" t="n">
-        <v>8.337853288994355</v>
+        <v>37.09074293711529</v>
       </c>
       <c r="I30" t="n">
-        <v>8.217433182492508</v>
+        <v>5.239664335972313</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>2.350736979378524</v>
       </c>
       <c r="K30" t="n">
-        <v>0.4933763101268797</v>
+        <v>0.1829208691444898</v>
       </c>
       <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.059598776400756</v>
+      </c>
+      <c r="N30" t="n">
+        <v>4.895673325838727</v>
+      </c>
+      <c r="O30" t="n">
         <v>4.627322969734951</v>
       </c>
-      <c r="M30" t="n">
+      <c r="P30" t="n">
         <v>5.042263199084529</v>
       </c>
-      <c r="N30" t="n">
+      <c r="Q30" t="n">
         <v>5.38802096915928</v>
       </c>
-      <c r="O30" t="n">
+      <c r="R30" t="n">
         <v>5.828003976392832</v>
       </c>
-      <c r="P30" t="n">
+      <c r="S30" t="n">
         <v>4.779207541144356</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="T30" t="n">
         <v>5.645588260601277</v>
       </c>
-      <c r="R30" t="n">
+      <c r="U30" t="n">
         <v>5.08821346639441</v>
       </c>
-      <c r="S30" t="n">
+      <c r="V30" t="n">
+        <v>3.903587563538361</v>
+      </c>
+      <c r="W30" t="n">
         <v>5.484755461647988</v>
       </c>
-      <c r="T30" t="n">
+      <c r="X30" t="n">
         <v>4.870529954754412</v>
       </c>
-      <c r="U30" t="n">
-        <v>25684249000</v>
-      </c>
-      <c r="V30" t="n">
+      <c r="Y30" t="n">
+        <v>40871225000</v>
+      </c>
+      <c r="Z30" t="n">
         <v>168.1</v>
       </c>
     </row>
@@ -2640,63 +3008,75 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0431465486476985</v>
+        <v>0.3507455819913728</v>
       </c>
       <c r="D31" t="n">
-        <v>2.521573624880793</v>
+        <v>0.3703131691228331</v>
       </c>
       <c r="E31" t="n">
-        <v>68.70270022796016</v>
+        <v>1.46752823079919</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2094122015410763</v>
+        <v>40.47494498082515</v>
       </c>
       <c r="G31" t="n">
-        <v>10.56781951758036</v>
+        <v>5.655459083422473</v>
       </c>
       <c r="H31" t="n">
-        <v>9.163127326909354</v>
+        <v>43.42694328827273</v>
       </c>
       <c r="I31" t="n">
-        <v>8.136987557612281</v>
+        <v>5.332839740216869</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>2.342087776470461</v>
       </c>
       <c r="K31" t="n">
-        <v>0.6552329948682669</v>
+        <v>0.1977997226548019</v>
       </c>
       <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.3813384262241167</v>
+      </c>
+      <c r="N31" t="n">
+        <v>5.04006461046321</v>
+      </c>
+      <c r="O31" t="n">
         <v>4.646120175246358</v>
       </c>
-      <c r="M31" t="n">
+      <c r="P31" t="n">
         <v>5.204830489946389</v>
       </c>
-      <c r="N31" t="n">
+      <c r="Q31" t="n">
         <v>5.473026659589078</v>
       </c>
-      <c r="O31" t="n">
+      <c r="R31" t="n">
         <v>5.923827888596244</v>
       </c>
-      <c r="P31" t="n">
+      <c r="S31" t="n">
         <v>5.079912535411032</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="T31" t="n">
         <v>5.72505464976542</v>
       </c>
-      <c r="R31" t="n">
+      <c r="U31" t="n">
         <v>5.253790566066715</v>
       </c>
-      <c r="S31" t="n">
+      <c r="V31" t="n">
+        <v>4.17561731048628</v>
+      </c>
+      <c r="W31" t="n">
         <v>5.661674948926651</v>
       </c>
-      <c r="T31" t="n">
+      <c r="X31" t="n">
         <v>4.955122541153201</v>
       </c>
-      <c r="U31" t="n">
-        <v>28526036000</v>
-      </c>
-      <c r="V31" t="n">
+      <c r="Y31" t="n">
+        <v>49014730000</v>
+      </c>
+      <c r="Z31" t="n">
         <v>174.1</v>
       </c>
     </row>
@@ -2712,63 +3092,75 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.1341321112193398</v>
+        <v>0.518692277909911</v>
       </c>
       <c r="D32" t="n">
-        <v>2.774303883919075</v>
+        <v>0.4175163354908727</v>
       </c>
       <c r="E32" t="n">
-        <v>70.33989734441496</v>
+        <v>1.577569050754756</v>
       </c>
       <c r="F32" t="n">
-        <v>0.272335240398431</v>
+        <v>40.77754784326142</v>
       </c>
       <c r="G32" t="n">
-        <v>9.139413549492255</v>
+        <v>4.74146815309879</v>
       </c>
       <c r="H32" t="n">
-        <v>8.649743796440394</v>
+        <v>44.14733753909712</v>
       </c>
       <c r="I32" t="n">
-        <v>8.164145061348281</v>
+        <v>4.918555674206144</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>2.443205096674214</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5260290127672598</v>
+        <v>0.1589889981883969</v>
       </c>
       <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.2991190313183851</v>
+      </c>
+      <c r="N32" t="n">
+        <v>5.230680708036298</v>
+      </c>
+      <c r="O32" t="n">
         <v>4.684812822094692</v>
       </c>
-      <c r="M32" t="n">
+      <c r="P32" t="n">
         <v>5.377498144686424</v>
       </c>
-      <c r="N32" t="n">
+      <c r="Q32" t="n">
         <v>5.572876214084614</v>
       </c>
-      <c r="O32" t="n">
+      <c r="R32" t="n">
         <v>6.014472809192214</v>
       </c>
-      <c r="P32" t="n">
+      <c r="S32" t="n">
         <v>5.304199993299895</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="T32" t="n">
         <v>5.81042220107183</v>
       </c>
-      <c r="R32" t="n">
+      <c r="U32" t="n">
         <v>5.4463924767182</v>
       </c>
-      <c r="S32" t="n">
+      <c r="V32" t="n">
+        <v>4.451086184845964</v>
+      </c>
+      <c r="W32" t="n">
         <v>5.816068932200594</v>
       </c>
-      <c r="T32" t="n">
+      <c r="X32" t="n">
         <v>5.00347634771884</v>
       </c>
-      <c r="U32" t="n">
-        <v>64308240000</v>
-      </c>
-      <c r="V32" t="n">
+      <c r="Y32" t="n">
+        <v>113092102000</v>
+      </c>
+      <c r="Z32" t="n">
         <v>174.1</v>
       </c>
     </row>
@@ -2784,63 +3176,75 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.1029332336200091</v>
+        <v>0.4140616913666763</v>
       </c>
       <c r="D33" t="n">
-        <v>2.92927404419365</v>
+        <v>0.3880973870115159</v>
       </c>
       <c r="E33" t="n">
-        <v>73.36747129779661</v>
+        <v>1.606541547754952</v>
       </c>
       <c r="F33" t="n">
-        <v>0.09053201842682081</v>
+        <v>41.05834481797643</v>
       </c>
       <c r="G33" t="n">
-        <v>9.620865894392008</v>
+        <v>3.374239239495323</v>
       </c>
       <c r="H33" t="n">
-        <v>6.915603750328915</v>
+        <v>47.32589933576539</v>
       </c>
       <c r="I33" t="n">
-        <v>6.527442567265576</v>
+        <v>3.792818488504274</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1.520435207382652</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4458771939764087</v>
+        <v>0.275023799605355</v>
       </c>
       <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.2445384851374252</v>
+      </c>
+      <c r="N33" t="n">
+        <v>5.297366902793402</v>
+      </c>
+      <c r="O33" t="n">
         <v>4.741796778195845</v>
       </c>
-      <c r="M33" t="n">
+      <c r="P33" t="n">
         <v>5.459883373287034</v>
       </c>
-      <c r="N33" t="n">
+      <c r="Q33" t="n">
         <v>5.614222353441073</v>
       </c>
-      <c r="O33" t="n">
+      <c r="R33" t="n">
         <v>6.063668951248651</v>
       </c>
-      <c r="P33" t="n">
+      <c r="S33" t="n">
         <v>5.26672348865743</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="T33" t="n">
         <v>5.89225176540645</v>
       </c>
-      <c r="R33" t="n">
+      <c r="U33" t="n">
         <v>5.49302031283694</v>
       </c>
-      <c r="S33" t="n">
+      <c r="V33" t="n">
+        <v>4.545207848055754</v>
+      </c>
+      <c r="W33" t="n">
         <v>5.915420062734056</v>
       </c>
-      <c r="T33" t="n">
+      <c r="X33" t="n">
         <v>5.062531774653818</v>
       </c>
-      <c r="U33" t="n">
-        <v>63542160000</v>
-      </c>
-      <c r="V33" t="n">
+      <c r="Y33" t="n">
+        <v>115859064000</v>
+      </c>
+      <c r="Z33" t="n">
         <v>178.1</v>
       </c>
     </row>
@@ -2856,63 +3260,75 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.09280288436878099</v>
+        <v>0.5751683903682133</v>
       </c>
       <c r="D34" t="n">
-        <v>3.235999035849403</v>
+        <v>0.4798105801620611</v>
       </c>
       <c r="E34" t="n">
-        <v>71.56567268791648</v>
+        <v>1.968148292487554</v>
       </c>
       <c r="F34" t="n">
-        <v>0.09119854913864139</v>
+        <v>44.37699809411995</v>
       </c>
       <c r="G34" t="n">
-        <v>10.92532600689064</v>
+        <v>3.489196659040856</v>
       </c>
       <c r="H34" t="n">
-        <v>6.130277895717758</v>
+        <v>42.79941238228135</v>
       </c>
       <c r="I34" t="n">
-        <v>7.553926888087094</v>
+        <v>3.728460929458878</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1.917286867097383</v>
       </c>
       <c r="K34" t="n">
-        <v>0.4047960520312062</v>
+        <v>0.4193191350259328</v>
       </c>
       <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.2461986699578232</v>
+      </c>
+      <c r="N34" t="n">
+        <v>5.321154576587962</v>
+      </c>
+      <c r="O34" t="n">
         <v>4.68351916650798</v>
       </c>
-      <c r="M34" t="n">
+      <c r="P34" t="n">
         <v>5.555630443069917</v>
       </c>
-      <c r="N34" t="n">
+      <c r="Q34" t="n">
         <v>5.663411784126078</v>
       </c>
-      <c r="O34" t="n">
+      <c r="R34" t="n">
         <v>6.064505873501199</v>
       </c>
-      <c r="P34" t="n">
+      <c r="S34" t="n">
         <v>5.369474560864365</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="T34" t="n">
         <v>5.920720122929389</v>
       </c>
-      <c r="R34" t="n">
+      <c r="U34" t="n">
         <v>5.610387127056648</v>
       </c>
-      <c r="S34" t="n">
+      <c r="V34" t="n">
+        <v>4.635214336950808</v>
+      </c>
+      <c r="W34" t="n">
         <v>5.931953406551048</v>
       </c>
-      <c r="T34" t="n">
+      <c r="X34" t="n">
         <v>5.0152910853819</v>
       </c>
-      <c r="U34" t="n">
-        <v>30978563000</v>
-      </c>
-      <c r="V34" t="n">
+      <c r="Y34" t="n">
+        <v>50934475000</v>
+      </c>
+      <c r="Z34" t="n">
         <v>183.3</v>
       </c>
     </row>
@@ -2928,63 +3344,75 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0807313605043669</v>
+        <v>0.4440749418453295</v>
       </c>
       <c r="D35" t="n">
-        <v>3.03307487051326</v>
+        <v>0.4749787955894826</v>
       </c>
       <c r="E35" t="n">
-        <v>69.75224012809763</v>
+        <v>1.894969101529452</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0829647075675</v>
+        <v>44.44500214358879</v>
       </c>
       <c r="G35" t="n">
-        <v>9.731475514847672</v>
+        <v>3.128851542425724</v>
       </c>
       <c r="H35" t="n">
-        <v>9.449174242325808</v>
+        <v>40.65391624306294</v>
       </c>
       <c r="I35" t="n">
-        <v>6.739314321782644</v>
+        <v>5.903544748681171</v>
       </c>
       <c r="J35" t="n">
-        <v>0.6924203061291556</v>
+        <v>1.961132891523641</v>
       </c>
       <c r="K35" t="n">
-        <v>0.4386045482319732</v>
+        <v>0.3869010897958068</v>
       </c>
       <c r="L35" t="n">
+        <v>0.4326022737329517</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.2740262282247015</v>
+      </c>
+      <c r="N35" t="n">
+        <v>5.150165364454174</v>
+      </c>
+      <c r="O35" t="n">
         <v>4.625364902245851</v>
       </c>
-      <c r="M35" t="n">
+      <c r="P35" t="n">
         <v>5.43681767302072</v>
       </c>
-      <c r="N35" t="n">
+      <c r="Q35" t="n">
         <v>5.570784328967161</v>
       </c>
-      <c r="O35" t="n">
+      <c r="R35" t="n">
         <v>5.922543062407476</v>
       </c>
-      <c r="P35" t="n">
+      <c r="S35" t="n">
         <v>5.223809311085152</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="T35" t="n">
         <v>5.789593146006942</v>
       </c>
-      <c r="R35" t="n">
+      <c r="U35" t="n">
         <v>5.473488391137955</v>
       </c>
-      <c r="S35" t="n">
+      <c r="V35" t="n">
+        <v>4.58812572654508</v>
+      </c>
+      <c r="W35" t="n">
         <v>5.798880488548207</v>
       </c>
-      <c r="T35" t="n">
+      <c r="X35" t="n">
         <v>4.965916846317278</v>
       </c>
-      <c r="U35" t="n">
-        <v>29014747000</v>
-      </c>
-      <c r="V35" t="n">
+      <c r="Y35" t="n">
+        <v>46440810000</v>
+      </c>
+      <c r="Z35" t="n">
         <v>183.5</v>
       </c>
     </row>
@@ -3000,63 +3428,75 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0684477907665882</v>
+        <v>0.4636869406650926</v>
       </c>
       <c r="D36" t="n">
-        <v>1.404876191926795</v>
+        <v>0.0503712994047015</v>
       </c>
       <c r="E36" t="n">
-        <v>71.82768948071015</v>
+        <v>0.8995030801919858</v>
       </c>
       <c r="F36" t="n">
-        <v>0.083820644211323</v>
+        <v>46.93987766787762</v>
       </c>
       <c r="G36" t="n">
-        <v>9.39209626931078</v>
+        <v>3.496110411944443</v>
       </c>
       <c r="H36" t="n">
-        <v>9.570633630426055</v>
+        <v>40.73856984675013</v>
       </c>
       <c r="I36" t="n">
-        <v>6.975519084657853</v>
+        <v>6.127810037231971</v>
       </c>
       <c r="J36" t="n">
-        <v>0.676916907990449</v>
+        <v>0.8506596813742473</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
+        <v>0.433411034559814</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>5.309306794550086</v>
+      </c>
+      <c r="O36" t="n">
         <v>4.800243434239934</v>
       </c>
-      <c r="M36" t="n">
+      <c r="P36" t="n">
         <v>5.574167208861058</v>
       </c>
-      <c r="N36" t="n">
+      <c r="Q36" t="n">
         <v>5.663897502846042</v>
       </c>
-      <c r="O36" t="n">
+      <c r="R36" t="n">
         <v>6.03851507759579</v>
       </c>
-      <c r="P36" t="n">
+      <c r="S36" t="n">
         <v>5.263622358837189</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="T36" t="n">
         <v>5.868590448957447</v>
       </c>
-      <c r="R36" t="n">
+      <c r="U36" t="n">
         <v>5.601454420599278</v>
       </c>
-      <c r="S36" t="n">
+      <c r="V36" t="n">
+        <v>4.714472948236298</v>
+      </c>
+      <c r="W36" t="n">
         <v>5.907702391181965</v>
       </c>
-      <c r="T36" t="n">
+      <c r="X36" t="n">
         <v>5.071228512233326</v>
       </c>
-      <c r="U36" t="n">
-        <v>62187544000</v>
-      </c>
-      <c r="V36" t="n">
+      <c r="Y36" t="n">
+        <v>97126738000</v>
+      </c>
+      <c r="Z36" t="n">
         <v>184.9</v>
       </c>
     </row>
@@ -3072,63 +3512,75 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0802930347198884</v>
+        <v>0.5466570170660299</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>0.0499615879862662</v>
       </c>
       <c r="E37" t="n">
-        <v>74.21539624750227</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0943030379600456</v>
+        <v>46.7751726067272</v>
       </c>
       <c r="G37" t="n">
-        <v>10.10826625965294</v>
+        <v>3.830276794617482</v>
       </c>
       <c r="H37" t="n">
-        <v>8.642490309569398</v>
+        <v>42.86888798880236</v>
       </c>
       <c r="I37" t="n">
-        <v>6.859251110595461</v>
+        <v>5.377708558760583</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>0.5513354460400676</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>5.479012604144678</v>
+      </c>
+      <c r="O37" t="n">
         <v>4.857794909293135</v>
       </c>
-      <c r="M37" t="n">
+      <c r="P37" t="n">
         <v>5.688804220388399</v>
       </c>
-      <c r="N37" t="n">
+      <c r="Q37" t="n">
         <v>5.715645122967424</v>
       </c>
-      <c r="O37" t="n">
+      <c r="R37" t="n">
         <v>6.228017785332109</v>
       </c>
-      <c r="P37" t="n">
+      <c r="S37" t="n">
         <v>5.369567707969396</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="T37" t="n">
         <v>5.899294428789442</v>
       </c>
-      <c r="R37" t="n">
+      <c r="U37" t="n">
         <v>5.707508840181511</v>
       </c>
-      <c r="S37" t="n">
+      <c r="V37" t="n">
+        <v>4.792313448246652</v>
+      </c>
+      <c r="W37" t="n">
         <v>6.002775308079503</v>
       </c>
-      <c r="T37" t="n">
+      <c r="X37" t="n">
         <v>5.071040260969231</v>
       </c>
-      <c r="U37" t="n">
-        <v>32705203000</v>
-      </c>
-      <c r="V37" t="n">
+      <c r="Y37" t="n">
+        <v>52560379000</v>
+      </c>
+      <c r="Z37" t="n">
         <v>189.7</v>
       </c>
     </row>
@@ -3144,63 +3596,75 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0807878214736675</v>
+        <v>0.5234289205212246</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>0.0487758026231863</v>
       </c>
       <c r="E38" t="n">
-        <v>73.41194580107707</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1081661874741384</v>
+        <v>44.90731318480209</v>
       </c>
       <c r="G38" t="n">
-        <v>10.84678920685191</v>
+        <v>4.342310732301578</v>
       </c>
       <c r="H38" t="n">
-        <v>8.311193444676695</v>
+        <v>43.23928894581935</v>
       </c>
       <c r="I38" t="n">
-        <v>7.241117538446533</v>
+        <v>5.017899030150288</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>0.5651967901384838</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
+        <v>1.355786593643808</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>5.518897637906754</v>
+      </c>
+      <c r="O38" t="n">
         <v>4.892227063045954</v>
       </c>
-      <c r="M38" t="n">
+      <c r="P38" t="n">
         <v>5.731397621898267</v>
       </c>
-      <c r="N38" t="n">
+      <c r="Q38" t="n">
         <v>5.732855741903979</v>
       </c>
-      <c r="O38" t="n">
+      <c r="R38" t="n">
         <v>6.378952356842662</v>
       </c>
-      <c r="P38" t="n">
+      <c r="S38" t="n">
         <v>5.396849653031689</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="T38" t="n">
         <v>5.948034989180646</v>
       </c>
-      <c r="R38" t="n">
+      <c r="U38" t="n">
         <v>5.786283658700077</v>
       </c>
-      <c r="S38" t="n">
+      <c r="V38" t="n">
+        <v>4.876951476351151</v>
+      </c>
+      <c r="W38" t="n">
         <v>6.034595884760305</v>
       </c>
-      <c r="T38" t="n">
+      <c r="X38" t="n">
         <v>5.087102374790709</v>
       </c>
-      <c r="U38" t="n">
-        <v>32806925000</v>
-      </c>
-      <c r="V38" t="n">
+      <c r="Y38" t="n">
+        <v>54338419000</v>
+      </c>
+      <c r="Z38" t="n">
         <v>199.2</v>
       </c>
     </row>
@@ -3216,63 +3680,75 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0785990867177226</v>
+        <v>0.4323724397543229</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>0.0440116871869686</v>
       </c>
       <c r="E39" t="n">
-        <v>77.87776346992638</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1082661416802787</v>
+        <v>44.22952914347252</v>
       </c>
       <c r="G39" t="n">
-        <v>11.58105500854229</v>
+        <v>3.925160775117162</v>
       </c>
       <c r="H39" t="n">
-        <v>9.662215378340267</v>
+        <v>37.78855824706607</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6921009147930703</v>
+        <v>5.410373307413299</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.6395611660370216</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
+        <v>7.530433233952635</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>5.505046912812269</v>
+      </c>
+      <c r="O39" t="n">
         <v>4.900373872578711</v>
       </c>
-      <c r="M39" t="n">
+      <c r="P39" t="n">
         <v>5.76170545706936</v>
       </c>
-      <c r="N39" t="n">
+      <c r="Q39" t="n">
         <v>5.776599148587745</v>
       </c>
-      <c r="O39" t="n">
+      <c r="R39" t="n">
         <v>6.326972072067101</v>
       </c>
-      <c r="P39" t="n">
+      <c r="S39" t="n">
         <v>5.332090553051668</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="T39" t="n">
         <v>6.018422865865544</v>
       </c>
-      <c r="R39" t="n">
+      <c r="U39" t="n">
         <v>5.774116622878518</v>
       </c>
-      <c r="S39" t="n">
+      <c r="V39" t="n">
+        <v>4.898287442718516</v>
+      </c>
+      <c r="W39" t="n">
         <v>6.018374221327033</v>
       </c>
-      <c r="T39" t="n">
+      <c r="X39" t="n">
         <v>5.135974884890055</v>
       </c>
-      <c r="U39" t="n">
-        <v>31705203000</v>
-      </c>
-      <c r="V39" t="n">
+      <c r="Y39" t="n">
+        <v>56621324000</v>
+      </c>
+      <c r="Z39" t="n">
         <v>203.9</v>
       </c>
     </row>
@@ -3288,63 +3764,75 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0539242894392088</v>
+        <v>0.1944379930376252</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>0.3320385467025857</v>
       </c>
       <c r="E40" t="n">
-        <v>78.48202670006695</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.09961231349313571</v>
+        <v>41.44845135662199</v>
       </c>
       <c r="G40" t="n">
-        <v>10.96610450009641</v>
+        <v>3.170187465058327</v>
       </c>
       <c r="H40" t="n">
-        <v>9.009479346418363</v>
+        <v>31.97778652205708</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7412443751640018</v>
+        <v>4.689005825761383</v>
       </c>
       <c r="J40" t="n">
-        <v>0.6476084753219313</v>
+        <v>0.8796586274277927</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
+        <v>17.30843366333323</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>5.217920446012219</v>
+      </c>
+      <c r="O40" t="n">
         <v>4.804103026095894</v>
       </c>
-      <c r="M40" t="n">
+      <c r="P40" t="n">
         <v>5.618696511156143</v>
       </c>
-      <c r="N40" t="n">
+      <c r="Q40" t="n">
         <v>5.725902647880344</v>
       </c>
-      <c r="O40" t="n">
+      <c r="R40" t="n">
         <v>6.093095636318211</v>
       </c>
-      <c r="P40" t="n">
+      <c r="S40" t="n">
         <v>5.069218637382565</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="T40" t="n">
         <v>5.90734900310645</v>
       </c>
-      <c r="R40" t="n">
+      <c r="U40" t="n">
         <v>5.531886364017144</v>
       </c>
-      <c r="S40" t="n">
+      <c r="V40" t="n">
+        <v>4.729597764363143</v>
+      </c>
+      <c r="W40" t="n">
         <v>5.9353967212938</v>
       </c>
-      <c r="T40" t="n">
+      <c r="X40" t="n">
         <v>5.14031764691795</v>
       </c>
-      <c r="U40" t="n">
-        <v>61508460000</v>
-      </c>
-      <c r="V40" t="n">
+      <c r="Y40" t="n">
+        <v>118182664000</v>
+      </c>
+      <c r="Z40" t="n">
         <v>203.7</v>
       </c>
     </row>
@@ -3360,63 +3848,75 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0713149602676638</v>
+        <v>0.2622053496615281</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1.551223555679775</v>
       </c>
       <c r="E41" t="n">
-        <v>78.2683635256422</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>39.14743874549828</v>
       </c>
       <c r="G41" t="n">
-        <v>11.94393020249409</v>
+        <v>3.205644937890908</v>
       </c>
       <c r="H41" t="n">
-        <v>8.011278105265074</v>
+        <v>32.68725510697121</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8507129641660026</v>
+        <v>3.951129698521065</v>
       </c>
       <c r="J41" t="n">
-        <v>0.854400242164971</v>
+        <v>1.009934954394972</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
+        <v>18.18516765138227</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>5.355217445393413</v>
+      </c>
+      <c r="O41" t="n">
         <v>4.866148932023583</v>
       </c>
-      <c r="M41" t="n">
+      <c r="P41" t="n">
         <v>5.748468965040323</v>
       </c>
-      <c r="N41" t="n">
+      <c r="Q41" t="n">
         <v>5.815741199808434</v>
       </c>
-      <c r="O41" t="n">
-        <v>6.282565717423287</v>
-      </c>
-      <c r="P41" t="n">
+      <c r="R41" t="n">
+        <v>6.255385287251187</v>
+      </c>
+      <c r="S41" t="n">
         <v>5.16609937233831</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="T41" t="n">
         <v>5.997968315062957</v>
       </c>
-      <c r="R41" t="n">
+      <c r="U41" t="n">
         <v>5.678362101483062</v>
       </c>
-      <c r="S41" t="n">
+      <c r="V41" t="n">
+        <v>4.861748513388538</v>
+      </c>
+      <c r="W41" t="n">
         <v>6.015986395547721</v>
       </c>
-      <c r="T41" t="n">
+      <c r="X41" t="n">
         <v>5.186715217263315</v>
       </c>
-      <c r="U41" t="n">
-        <v>32625693000</v>
-      </c>
-      <c r="V41" t="n">
+      <c r="Y41" t="n">
+        <v>66151587000</v>
+      </c>
+      <c r="Z41" t="n">
         <v>199.8</v>
       </c>
     </row>
@@ -3432,63 +3932,75 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.08261306883840031</v>
+        <v>0.3899505472397555</v>
       </c>
       <c r="D42" t="n">
-        <v>0.7358492953102646</v>
+        <v>1.9967339938535</v>
       </c>
       <c r="E42" t="n">
-        <v>75.62998525346536</v>
+        <v>0.3406267338016949</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>35.5318542501631</v>
       </c>
       <c r="G42" t="n">
-        <v>13.50030141133026</v>
+        <v>2.937441450215198</v>
       </c>
       <c r="H42" t="n">
-        <v>8.602783988986531</v>
+        <v>35.77667523315236</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8237811344937146</v>
+        <v>3.98225320109119</v>
       </c>
       <c r="J42" t="n">
-        <v>0.6246858475754598</v>
+        <v>0.9123471268214682</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
+        <v>18.13211746366174</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>5.457157004618757</v>
+      </c>
+      <c r="O42" t="n">
         <v>4.873057640449997</v>
       </c>
-      <c r="M42" t="n">
+      <c r="P42" t="n">
         <v>5.878911598437154</v>
       </c>
-      <c r="N42" t="n">
+      <c r="Q42" t="n">
         <v>5.86329022226083</v>
       </c>
-      <c r="O42" t="n">
-        <v>6.275740863170959</v>
-      </c>
-      <c r="P42" t="n">
+      <c r="R42" t="n">
+        <v>6.288917492462712</v>
+      </c>
+      <c r="S42" t="n">
         <v>5.360305732330494</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="T42" t="n">
         <v>6.077389951545485</v>
       </c>
-      <c r="R42" t="n">
+      <c r="U42" t="n">
         <v>5.781052128979701</v>
       </c>
-      <c r="S42" t="n">
+      <c r="V42" t="n">
+        <v>4.944566740208093</v>
+      </c>
+      <c r="W42" t="n">
         <v>6.210499694892221</v>
       </c>
-      <c r="T42" t="n">
+      <c r="X42" t="n">
         <v>5.185316654795577</v>
       </c>
-      <c r="U42" t="n">
-        <v>34857681000</v>
-      </c>
-      <c r="V42" t="n">
+      <c r="Y42" t="n">
+        <v>75302369000</v>
+      </c>
+      <c r="Z42" t="n">
         <v>204.2</v>
       </c>
     </row>
@@ -3504,63 +4016,75 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.1471842894407703</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>4.724676552878352</v>
       </c>
       <c r="E43" t="n">
-        <v>90.82673944769202</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>54.26448154460626</v>
       </c>
       <c r="G43" t="n">
-        <v>2.359249209689726</v>
+        <v>5.393518596686155</v>
       </c>
       <c r="H43" t="n">
-        <v>6.666827053177488</v>
+        <v>30.88022599296955</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>3.88207091882831</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>0.8550263940313751</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>5.416233721225031</v>
+      </c>
+      <c r="O43" t="n">
         <v>4.991384510356018</v>
       </c>
-      <c r="M43" t="n">
+      <c r="P43" t="n">
         <v>5.848661704292398</v>
       </c>
-      <c r="N43" t="n">
+      <c r="Q43" t="n">
         <v>5.879415060367355</v>
       </c>
-      <c r="O43" t="n">
-        <v>6.242301040693907</v>
-      </c>
-      <c r="P43" t="n">
+      <c r="R43" t="n">
+        <v>6.215627598087005</v>
+      </c>
+      <c r="S43" t="n">
         <v>5.279185548449772</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="T43" t="n">
         <v>6.084544945099329</v>
       </c>
-      <c r="R43" t="n">
-        <v>5.737700712526218</v>
-      </c>
-      <c r="S43" t="n">
+      <c r="U43" t="n">
+        <v>5.733341276897746</v>
+      </c>
+      <c r="V43" t="n">
+        <v>5.002603142908116</v>
+      </c>
+      <c r="W43" t="n">
         <v>6.14714264173486</v>
       </c>
-      <c r="T43" t="n">
+      <c r="X43" t="n">
         <v>5.239628402561581</v>
       </c>
-      <c r="U43" t="n">
-        <v>17416261000</v>
-      </c>
-      <c r="V43" t="n">
+      <c r="Y43" t="n">
+        <v>29909603000</v>
+      </c>
+      <c r="Z43" t="n">
         <v>199.8</v>
       </c>
     </row>
@@ -3576,63 +4100,75 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.1813617390200524</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>5.400335433430566</v>
       </c>
       <c r="E44" t="n">
-        <v>89.08091244171827</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>53.31388948160593</v>
       </c>
       <c r="G44" t="n">
-        <v>2.607601222825169</v>
+        <v>4.712373724795776</v>
       </c>
       <c r="H44" t="n">
-        <v>6.203547301512408</v>
+        <v>30.96717276844086</v>
       </c>
       <c r="I44" t="n">
-        <v>1.926577294924108</v>
+        <v>3.60949301068756</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1.996735581039313</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>5.456218177466323</v>
+      </c>
+      <c r="O44" t="n">
         <v>5.054524552405969</v>
       </c>
-      <c r="M44" t="n">
+      <c r="P44" t="n">
         <v>5.926579286175616</v>
       </c>
-      <c r="N44" t="n">
+      <c r="Q44" t="n">
         <v>5.920237037819614</v>
       </c>
-      <c r="O44" t="n">
-        <v>6.31579188610481</v>
-      </c>
-      <c r="P44" t="n">
+      <c r="R44" t="n">
+        <v>6.317489530506517</v>
+      </c>
+      <c r="S44" t="n">
         <v>5.352095086688388</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="T44" t="n">
         <v>6.14857510173714</v>
       </c>
-      <c r="R44" t="n">
+      <c r="U44" t="n">
         <v>5.771628013947063</v>
       </c>
-      <c r="S44" t="n">
+      <c r="V44" t="n">
+        <v>4.996536328448899</v>
+      </c>
+      <c r="W44" t="n">
         <v>6.206656585860848</v>
       </c>
-      <c r="T44" t="n">
+      <c r="X44" t="n">
         <v>5.231910401737476</v>
       </c>
-      <c r="U44" t="n">
-        <v>17031707000</v>
-      </c>
-      <c r="V44" t="n">
+      <c r="Y44" t="n">
+        <v>29271978000</v>
+      </c>
+      <c r="Z44" t="n">
         <v>204.4</v>
       </c>
     </row>
@@ -3648,63 +4184,75 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.1856328622405392</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>5.88096115763537</v>
       </c>
       <c r="E45" t="n">
-        <v>85.88081496036689</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>51.04467670531716</v>
       </c>
       <c r="G45" t="n">
-        <v>2.988604978102169</v>
+        <v>4.731878004344839</v>
       </c>
       <c r="H45" t="n">
-        <v>8.908416935838858</v>
+        <v>31.18351052584901</v>
       </c>
       <c r="I45" t="n">
-        <v>2.036530263451542</v>
+        <v>5.087510036609737</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>2.071463570243888</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>5.465102197107623</v>
+      </c>
+      <c r="O45" t="n">
         <v>4.974731786145223</v>
       </c>
-      <c r="M45" t="n">
+      <c r="P45" t="n">
         <v>5.921980467220662</v>
       </c>
-      <c r="N45" t="n">
+      <c r="Q45" t="n">
         <v>5.880421224443493</v>
       </c>
-      <c r="O45" t="n">
+      <c r="R45" t="n">
         <v>6.26862268672843</v>
       </c>
-      <c r="P45" t="n">
+      <c r="S45" t="n">
         <v>5.391853248718454</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="T45" t="n">
         <v>6.130030148515686</v>
       </c>
-      <c r="R45" t="n">
+      <c r="U45" t="n">
         <v>5.786928085697856</v>
       </c>
-      <c r="S45" t="n">
+      <c r="V45" t="n">
+        <v>5.012566716273255</v>
+      </c>
+      <c r="W45" t="n">
         <v>6.132790485847972</v>
       </c>
-      <c r="T45" t="n">
+      <c r="X45" t="n">
         <v>5.17076806293567</v>
       </c>
-      <c r="U45" t="n">
-        <v>16883864000</v>
-      </c>
-      <c r="V45" t="n">
+      <c r="Y45" t="n">
+        <v>29564266000</v>
+      </c>
+      <c r="Z45" t="n">
         <v>201.5</v>
       </c>
     </row>
@@ -3720,63 +4268,75 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>1.256273558528777</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>2.510986818366655</v>
       </c>
       <c r="E46" t="n">
-        <v>85.93305254219676</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>51.70684710350285</v>
       </c>
       <c r="G46" t="n">
-        <v>2.816124304582948</v>
+        <v>4.50636329901474</v>
       </c>
       <c r="H46" t="n">
-        <v>9.433489963533702</v>
+        <v>33.43690256217518</v>
       </c>
       <c r="I46" t="n">
-        <v>1.817333189686589</v>
+        <v>5.51934215569313</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1.063284502718665</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>5.080720897869348</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>5.501829473423211</v>
+      </c>
+      <c r="O46" t="n">
+        <v>5.070475294452272</v>
+      </c>
+      <c r="P46" t="n">
         <v>6.035505379045752</v>
       </c>
-      <c r="N46" t="n">
+      <c r="Q46" t="n">
         <v>6.017132278984445</v>
       </c>
-      <c r="O46" t="n">
-        <v>6.34586441356437</v>
-      </c>
-      <c r="P46" t="n">
+      <c r="R46" t="n">
+        <v>6.369695490625076</v>
+      </c>
+      <c r="S46" t="n">
         <v>5.4981103867604</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="T46" t="n">
         <v>6.2813317304651</v>
       </c>
-      <c r="R46" t="n">
+      <c r="U46" t="n">
         <v>5.880281568379149</v>
       </c>
-      <c r="S46" t="n">
+      <c r="V46" t="n">
+        <v>5.087164097854608</v>
+      </c>
+      <c r="W46" t="n">
         <v>6.164093437909409</v>
       </c>
-      <c r="T46" t="n">
+      <c r="X46" t="n">
         <v>5.297717210904723</v>
       </c>
-      <c r="U46" t="n">
-        <v>18823956000</v>
-      </c>
-      <c r="V46" t="n">
+      <c r="Y46" t="n">
+        <v>32173327000</v>
+      </c>
+      <c r="Z46" t="n">
         <v>204</v>
       </c>
     </row>
@@ -3792,63 +4352,75 @@
         </is>
       </c>
       <c r="C47" t="n">
+        <v>0.4460248190427928</v>
+      </c>
+      <c r="D47" t="n">
         <v>4.224125271288404</v>
       </c>
-      <c r="D47" t="n">
+      <c r="E47" t="n">
         <v>1.510196508618797</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>28.47112589259778</v>
       </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
         <v>4.164689796598052</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>41.80317104689769</v>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>2.082054790728499</v>
       </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
         <v>1.990960154434824</v>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
         <v>15.30765171979316</v>
       </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>5.494911570093249</v>
+      </c>
+      <c r="O47" t="n">
         <v>5.060757946070432</v>
       </c>
-      <c r="M47" t="n">
+      <c r="P47" t="n">
         <v>6.109758587704272</v>
       </c>
-      <c r="N47" t="n">
+      <c r="Q47" t="n">
         <v>6.022939009768135</v>
       </c>
-      <c r="O47" t="n">
+      <c r="R47" t="n">
         <v>6.366058008335406</v>
       </c>
-      <c r="P47" t="n">
+      <c r="S47" t="n">
         <v>5.57340794749295</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="T47" t="n">
         <v>6.316442360202912</v>
       </c>
-      <c r="R47" t="n">
+      <c r="U47" t="n">
         <v>5.922221618201355</v>
       </c>
-      <c r="S47" t="n">
+      <c r="V47" t="n">
+        <v>5.042908842827195</v>
+      </c>
+      <c r="W47" t="n">
         <v>6.202009043066795</v>
       </c>
-      <c r="T47" t="n">
+      <c r="X47" t="n">
         <v>5.239151026738912</v>
       </c>
-      <c r="U47" t="n">
+      <c r="Y47" t="n">
         <v>88226928906</v>
       </c>
-      <c r="V47" t="n">
+      <c r="Z47" t="n">
         <v>204.3</v>
       </c>
     </row>
@@ -3864,63 +4436,75 @@
         </is>
       </c>
       <c r="C48" t="n">
+        <v>0.5351456839946656</v>
+      </c>
+      <c r="D48" t="n">
         <v>4.272260690243093</v>
       </c>
-      <c r="D48" t="n">
+      <c r="E48" t="n">
         <v>1.578051475604808</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>26.72703492276832</v>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>7.297933102440755</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>41.08104730016264</v>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>1.993601740498209</v>
       </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
         <v>2.067374659877975</v>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
         <v>14.44755042440953</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>5.579767597973324</v>
+      </c>
+      <c r="O48" t="n">
         <v>5.005957724985585</v>
       </c>
-      <c r="M48" t="n">
+      <c r="P48" t="n">
         <v>6.174410883255348</v>
       </c>
-      <c r="N48" t="n">
+      <c r="Q48" t="n">
         <v>6.016742330487587</v>
       </c>
-      <c r="O48" t="n">
+      <c r="R48" t="n">
         <v>6.404997002076008</v>
       </c>
-      <c r="P48" t="n">
+      <c r="S48" t="n">
         <v>5.592366607183647</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="T48" t="n">
         <v>6.373353952016081</v>
       </c>
-      <c r="R48" t="n">
+      <c r="U48" t="n">
         <v>5.993213048106364</v>
       </c>
-      <c r="S48" t="n">
+      <c r="V48" t="n">
+        <v>5.01156818807964</v>
+      </c>
+      <c r="W48" t="n">
         <v>6.25240473992357</v>
       </c>
-      <c r="T48" t="n">
+      <c r="X48" t="n">
         <v>5.246181592837003</v>
       </c>
-      <c r="U48" t="n">
+      <c r="Y48" t="n">
         <v>91175733000</v>
       </c>
-      <c r="V48" t="n">
+      <c r="Z48" t="n">
         <v>203.9</v>
       </c>
     </row>
@@ -3936,63 +4520,75 @@
         </is>
       </c>
       <c r="C49" t="n">
+        <v>0.950532799906416</v>
+      </c>
+      <c r="D49" t="n">
         <v>4.283301327289504</v>
       </c>
-      <c r="D49" t="n">
+      <c r="E49" t="n">
         <v>1.569335619730281</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>25.35086501754401</v>
       </c>
-      <c r="F49" t="n">
+      <c r="G49" t="n">
         <v>7.436295106171631</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>42.89063941508515</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>2.246786934591718</v>
       </c>
-      <c r="I49" t="n">
+      <c r="J49" t="n">
         <v>2.377234358147827</v>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
         <v>12.89500942153346</v>
       </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>5.675520215166035</v>
+      </c>
+      <c r="O49" t="n">
         <v>5.046774368184228</v>
       </c>
-      <c r="M49" t="n">
+      <c r="P49" t="n">
         <v>6.27306562193818</v>
       </c>
-      <c r="N49" t="n">
+      <c r="Q49" t="n">
         <v>6.092711603092653</v>
       </c>
-      <c r="O49" t="n">
+      <c r="R49" t="n">
         <v>6.479538272603098</v>
       </c>
-      <c r="P49" t="n">
+      <c r="S49" t="n">
         <v>5.685991792986634</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="T49" t="n">
         <v>6.46505546525856</v>
       </c>
-      <c r="R49" t="n">
+      <c r="U49" t="n">
         <v>6.114699342557135</v>
       </c>
-      <c r="S49" t="n">
+      <c r="V49" t="n">
+        <v>5.003610658670819</v>
+      </c>
+      <c r="W49" t="n">
         <v>6.372431990256366</v>
       </c>
-      <c r="T49" t="n">
+      <c r="X49" t="n">
         <v>5.263777715022358</v>
       </c>
-      <c r="U49" t="n">
+      <c r="Y49" t="n">
         <v>104171471000</v>
       </c>
-      <c r="V49" t="n">
+      <c r="Z49" t="n">
         <v>202</v>
       </c>
     </row>
@@ -4008,63 +4604,75 @@
         </is>
       </c>
       <c r="C50" t="n">
+        <v>1.086065336323432</v>
+      </c>
+      <c r="D50" t="n">
         <v>4.998200715858795</v>
       </c>
-      <c r="D50" t="n">
+      <c r="E50" t="n">
         <v>0.9823617639761986</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>24.62726810597094</v>
       </c>
-      <c r="F50" t="n">
+      <c r="G50" t="n">
         <v>5.935619857239604</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>44.38307785870555</v>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>2.494764114543572</v>
       </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
         <v>2.375797117693884</v>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
         <v>13.11684512968802</v>
       </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>5.698267314425659</v>
+      </c>
+      <c r="O50" t="n">
         <v>5.039481864700525</v>
       </c>
-      <c r="M50" t="n">
+      <c r="P50" t="n">
         <v>6.240977324907824</v>
       </c>
-      <c r="N50" t="n">
+      <c r="Q50" t="n">
         <v>6.091128900605915</v>
       </c>
-      <c r="O50" t="n">
+      <c r="R50" t="n">
         <v>6.481424015585851</v>
       </c>
-      <c r="P50" t="n">
+      <c r="S50" t="n">
         <v>5.70730957232299</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="T50" t="n">
         <v>6.517686058276568</v>
       </c>
-      <c r="R50" t="n">
+      <c r="U50" t="n">
         <v>6.110779747159483</v>
       </c>
-      <c r="S50" t="n">
+      <c r="V50" t="n">
+        <v>5.070538052337498</v>
+      </c>
+      <c r="W50" t="n">
         <v>6.390844486997119</v>
       </c>
-      <c r="T50" t="n">
+      <c r="X50" t="n">
         <v>5.350150512290448</v>
       </c>
-      <c r="U50" t="n">
+      <c r="Y50" t="n">
         <v>105114026000</v>
       </c>
-      <c r="V50" t="n">
+      <c r="Z50" t="n">
         <v>207</v>
       </c>
     </row>
@@ -4080,63 +4688,75 @@
         </is>
       </c>
       <c r="C51" t="n">
+        <v>1.101639618554197</v>
+      </c>
+      <c r="D51" t="n">
         <v>4.822425599828168</v>
       </c>
-      <c r="D51" t="n">
+      <c r="E51" t="n">
         <v>1.121626289544559</v>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>24.48319198310253</v>
       </c>
-      <c r="F51" t="n">
+      <c r="G51" t="n">
         <v>5.044398580305137</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>46.03435058145229</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>2.58268943738468</v>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
         <v>2.290601865129513</v>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
         <v>12.51907604469893</v>
       </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>5.747607961985301</v>
+      </c>
+      <c r="O51" t="n">
         <v>5.064176061024286</v>
       </c>
-      <c r="M51" t="n">
+      <c r="P51" t="n">
         <v>6.27180094227923</v>
       </c>
-      <c r="N51" t="n">
+      <c r="Q51" t="n">
         <v>6.129768876751807</v>
       </c>
-      <c r="O51" t="n">
+      <c r="R51" t="n">
         <v>6.589792683950394</v>
       </c>
-      <c r="P51" t="n">
+      <c r="S51" t="n">
         <v>5.725576533916398</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="T51" t="n">
         <v>6.55751674758687</v>
       </c>
-      <c r="R51" t="n">
+      <c r="U51" t="n">
         <v>6.143348342389071</v>
       </c>
-      <c r="S51" t="n">
+      <c r="V51" t="n">
+        <v>5.134562339785737</v>
+      </c>
+      <c r="W51" t="n">
         <v>6.449617012236727</v>
       </c>
-      <c r="T51" t="n">
+      <c r="X51" t="n">
         <v>5.415789210125993</v>
       </c>
-      <c r="U51" t="n">
+      <c r="Y51" t="n">
         <v>106671091000</v>
       </c>
-      <c r="V51" t="n">
+      <c r="Z51" t="n">
         <v>208.3</v>
       </c>
     </row>
@@ -4152,63 +4772,75 @@
         </is>
       </c>
       <c r="C52" t="n">
+        <v>1.002984000547498</v>
+      </c>
+      <c r="D52" t="n">
         <v>5.666645472970113</v>
       </c>
-      <c r="D52" t="n">
+      <c r="E52" t="n">
         <v>1.195162278135553</v>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>25.02538843979609</v>
       </c>
-      <c r="F52" t="n">
+      <c r="G52" t="n">
         <v>4.578563224052674</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>44.92169156343604</v>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>2.636376812880628</v>
       </c>
-      <c r="I52" t="n">
+      <c r="J52" t="n">
         <v>1.788073950175883</v>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
         <v>13.18511425800552</v>
       </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>5.744828467524453</v>
+      </c>
+      <c r="O52" t="n">
         <v>5.082211522889036</v>
       </c>
-      <c r="M52" t="n">
+      <c r="P52" t="n">
         <v>6.270799424232006</v>
       </c>
-      <c r="N52" t="n">
+      <c r="Q52" t="n">
         <v>6.14218794764075</v>
       </c>
-      <c r="O52" t="n">
+      <c r="R52" t="n">
         <v>6.493829461489981</v>
       </c>
-      <c r="P52" t="n">
+      <c r="S52" t="n">
         <v>5.743932270645387</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="T52" t="n">
         <v>6.606596160377571</v>
       </c>
-      <c r="R52" t="n">
+      <c r="U52" t="n">
         <v>6.127109297973546</v>
       </c>
-      <c r="S52" t="n">
+      <c r="V52" t="n">
+        <v>5.115115447984119</v>
+      </c>
+      <c r="W52" t="n">
         <v>6.492118589655634</v>
       </c>
-      <c r="T52" t="n">
+      <c r="X52" t="n">
         <v>5.365929310628246</v>
       </c>
-      <c r="U52" t="n">
+      <c r="Y52" t="n">
         <v>106897617451</v>
       </c>
-      <c r="V52" t="n">
+      <c r="Z52" t="n">
         <v>206.4</v>
       </c>
     </row>
@@ -4224,63 +4856,75 @@
         </is>
       </c>
       <c r="C53" t="n">
+        <v>1.006359826169871</v>
+      </c>
+      <c r="D53" t="n">
         <v>6.160060703170128</v>
       </c>
-      <c r="D53" t="n">
+      <c r="E53" t="n">
         <v>1.623149382659634</v>
       </c>
-      <c r="E53" t="n">
+      <c r="F53" t="n">
         <v>25.46449349720765</v>
       </c>
-      <c r="F53" t="n">
+      <c r="G53" t="n">
         <v>0.751754936661195</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>46.97908740906009</v>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>2.724235535652829</v>
       </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
         <v>3.2242101523233</v>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
         <v>12.0666485570953</v>
       </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>5.721229384261287</v>
+      </c>
+      <c r="O53" t="n">
         <v>5.027492431167646</v>
       </c>
-      <c r="M53" t="n">
+      <c r="P53" t="n">
         <v>6.350449321333605</v>
       </c>
-      <c r="N53" t="n">
+      <c r="Q53" t="n">
         <v>6.213767718546452</v>
       </c>
-      <c r="O53" t="n">
+      <c r="R53" t="n">
         <v>6.374326154788642</v>
       </c>
-      <c r="P53" t="n">
+      <c r="S53" t="n">
         <v>5.809103011487541</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="T53" t="n">
         <v>6.674523475316722</v>
       </c>
-      <c r="R53" t="n">
+      <c r="U53" t="n">
         <v>6.187175237280255</v>
       </c>
-      <c r="S53" t="n">
+      <c r="V53" t="n">
+        <v>5.23585668195698</v>
+      </c>
+      <c r="W53" t="n">
         <v>6.539513716313432</v>
       </c>
-      <c r="T53" t="n">
+      <c r="X53" t="n">
         <v>5.481222084060923</v>
       </c>
-      <c r="U53" t="n">
+      <c r="Y53" t="n">
         <v>108476707000</v>
       </c>
-      <c r="V53" t="n">
+      <c r="Z53" t="n">
         <v>197</v>
       </c>
     </row>
@@ -4296,63 +4940,75 @@
         </is>
       </c>
       <c r="C54" t="n">
+        <v>0.9797612225649448</v>
+      </c>
+      <c r="D54" t="n">
         <v>6.362580786240707</v>
       </c>
-      <c r="D54" t="n">
+      <c r="E54" t="n">
         <v>1.751504511263984</v>
       </c>
-      <c r="E54" t="n">
+      <c r="F54" t="n">
         <v>24.76287653779277</v>
       </c>
-      <c r="F54" t="n">
+      <c r="G54" t="n">
         <v>0.6476663938600147</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>46.08696010516255</v>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>2.980167501785199</v>
       </c>
-      <c r="I54" t="n">
+      <c r="J54" t="n">
         <v>3.595428089561207</v>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
         <v>12.83305485176863</v>
       </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>5.725250413132147</v>
+      </c>
+      <c r="O54" t="n">
         <v>5.029980252467408</v>
       </c>
-      <c r="M54" t="n">
+      <c r="P54" t="n">
         <v>6.393356588327912</v>
       </c>
-      <c r="N54" t="n">
+      <c r="Q54" t="n">
         <v>6.217264540099178</v>
       </c>
-      <c r="O54" t="n">
+      <c r="R54" t="n">
         <v>6.338169977270297</v>
       </c>
-      <c r="P54" t="n">
+      <c r="S54" t="n">
         <v>5.783671361906233</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="T54" t="n">
         <v>6.734270538821864</v>
       </c>
-      <c r="R54" t="n">
+      <c r="U54" t="n">
         <v>6.173077527216821</v>
       </c>
-      <c r="S54" t="n">
+      <c r="V54" t="n">
+        <v>5.263932968112846</v>
+      </c>
+      <c r="W54" t="n">
         <v>6.541203137327885</v>
       </c>
-      <c r="T54" t="n">
+      <c r="X54" t="n">
         <v>5.41911803423974</v>
       </c>
-      <c r="U54" t="n">
+      <c r="Y54" t="n">
         <v>106286509000</v>
       </c>
-      <c r="V54" t="n">
+      <c r="Z54" t="n">
         <v>191.5</v>
       </c>
     </row>
@@ -4368,63 +5024,75 @@
         </is>
       </c>
       <c r="C55" t="n">
+        <v>1.64084308088374</v>
+      </c>
+      <c r="D55" t="n">
         <v>6.649929304602164</v>
       </c>
-      <c r="D55" t="n">
+      <c r="E55" t="n">
         <v>1.587719340092558</v>
       </c>
-      <c r="E55" t="n">
+      <c r="F55" t="n">
         <v>23.35744683989813</v>
       </c>
-      <c r="F55" t="n">
+      <c r="G55" t="n">
         <v>0.0022490629569368</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>47.27353196181367</v>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>2.911069316207467</v>
       </c>
-      <c r="I55" t="n">
+      <c r="J55" t="n">
         <v>3.657497779878182</v>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
         <v>12.91971331366716</v>
       </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>5.715447469990314</v>
+      </c>
+      <c r="O55" t="n">
         <v>5.033505116141021</v>
       </c>
-      <c r="M55" t="n">
+      <c r="P55" t="n">
         <v>6.40887473117027</v>
       </c>
-      <c r="N55" t="n">
+      <c r="Q55" t="n">
         <v>6.192914461882405</v>
       </c>
-      <c r="O55" t="n">
+      <c r="R55" t="n">
         <v>6.311934399671809</v>
       </c>
-      <c r="P55" t="n">
+      <c r="S55" t="n">
         <v>5.795875370735164</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="T55" t="n">
         <v>6.758315156553115</v>
       </c>
-      <c r="R55" t="n">
+      <c r="U55" t="n">
         <v>6.144979300027695</v>
       </c>
-      <c r="S55" t="n">
+      <c r="V55" t="n">
+        <v>5.160261506590999</v>
+      </c>
+      <c r="W55" t="n">
         <v>6.539296878857749</v>
       </c>
-      <c r="T55" t="n">
+      <c r="X55" t="n">
         <v>5.349770636542128</v>
       </c>
-      <c r="U55" t="n">
+      <c r="Y55" t="n">
         <v>106376168467</v>
       </c>
-      <c r="V55" t="n">
+      <c r="Z55" t="n">
         <v>194.8</v>
       </c>
     </row>
@@ -4440,63 +5108,75 @@
         </is>
       </c>
       <c r="C56" t="n">
+        <v>1.286269518681892</v>
+      </c>
+      <c r="D56" t="n">
         <v>5.012870138596929</v>
       </c>
-      <c r="D56" t="n">
+      <c r="E56" t="n">
         <v>1.427063084284952</v>
       </c>
-      <c r="E56" t="n">
+      <c r="F56" t="n">
         <v>37.32386783636046</v>
       </c>
-      <c r="F56" t="n">
+      <c r="G56" t="n">
         <v>3.737252369175739</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>36.51759306536793</v>
       </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
         <v>2.230636553946332</v>
       </c>
-      <c r="I56" t="n">
+      <c r="J56" t="n">
         <v>2.447372677938832</v>
       </c>
-      <c r="J56" t="n">
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
         <v>10.01707475564693</v>
       </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>5.525054429045889</v>
+      </c>
+      <c r="O56" t="n">
         <v>4.950106518313071</v>
       </c>
-      <c r="M56" t="n">
+      <c r="P56" t="n">
         <v>6.37905416150384</v>
       </c>
-      <c r="N56" t="n">
+      <c r="Q56" t="n">
         <v>6.183963314259628</v>
       </c>
-      <c r="O56" t="n">
+      <c r="R56" t="n">
         <v>6.112198749500987</v>
       </c>
-      <c r="P56" t="n">
+      <c r="S56" t="n">
         <v>5.721393114938085</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="T56" t="n">
         <v>6.641260492467795</v>
       </c>
-      <c r="R56" t="n">
+      <c r="U56" t="n">
         <v>6.067916196441171</v>
       </c>
-      <c r="S56" t="n">
+      <c r="V56" t="n">
+        <v>5.174849476717395</v>
+      </c>
+      <c r="W56" t="n">
         <v>6.497604190486707</v>
       </c>
-      <c r="T56" t="n">
+      <c r="X56" t="n">
         <v>5.392809062959918</v>
       </c>
-      <c r="U56" t="n">
+      <c r="Y56" t="n">
         <v>126420550000</v>
       </c>
-      <c r="V56" t="n">
+      <c r="Z56" t="n">
         <v>189.1</v>
       </c>
     </row>
@@ -4512,63 +5192,75 @@
         </is>
       </c>
       <c r="C57" t="n">
+        <v>1.198445250141408</v>
+      </c>
+      <c r="D57" t="n">
         <v>4.765024162633832</v>
       </c>
-      <c r="D57" t="n">
+      <c r="E57" t="n">
         <v>1.539742405279153</v>
       </c>
-      <c r="E57" t="n">
+      <c r="F57" t="n">
         <v>37.65159899614215</v>
       </c>
-      <c r="F57" t="n">
+      <c r="G57" t="n">
         <v>4.144302847001049</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>36.52879827704933</v>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>2.079217079485574</v>
       </c>
-      <c r="I57" t="n">
+      <c r="J57" t="n">
         <v>2.70800470076183</v>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
         <v>9.384866281505664</v>
       </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>5.61181342742458</v>
+      </c>
+      <c r="O57" t="n">
         <v>5.010035138452943</v>
       </c>
-      <c r="M57" t="n">
+      <c r="P57" t="n">
         <v>6.43136331898431</v>
       </c>
-      <c r="N57" t="n">
+      <c r="Q57" t="n">
         <v>6.250785691575532</v>
       </c>
-      <c r="O57" t="n">
+      <c r="R57" t="n">
         <v>6.105774898729614</v>
       </c>
-      <c r="P57" t="n">
+      <c r="S57" t="n">
         <v>5.773712718629723</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="T57" t="n">
         <v>6.72530969105914</v>
       </c>
-      <c r="R57" t="n">
+      <c r="U57" t="n">
         <v>6.138871105196944</v>
       </c>
-      <c r="S57" t="n">
+      <c r="V57" t="n">
+        <v>5.248181303471562</v>
+      </c>
+      <c r="W57" t="n">
         <v>6.581304630730908</v>
       </c>
-      <c r="T57" t="n">
+      <c r="X57" t="n">
         <v>5.393627546352362</v>
       </c>
-      <c r="U57" t="n">
+      <c r="Y57" t="n">
         <v>130914950000</v>
       </c>
-      <c r="V57" t="n">
+      <c r="Z57" t="n">
         <v>183.5</v>
       </c>
     </row>
@@ -4584,63 +5276,75 @@
         </is>
       </c>
       <c r="C58" t="n">
+        <v>1.292303362665056</v>
+      </c>
+      <c r="D58" t="n">
         <v>4.126001468852729</v>
       </c>
-      <c r="D58" t="n">
+      <c r="E58" t="n">
         <v>1.488617817921817</v>
       </c>
-      <c r="E58" t="n">
+      <c r="F58" t="n">
         <v>38.17619681488448</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>5.499225218083605</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>33.72094075959409</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>2.245937541770857</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>2.068210860732854</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
         <v>11.38256615549452</v>
       </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>5.641233076332052</v>
+      </c>
+      <c r="O58" t="n">
         <v>5.150687067230235</v>
       </c>
-      <c r="M58" t="n">
+      <c r="P58" t="n">
         <v>6.443240561964264</v>
       </c>
-      <c r="N58" t="n">
+      <c r="Q58" t="n">
         <v>6.298140091560785</v>
       </c>
-      <c r="O58" t="n">
+      <c r="R58" t="n">
         <v>6.136451951341516</v>
       </c>
-      <c r="P58" t="n">
+      <c r="S58" t="n">
         <v>5.716073270605298</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="T58" t="n">
         <v>6.664217644368194</v>
       </c>
-      <c r="R58" t="n">
+      <c r="U58" t="n">
         <v>6.18134085859394</v>
       </c>
-      <c r="S58" t="n">
+      <c r="V58" t="n">
+        <v>5.284015600411479</v>
+      </c>
+      <c r="W58" t="n">
         <v>6.602750694563431</v>
       </c>
-      <c r="T58" t="n">
+      <c r="X58" t="n">
         <v>5.529151242073817</v>
       </c>
-      <c r="U58" t="n">
+      <c r="Y58" t="n">
         <v>127578481000</v>
       </c>
-      <c r="V58" t="n">
+      <c r="Z58" t="n">
         <v>182.1</v>
       </c>
     </row>
@@ -4656,63 +5360,75 @@
         </is>
       </c>
       <c r="C59" t="n">
+        <v>1.295558250657866</v>
+      </c>
+      <c r="D59" t="n">
         <v>4.07284473823228</v>
       </c>
-      <c r="D59" t="n">
+      <c r="E59" t="n">
         <v>1.369827057385176</v>
       </c>
-      <c r="E59" t="n">
+      <c r="F59" t="n">
         <v>39.30055879462355</v>
       </c>
-      <c r="F59" t="n">
+      <c r="G59" t="n">
         <v>5.233543246326696</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>32.82508752045611</v>
       </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
         <v>2.343687741700366</v>
       </c>
-      <c r="I59" t="n">
+      <c r="J59" t="n">
         <v>1.997701366857856</v>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
         <v>11.5611912837601</v>
       </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>5.672016555091186</v>
+      </c>
+      <c r="O59" t="n">
         <v>5.207516998879711</v>
       </c>
-      <c r="M59" t="n">
+      <c r="P59" t="n">
         <v>6.430380506518972</v>
       </c>
-      <c r="N59" t="n">
+      <c r="Q59" t="n">
         <v>6.336808014590168</v>
       </c>
-      <c r="O59" t="n">
+      <c r="R59" t="n">
         <v>6.23908608241747</v>
       </c>
-      <c r="P59" t="n">
+      <c r="S59" t="n">
         <v>5.731365263241644</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="T59" t="n">
         <v>6.720762845255303</v>
       </c>
-      <c r="R59" t="n">
+      <c r="U59" t="n">
         <v>6.18931082307967</v>
       </c>
-      <c r="S59" t="n">
+      <c r="V59" t="n">
+        <v>5.331461991710737</v>
+      </c>
+      <c r="W59" t="n">
         <v>6.569537489007001</v>
       </c>
-      <c r="T59" t="n">
+      <c r="X59" t="n">
         <v>5.586124476958614</v>
       </c>
-      <c r="U59" t="n">
+      <c r="Y59" t="n">
         <v>128923574000</v>
       </c>
-      <c r="V59" t="n">
+      <c r="Z59" t="n">
         <v>187.6</v>
       </c>
     </row>
@@ -4728,63 +5444,75 @@
         </is>
       </c>
       <c r="C60" t="n">
+        <v>1.296329010852902</v>
+      </c>
+      <c r="D60" t="n">
         <v>4.509851272888415</v>
       </c>
-      <c r="D60" t="n">
+      <c r="E60" t="n">
         <v>1.527291966612184</v>
       </c>
-      <c r="E60" t="n">
+      <c r="F60" t="n">
         <v>37.14100765524511</v>
       </c>
-      <c r="F60" t="n">
+      <c r="G60" t="n">
         <v>5.412221875901391</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>32.87284634405501</v>
       </c>
-      <c r="H60" t="n">
+      <c r="I60" t="n">
         <v>2.010811817617267</v>
       </c>
-      <c r="I60" t="n">
+      <c r="J60" t="n">
         <v>3.072521875252283</v>
       </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
         <v>12.15711818157543</v>
       </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>5.703349031123749</v>
+      </c>
+      <c r="O60" t="n">
         <v>5.13920440562525</v>
       </c>
-      <c r="M60" t="n">
+      <c r="P60" t="n">
         <v>6.455135702830883</v>
       </c>
-      <c r="N60" t="n">
+      <c r="Q60" t="n">
         <v>6.303607457781574</v>
       </c>
-      <c r="O60" t="n">
+      <c r="R60" t="n">
         <v>6.254501615165327</v>
       </c>
-      <c r="P60" t="n">
+      <c r="S60" t="n">
         <v>5.770880241018378</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="T60" t="n">
         <v>6.725981545738269</v>
       </c>
-      <c r="R60" t="n">
+      <c r="U60" t="n">
         <v>6.224300960721666</v>
       </c>
-      <c r="S60" t="n">
+      <c r="V60" t="n">
+        <v>5.302359175216576</v>
+      </c>
+      <c r="W60" t="n">
         <v>6.686759383182858</v>
       </c>
-      <c r="T60" t="n">
+      <c r="X60" t="n">
         <v>5.516609140145141</v>
       </c>
-      <c r="U60" t="n">
+      <c r="Y60" t="n">
         <v>128637945000</v>
       </c>
-      <c r="V60" t="n">
+      <c r="Z60" t="n">
         <v>186.9</v>
       </c>
     </row>
@@ -4800,63 +5528,75 @@
         </is>
       </c>
       <c r="C61" t="n">
+        <v>1.763455038345604</v>
+      </c>
+      <c r="D61" t="n">
         <v>3.879796988708001</v>
       </c>
-      <c r="D61" t="n">
+      <c r="E61" t="n">
         <v>1.450453196229152</v>
       </c>
-      <c r="E61" t="n">
+      <c r="F61" t="n">
         <v>31.06043273687472</v>
       </c>
-      <c r="F61" t="n">
+      <c r="G61" t="n">
         <v>4.716596051018876</v>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>34.26863295734152</v>
       </c>
-      <c r="H61" t="n">
+      <c r="I61" t="n">
         <v>1.700359767916936</v>
       </c>
-      <c r="I61" t="n">
+      <c r="J61" t="n">
         <v>6.878426909735076</v>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
         <v>14.28184635383011</v>
       </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>5.743515888606315</v>
+      </c>
+      <c r="O61" t="n">
         <v>5.173943915164208</v>
       </c>
-      <c r="M61" t="n">
+      <c r="P61" t="n">
         <v>6.473612891293051</v>
       </c>
-      <c r="N61" t="n">
+      <c r="Q61" t="n">
         <v>6.276248633252147</v>
       </c>
-      <c r="O61" t="n">
+      <c r="R61" t="n">
         <v>6.318066806790422</v>
       </c>
-      <c r="P61" t="n">
+      <c r="S61" t="n">
         <v>5.957209481520768</v>
       </c>
-      <c r="Q61" t="n">
+      <c r="T61" t="n">
         <v>6.680741715251393</v>
       </c>
-      <c r="R61" t="n">
+      <c r="U61" t="n">
         <v>6.287988676834196</v>
       </c>
-      <c r="S61" t="n">
+      <c r="V61" t="n">
+        <v>5.264502049620493</v>
+      </c>
+      <c r="W61" t="n">
         <v>6.694500190526903</v>
       </c>
-      <c r="T61" t="n">
+      <c r="X61" t="n">
         <v>5.509023912590322</v>
       </c>
-      <c r="U61" t="n">
+      <c r="Y61" t="n">
         <v>147827245000</v>
       </c>
-      <c r="V61" t="n">
+      <c r="Z61" t="n">
         <v>188.2</v>
       </c>
     </row>
@@ -4872,63 +5612,75 @@
         </is>
       </c>
       <c r="C62" t="n">
+        <v>1.794483128917162</v>
+      </c>
+      <c r="D62" t="n">
         <v>3.9046886990978</v>
       </c>
-      <c r="D62" t="n">
+      <c r="E62" t="n">
         <v>1.384284652246988</v>
       </c>
-      <c r="E62" t="n">
+      <c r="F62" t="n">
         <v>29.37080685867631</v>
       </c>
-      <c r="F62" t="n">
+      <c r="G62" t="n">
         <v>3.953227606013194</v>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>32.61144093564084</v>
       </c>
-      <c r="H62" t="n">
+      <c r="I62" t="n">
         <v>1.646313486532132</v>
       </c>
-      <c r="I62" t="n">
+      <c r="J62" t="n">
         <v>6.19119861711797</v>
       </c>
-      <c r="J62" t="n">
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
         <v>19.14355601575761</v>
       </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>5.795236778559979</v>
+      </c>
+      <c r="O62" t="n">
         <v>5.122057357452936</v>
       </c>
-      <c r="M62" t="n">
+      <c r="P62" t="n">
         <v>6.551423119478071</v>
       </c>
-      <c r="N62" t="n">
+      <c r="Q62" t="n">
         <v>6.331128075471054</v>
       </c>
-      <c r="O62" t="n">
+      <c r="R62" t="n">
         <v>6.242242739517733</v>
       </c>
-      <c r="P62" t="n">
+      <c r="S62" t="n">
         <v>5.977821874036374</v>
       </c>
-      <c r="Q62" t="n">
+      <c r="T62" t="n">
         <v>6.756641649312376</v>
       </c>
-      <c r="R62" t="n">
+      <c r="U62" t="n">
         <v>6.327275859800679</v>
       </c>
-      <c r="S62" t="n">
+      <c r="V62" t="n">
+        <v>5.273153386625434</v>
+      </c>
+      <c r="W62" t="n">
         <v>6.809271091510502</v>
       </c>
-      <c r="T62" t="n">
+      <c r="X62" t="n">
         <v>5.561642707495078</v>
       </c>
-      <c r="U62" t="n">
+      <c r="Y62" t="n">
         <v>161697090000</v>
       </c>
-      <c r="V62" t="n">
+      <c r="Z62" t="n">
         <v>191.5</v>
       </c>
     </row>
@@ -4944,63 +5696,75 @@
         </is>
       </c>
       <c r="C63" t="n">
+        <v>1.747977987109494</v>
+      </c>
+      <c r="D63" t="n">
         <v>4.210816185592088</v>
       </c>
-      <c r="D63" t="n">
+      <c r="E63" t="n">
         <v>1.619895493087131</v>
       </c>
-      <c r="E63" t="n">
+      <c r="F63" t="n">
         <v>28.86133126599708</v>
       </c>
-      <c r="F63" t="n">
+      <c r="G63" t="n">
         <v>4.119775723316028</v>
       </c>
-      <c r="G63" t="n">
+      <c r="H63" t="n">
         <v>33.70292029975766</v>
       </c>
-      <c r="H63" t="n">
+      <c r="I63" t="n">
         <v>1.568802162560147</v>
       </c>
-      <c r="I63" t="n">
+      <c r="J63" t="n">
         <v>6.452473468518185</v>
       </c>
-      <c r="J63" t="n">
+      <c r="K63" t="n">
+        <v>0.2581290949754001</v>
+      </c>
+      <c r="L63" t="n">
         <v>17.45787831908679</v>
       </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>5.82132848497314</v>
+      </c>
+      <c r="O63" t="n">
         <v>5.037147380711266</v>
       </c>
-      <c r="M63" t="n">
+      <c r="P63" t="n">
         <v>6.570966989003354</v>
       </c>
-      <c r="N63" t="n">
+      <c r="Q63" t="n">
         <v>6.340059465288361</v>
       </c>
-      <c r="O63" t="n">
+      <c r="R63" t="n">
         <v>6.169422437907632</v>
       </c>
-      <c r="P63" t="n">
+      <c r="S63" t="n">
         <v>6.015156650423855</v>
       </c>
-      <c r="Q63" t="n">
+      <c r="T63" t="n">
         <v>6.821031125477108</v>
       </c>
-      <c r="R63" t="n">
+      <c r="U63" t="n">
         <v>6.368049926347847</v>
       </c>
-      <c r="S63" t="n">
+      <c r="V63" t="n">
+        <v>5.304100629508722</v>
+      </c>
+      <c r="W63" t="n">
         <v>6.846177734406925</v>
       </c>
-      <c r="T63" t="n">
+      <c r="X63" t="n">
         <v>5.575077469648093</v>
       </c>
-      <c r="U63" t="n">
+      <c r="Y63" t="n">
         <v>161956559000</v>
       </c>
-      <c r="V63" t="n">
+      <c r="Z63" t="n">
         <v>193.6</v>
       </c>
     </row>
@@ -5016,63 +5780,75 @@
         </is>
       </c>
       <c r="C64" t="n">
+        <v>1.696581116617458</v>
+      </c>
+      <c r="D64" t="n">
         <v>3.825682760558423</v>
       </c>
-      <c r="D64" t="n">
+      <c r="E64" t="n">
         <v>1.668785980965651</v>
       </c>
-      <c r="E64" t="n">
+      <c r="F64" t="n">
         <v>24.89963210434627</v>
       </c>
-      <c r="F64" t="n">
+      <c r="G64" t="n">
         <v>4.164875592681319</v>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>41.47316743121601</v>
       </c>
-      <c r="H64" t="n">
+      <c r="I64" t="n">
         <v>1.31444645639713</v>
       </c>
-      <c r="I64" t="n">
+      <c r="J64" t="n">
         <v>5.248748406147692</v>
       </c>
-      <c r="J64" t="n">
+      <c r="K64" t="n">
+        <v>0.260936329729189</v>
+      </c>
+      <c r="L64" t="n">
         <v>15.44714382134086</v>
       </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>5.875351973286877</v>
+      </c>
+      <c r="O64" t="n">
         <v>5.089877651526888</v>
       </c>
-      <c r="M64" t="n">
+      <c r="P64" t="n">
         <v>6.575731094079357</v>
       </c>
-      <c r="N64" t="n">
+      <c r="Q64" t="n">
         <v>6.319670596044242</v>
       </c>
-      <c r="O64" t="n">
+      <c r="R64" t="n">
         <v>6.227958585199358</v>
       </c>
-      <c r="P64" t="n">
+      <c r="S64" t="n">
         <v>6.061643350434983</v>
       </c>
-      <c r="Q64" t="n">
+      <c r="T64" t="n">
         <v>6.852570208351747</v>
       </c>
-      <c r="R64" t="n">
+      <c r="U64" t="n">
         <v>6.404203147261689</v>
       </c>
-      <c r="S64" t="n">
+      <c r="V64" t="n">
+        <v>5.294309329830428</v>
+      </c>
+      <c r="W64" t="n">
         <v>6.92574255797537</v>
       </c>
-      <c r="T64" t="n">
+      <c r="X64" t="n">
         <v>5.603556954713747</v>
       </c>
-      <c r="U64" t="n">
+      <c r="Y64" t="n">
         <v>177484293000</v>
       </c>
-      <c r="V64" t="n">
+      <c r="Z64" t="n">
         <v>194.8</v>
       </c>
     </row>
@@ -5088,63 +5864,75 @@
         </is>
       </c>
       <c r="C65" t="n">
+        <v>1.897691242308293</v>
+      </c>
+      <c r="D65" t="n">
         <v>3.383969052719987</v>
       </c>
-      <c r="D65" t="n">
+      <c r="E65" t="n">
         <v>1.344115993265923</v>
       </c>
-      <c r="E65" t="n">
+      <c r="F65" t="n">
         <v>23.41021411803225</v>
       </c>
-      <c r="F65" t="n">
+      <c r="G65" t="n">
         <v>4.27148643324601</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>42.66703831649744</v>
       </c>
-      <c r="H65" t="n">
+      <c r="I65" t="n">
         <v>1.669367338385706</v>
       </c>
-      <c r="I65" t="n">
+      <c r="J65" t="n">
         <v>5.519010454064541</v>
       </c>
-      <c r="J65" t="n">
+      <c r="K65" t="n">
+        <v>0.2537776607329693</v>
+      </c>
+      <c r="L65" t="n">
         <v>15.58332939074688</v>
       </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>5.952281845927549</v>
+      </c>
+      <c r="O65" t="n">
         <v>5.114694945686653</v>
       </c>
-      <c r="M65" t="n">
+      <c r="P65" t="n">
         <v>6.68111815972557</v>
       </c>
-      <c r="N65" t="n">
+      <c r="Q65" t="n">
         <v>6.37020914197893</v>
       </c>
-      <c r="O65" t="n">
+      <c r="R65" t="n">
         <v>6.296980384689881</v>
       </c>
-      <c r="P65" t="n">
+      <c r="S65" t="n">
         <v>6.139151532905012</v>
       </c>
-      <c r="Q65" t="n">
+      <c r="T65" t="n">
         <v>6.875335362507492</v>
       </c>
-      <c r="R65" t="n">
+      <c r="U65" t="n">
         <v>6.465600290545812</v>
       </c>
-      <c r="S65" t="n">
+      <c r="V65" t="n">
+        <v>5.311529716090384</v>
+      </c>
+      <c r="W65" t="n">
         <v>7.022698783510905</v>
       </c>
-      <c r="T65" t="n">
+      <c r="X65" t="n">
         <v>5.563485431254279</v>
       </c>
-      <c r="U65" t="n">
+      <c r="Y65" t="n">
         <v>191075920000</v>
       </c>
-      <c r="V65" t="n">
+      <c r="Z65" t="n">
         <v>196.3</v>
       </c>
     </row>
@@ -5160,63 +5948,75 @@
         </is>
       </c>
       <c r="C66" t="n">
+        <v>2.380478915870994</v>
+      </c>
+      <c r="D66" t="n">
         <v>3.26888761921435</v>
       </c>
-      <c r="D66" t="n">
+      <c r="E66" t="n">
         <v>1.216820594473898</v>
       </c>
-      <c r="E66" t="n">
+      <c r="F66" t="n">
         <v>20.46946352900849</v>
       </c>
-      <c r="F66" t="n">
+      <c r="G66" t="n">
         <v>2.321333980248336</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>40.95210745419149</v>
       </c>
-      <c r="H66" t="n">
+      <c r="I66" t="n">
         <v>1.736140598110213</v>
       </c>
-      <c r="I66" t="n">
+      <c r="J66" t="n">
         <v>5.306503031303086</v>
       </c>
-      <c r="J66" t="n">
+      <c r="K66" t="n">
+        <v>0.2448098098334833</v>
+      </c>
+      <c r="L66" t="n">
         <v>22.10345446774566</v>
       </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>5.853953776828187</v>
+      </c>
+      <c r="O66" t="n">
         <v>5.007028843422972</v>
       </c>
-      <c r="M66" t="n">
+      <c r="P66" t="n">
         <v>6.664549297949263</v>
       </c>
-      <c r="N66" t="n">
+      <c r="Q66" t="n">
         <v>6.269967158121124</v>
       </c>
-      <c r="O66" t="n">
+      <c r="R66" t="n">
         <v>6.191032374391726</v>
       </c>
-      <c r="P66" t="n">
+      <c r="S66" t="n">
         <v>6.104346676904647</v>
       </c>
-      <c r="Q66" t="n">
+      <c r="T66" t="n">
         <v>6.825698846720581</v>
       </c>
-      <c r="R66" t="n">
+      <c r="U66" t="n">
         <v>6.416797603952926</v>
       </c>
-      <c r="S66" t="n">
+      <c r="V66" t="n">
+        <v>5.245022043739299</v>
+      </c>
+      <c r="W66" t="n">
         <v>7.015065918279396</v>
       </c>
-      <c r="T66" t="n">
+      <c r="X66" t="n">
         <v>5.543731105609067</v>
       </c>
-      <c r="U66" t="n">
+      <c r="Y66" t="n">
         <v>188795539000</v>
       </c>
-      <c r="V66" t="n">
+      <c r="Z66" t="n">
         <v>199.3</v>
       </c>
     </row>
@@ -5232,63 +6032,75 @@
         </is>
       </c>
       <c r="C67" t="n">
+        <v>1.236627746940204</v>
+      </c>
+      <c r="D67" t="n">
         <v>3.085484986612751</v>
       </c>
-      <c r="D67" t="n">
+      <c r="E67" t="n">
         <v>1.296241172103537</v>
       </c>
-      <c r="E67" t="n">
+      <c r="F67" t="n">
         <v>19.98981673265071</v>
       </c>
-      <c r="F67" t="n">
+      <c r="G67" t="n">
         <v>1.995455362027432</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>40.5270537899315</v>
       </c>
-      <c r="H67" t="n">
+      <c r="I67" t="n">
         <v>1.928454527644118</v>
       </c>
-      <c r="I67" t="n">
+      <c r="J67" t="n">
         <v>4.908725208150103</v>
       </c>
-      <c r="J67" t="n">
+      <c r="K67" t="n">
+        <v>0.2610323653704142</v>
+      </c>
+      <c r="L67" t="n">
         <v>24.77110810856923</v>
       </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>5.896191849816511</v>
+      </c>
+      <c r="O67" t="n">
         <v>4.998022723080163</v>
       </c>
-      <c r="M67" t="n">
+      <c r="P67" t="n">
         <v>6.768757522081929</v>
       </c>
-      <c r="N67" t="n">
+      <c r="Q67" t="n">
         <v>6.271139681458904</v>
       </c>
-      <c r="O67" t="n">
+      <c r="R67" t="n">
         <v>6.330682970267938</v>
       </c>
-      <c r="P67" t="n">
+      <c r="S67" t="n">
         <v>6.089384939832648</v>
       </c>
-      <c r="Q67" t="n">
+      <c r="T67" t="n">
         <v>6.872936095338796</v>
       </c>
-      <c r="R67" t="n">
+      <c r="U67" t="n">
         <v>6.400423503922216</v>
       </c>
-      <c r="S67" t="n">
+      <c r="V67" t="n">
+        <v>5.307772495088402</v>
+      </c>
+      <c r="W67" t="n">
         <v>7.105490773848762</v>
       </c>
-      <c r="T67" t="n">
+      <c r="X67" t="n">
         <v>5.583721838079611</v>
       </c>
-      <c r="U67" t="n">
+      <c r="Y67" t="n">
         <v>195467715000</v>
       </c>
-      <c r="V67" t="n">
+      <c r="Z67" t="n">
         <v>204.2</v>
       </c>
     </row>
@@ -5304,63 +6116,75 @@
         </is>
       </c>
       <c r="C68" t="n">
+        <v>1.084387874687115</v>
+      </c>
+      <c r="D68" t="n">
         <v>2.770292777387469</v>
       </c>
-      <c r="D68" t="n">
+      <c r="E68" t="n">
         <v>1.025514516713106</v>
       </c>
-      <c r="E68" t="n">
+      <c r="F68" t="n">
         <v>16.96254048335144</v>
       </c>
-      <c r="F68" t="n">
+      <c r="G68" t="n">
         <v>0.7870824390842832</v>
       </c>
-      <c r="G68" t="n">
+      <c r="H68" t="n">
         <v>42.58720053418472</v>
       </c>
-      <c r="H68" t="n">
+      <c r="I68" t="n">
         <v>1.691807531219197</v>
       </c>
-      <c r="I68" t="n">
+      <c r="J68" t="n">
         <v>5.165722041748252</v>
       </c>
-      <c r="J68" t="n">
+      <c r="K68" t="n">
+        <v>0.234139709335225</v>
+      </c>
+      <c r="L68" t="n">
         <v>27.69131209228921</v>
       </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="n">
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>5.9051165963537</v>
+      </c>
+      <c r="O68" t="n">
         <v>5.077546029824153</v>
       </c>
-      <c r="M68" t="n">
+      <c r="P68" t="n">
         <v>6.84203207200633</v>
       </c>
-      <c r="N68" t="n">
+      <c r="Q68" t="n">
         <v>6.318156952038252</v>
       </c>
-      <c r="O68" t="n">
+      <c r="R68" t="n">
         <v>6.344108887611997</v>
       </c>
-      <c r="P68" t="n">
+      <c r="S68" t="n">
         <v>6.130726340546189</v>
       </c>
-      <c r="Q68" t="n">
+      <c r="T68" t="n">
         <v>7.009661863046862</v>
       </c>
-      <c r="R68" t="n">
+      <c r="U68" t="n">
         <v>6.499802092821705</v>
       </c>
-      <c r="S68" t="n">
+      <c r="V68" t="n">
+        <v>5.299017118612687</v>
+      </c>
+      <c r="W68" t="n">
         <v>7.191843437676646</v>
       </c>
-      <c r="T68" t="n">
+      <c r="X68" t="n">
         <v>5.591136254984248</v>
       </c>
-      <c r="U68" t="n">
+      <c r="Y68" t="n">
         <v>221020177000</v>
       </c>
-      <c r="V68" t="n">
+      <c r="Z68" t="n">
         <v>203.6</v>
       </c>
     </row>
@@ -5376,63 +6200,75 @@
         </is>
       </c>
       <c r="C69" t="n">
+        <v>1.223036121890438</v>
+      </c>
+      <c r="D69" t="n">
         <v>2.805689155265374</v>
       </c>
-      <c r="D69" t="n">
+      <c r="E69" t="n">
         <v>1.56639913690407</v>
       </c>
-      <c r="E69" t="n">
+      <c r="F69" t="n">
         <v>18.56957261923306</v>
       </c>
-      <c r="F69" t="n">
+      <c r="G69" t="n">
         <v>0.5615363978105217</v>
       </c>
-      <c r="G69" t="n">
+      <c r="H69" t="n">
         <v>45.51510454862476</v>
       </c>
-      <c r="H69" t="n">
+      <c r="I69" t="n">
         <v>1.475968755982577</v>
       </c>
-      <c r="I69" t="n">
+      <c r="J69" t="n">
         <v>4.96725026706411</v>
       </c>
-      <c r="J69" t="n">
+      <c r="K69" t="n">
+        <v>0.2888595314694893</v>
+      </c>
+      <c r="L69" t="n">
         <v>23.0265834657556</v>
       </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>5.757702301223951</v>
+      </c>
+      <c r="O69" t="n">
         <v>4.932889936675444</v>
       </c>
-      <c r="M69" t="n">
+      <c r="P69" t="n">
         <v>6.661215149861532</v>
       </c>
-      <c r="N69" t="n">
+      <c r="Q69" t="n">
         <v>6.257437685753745</v>
       </c>
-      <c r="O69" t="n">
+      <c r="R69" t="n">
         <v>6.049898553216259</v>
       </c>
-      <c r="P69" t="n">
+      <c r="S69" t="n">
         <v>5.981161638695274</v>
       </c>
-      <c r="Q69" t="n">
+      <c r="T69" t="n">
         <v>6.908934576013744</v>
       </c>
-      <c r="R69" t="n">
+      <c r="U69" t="n">
         <v>6.295561111293644</v>
       </c>
-      <c r="S69" t="n">
+      <c r="V69" t="n">
+        <v>5.259368619582427</v>
+      </c>
+      <c r="W69" t="n">
         <v>6.992381367141846</v>
       </c>
-      <c r="T69" t="n">
+      <c r="X69" t="n">
         <v>5.593260458943798</v>
       </c>
-      <c r="U69" t="n">
+      <c r="Y69" t="n">
         <v>182503931000</v>
       </c>
-      <c r="V69" t="n">
+      <c r="Z69" t="n">
         <v>201</v>
       </c>
     </row>
@@ -5448,63 +6284,75 @@
         </is>
       </c>
       <c r="C70" t="n">
+        <v>1.158627466011735</v>
+      </c>
+      <c r="D70" t="n">
         <v>2.65316066565813</v>
       </c>
-      <c r="D70" t="n">
+      <c r="E70" t="n">
         <v>2.060541379118143</v>
       </c>
-      <c r="E70" t="n">
+      <c r="F70" t="n">
         <v>15.35459920911268</v>
       </c>
-      <c r="F70" t="n">
+      <c r="G70" t="n">
         <v>0.2661523695975296</v>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>46.41032272226372</v>
       </c>
-      <c r="H70" t="n">
+      <c r="I70" t="n">
         <v>1.419070512412915</v>
       </c>
-      <c r="I70" t="n">
+      <c r="J70" t="n">
         <v>4.831101765759796</v>
       </c>
-      <c r="J70" t="n">
+      <c r="K70" t="n">
+        <v>0.3141870370753607</v>
+      </c>
+      <c r="L70" t="n">
         <v>25.53223687298999</v>
       </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>5.86499391422269</v>
+      </c>
+      <c r="O70" t="n">
         <v>5.074986305284329</v>
       </c>
-      <c r="M70" t="n">
+      <c r="P70" t="n">
         <v>6.815387786707124</v>
       </c>
-      <c r="N70" t="n">
+      <c r="Q70" t="n">
         <v>6.361129793258153</v>
       </c>
-      <c r="O70" t="n">
+      <c r="R70" t="n">
         <v>6.206858174486936</v>
       </c>
-      <c r="P70" t="n">
+      <c r="S70" t="n">
         <v>6.08114527208534</v>
       </c>
-      <c r="Q70" t="n">
+      <c r="T70" t="n">
         <v>6.970016199199501</v>
       </c>
-      <c r="R70" t="n">
+      <c r="U70" t="n">
         <v>6.46996327494141</v>
       </c>
-      <c r="S70" t="n">
+      <c r="V70" t="n">
+        <v>5.41043994858848</v>
+      </c>
+      <c r="W70" t="n">
         <v>7.183415394738597</v>
       </c>
-      <c r="T70" t="n">
+      <c r="X70" t="n">
         <v>5.675965783005354</v>
       </c>
-      <c r="U70" t="n">
+      <c r="Y70" t="n">
         <v>198552431000</v>
       </c>
-      <c r="V70" t="n">
+      <c r="Z70" t="n">
         <v>200.8</v>
       </c>
     </row>
@@ -5520,63 +6368,75 @@
         </is>
       </c>
       <c r="C71" t="n">
+        <v>0.3483723785935723</v>
+      </c>
+      <c r="D71" t="n">
         <v>2.630707029072828</v>
       </c>
-      <c r="D71" t="n">
+      <c r="E71" t="n">
         <v>2.11664316642524</v>
       </c>
-      <c r="E71" t="n">
+      <c r="F71" t="n">
         <v>15.28192240395543</v>
       </c>
-      <c r="F71" t="n">
+      <c r="G71" t="n">
         <v>0.2504986741874384</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>47.34248185139635</v>
       </c>
-      <c r="H71" t="n">
+      <c r="I71" t="n">
         <v>1.260905364512825</v>
       </c>
-      <c r="I71" t="n">
+      <c r="J71" t="n">
         <v>4.871256613424756</v>
       </c>
-      <c r="J71" t="n">
+      <c r="K71" t="n">
+        <v>0.2980769330008392</v>
+      </c>
+      <c r="L71" t="n">
         <v>25.59913558543072</v>
       </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>5.905743286601282</v>
+      </c>
+      <c r="O71" t="n">
         <v>5.101267858334363</v>
       </c>
-      <c r="M71" t="n">
+      <c r="P71" t="n">
         <v>6.851798513909338</v>
       </c>
-      <c r="N71" t="n">
+      <c r="Q71" t="n">
         <v>6.392486510477201</v>
       </c>
-      <c r="O71" t="n">
+      <c r="R71" t="n">
         <v>6.156427965654443</v>
       </c>
-      <c r="P71" t="n">
+      <c r="S71" t="n">
         <v>6.128875932190365</v>
       </c>
-      <c r="Q71" t="n">
+      <c r="T71" t="n">
         <v>6.977719651065778</v>
       </c>
-      <c r="R71" t="n">
+      <c r="U71" t="n">
         <v>6.479568992483218</v>
       </c>
-      <c r="S71" t="n">
+      <c r="V71" t="n">
+        <v>5.426094712318587</v>
+      </c>
+      <c r="W71" t="n">
         <v>7.22443293096456</v>
       </c>
-      <c r="T71" t="n">
+      <c r="X71" t="n">
         <v>5.713864838195053</v>
       </c>
-      <c r="U71" t="n">
+      <c r="Y71" t="n">
         <v>207346806000</v>
       </c>
-      <c r="V71" t="n">
+      <c r="Z71" t="n">
         <v>200.3</v>
       </c>
     </row>
@@ -5592,63 +6452,75 @@
         </is>
       </c>
       <c r="C72" t="n">
+        <v>0.3421048814180287</v>
+      </c>
+      <c r="D72" t="n">
         <v>2.686130312592186</v>
       </c>
-      <c r="D72" t="n">
+      <c r="E72" t="n">
         <v>2.080053889047787</v>
       </c>
-      <c r="E72" t="n">
+      <c r="F72" t="n">
         <v>15.05432540032785</v>
       </c>
-      <c r="F72" t="n">
+      <c r="G72" t="n">
         <v>0.4034687403558535</v>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>45.98826705022418</v>
       </c>
-      <c r="H72" t="n">
+      <c r="I72" t="n">
         <v>1.188178943580164</v>
       </c>
-      <c r="I72" t="n">
+      <c r="J72" t="n">
         <v>4.726570162313324</v>
       </c>
-      <c r="J72" t="n">
+      <c r="K72" t="n">
+        <v>0.3257735773913436</v>
+      </c>
+      <c r="L72" t="n">
         <v>27.20512704274928</v>
       </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>5.89896542265359</v>
+      </c>
+      <c r="O72" t="n">
         <v>5.119549455111312</v>
       </c>
-      <c r="M72" t="n">
+      <c r="P72" t="n">
         <v>6.853584184044609</v>
       </c>
-      <c r="N72" t="n">
+      <c r="Q72" t="n">
         <v>6.444735215588676</v>
       </c>
-      <c r="O72" t="n">
+      <c r="R72" t="n">
         <v>6.080230644864034</v>
       </c>
-      <c r="P72" t="n">
+      <c r="S72" t="n">
         <v>6.143198040488773</v>
       </c>
-      <c r="Q72" t="n">
+      <c r="T72" t="n">
         <v>6.950211133338682</v>
       </c>
-      <c r="R72" t="n">
+      <c r="U72" t="n">
         <v>6.484467304968415</v>
       </c>
-      <c r="S72" t="n">
+      <c r="V72" t="n">
+        <v>5.495527560891224</v>
+      </c>
+      <c r="W72" t="n">
         <v>7.25372511694016</v>
       </c>
-      <c r="T72" t="n">
+      <c r="X72" t="n">
         <v>5.794506366332176</v>
       </c>
-      <c r="U72" t="n">
+      <c r="Y72" t="n">
         <v>213840854000</v>
       </c>
-      <c r="V72" t="n">
+      <c r="Z72" t="n">
         <v>198.4</v>
       </c>
     </row>
@@ -5664,63 +6536,75 @@
         </is>
       </c>
       <c r="C73" t="n">
+        <v>0.3060777940250467</v>
+      </c>
+      <c r="D73" t="n">
         <v>2.701049621026099</v>
       </c>
-      <c r="D73" t="n">
+      <c r="E73" t="n">
         <v>1.925650274436831</v>
       </c>
-      <c r="E73" t="n">
+      <c r="F73" t="n">
         <v>14.31436337143778</v>
       </c>
-      <c r="F73" t="n">
+      <c r="G73" t="n">
         <v>0.3342711462621395</v>
       </c>
-      <c r="G73" t="n">
+      <c r="H73" t="n">
         <v>43.51380258664048</v>
       </c>
-      <c r="H73" t="n">
+      <c r="I73" t="n">
         <v>1.476203159626462</v>
       </c>
-      <c r="I73" t="n">
+      <c r="J73" t="n">
         <v>4.233010006212588</v>
       </c>
-      <c r="J73" t="n">
+      <c r="K73" t="n">
+        <v>0.2877556836395994</v>
+      </c>
+      <c r="L73" t="n">
         <v>30.90781635669298</v>
       </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>5.955448708721976</v>
+      </c>
+      <c r="O73" t="n">
         <v>5.202026702869524</v>
       </c>
-      <c r="M73" t="n">
+      <c r="P73" t="n">
         <v>6.893950406727489</v>
       </c>
-      <c r="N73" t="n">
+      <c r="Q73" t="n">
         <v>6.472299880291049</v>
       </c>
-      <c r="O73" t="n">
+      <c r="R73" t="n">
         <v>6.123501054255751</v>
       </c>
-      <c r="P73" t="n">
+      <c r="S73" t="n">
         <v>6.23713253714522</v>
       </c>
-      <c r="Q73" t="n">
+      <c r="T73" t="n">
         <v>7.080194794827444</v>
       </c>
-      <c r="R73" t="n">
+      <c r="U73" t="n">
         <v>6.533207238002494</v>
       </c>
-      <c r="S73" t="n">
+      <c r="V73" t="n">
+        <v>5.481971399052711</v>
+      </c>
+      <c r="W73" t="n">
         <v>7.38471592940399</v>
       </c>
-      <c r="T73" t="n">
+      <c r="X73" t="n">
         <v>5.794110522869158</v>
       </c>
-      <c r="U73" t="n">
+      <c r="Y73" t="n">
         <v>240992981000</v>
       </c>
-      <c r="V73" t="n">
+      <c r="Z73" t="n">
         <v>199</v>
       </c>
     </row>
@@ -5736,63 +6620,75 @@
         </is>
       </c>
       <c r="C74" t="n">
+        <v>0.2375606790862851</v>
+      </c>
+      <c r="D74" t="n">
         <v>2.825055258036157</v>
       </c>
-      <c r="D74" t="n">
+      <c r="E74" t="n">
         <v>1.772224416762384</v>
       </c>
-      <c r="E74" t="n">
+      <c r="F74" t="n">
         <v>15.78782672008412</v>
       </c>
-      <c r="F74" t="n">
+      <c r="G74" t="n">
         <v>0.1252955721375176</v>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>37.13874998320544</v>
       </c>
-      <c r="H74" t="n">
+      <c r="I74" t="n">
         <v>2.016278897696824</v>
       </c>
-      <c r="I74" t="n">
+      <c r="J74" t="n">
         <v>2.958383645343758</v>
       </c>
-      <c r="J74" t="n">
+      <c r="K74" t="n">
+        <v>0.1928338544938397</v>
+      </c>
+      <c r="L74" t="n">
         <v>36.94579097315367</v>
       </c>
-      <c r="K74" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" t="n">
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>5.646259327201957</v>
+      </c>
+      <c r="O74" t="n">
         <v>5.012965950029919</v>
       </c>
-      <c r="M74" t="n">
+      <c r="P74" t="n">
         <v>6.675961907290641</v>
       </c>
-      <c r="N74" t="n">
+      <c r="Q74" t="n">
         <v>6.32852592638244</v>
       </c>
-      <c r="O74" t="n">
+      <c r="R74" t="n">
         <v>5.408963859314081</v>
       </c>
-      <c r="P74" t="n">
+      <c r="S74" t="n">
         <v>5.846496545104817</v>
       </c>
-      <c r="Q74" t="n">
+      <c r="T74" t="n">
         <v>6.940125682649011</v>
       </c>
-      <c r="R74" t="n">
+      <c r="U74" t="n">
         <v>6.212846538019688</v>
       </c>
-      <c r="S74" t="n">
+      <c r="V74" t="n">
+        <v>5.260823158952103</v>
+      </c>
+      <c r="W74" t="n">
         <v>7.254432400583553</v>
       </c>
-      <c r="T74" t="n">
+      <c r="X74" t="n">
         <v>5.641091096325869</v>
       </c>
-      <c r="U74" t="n">
+      <c r="Y74" t="n">
         <v>174982241000</v>
       </c>
-      <c r="V74" t="n">
+      <c r="Z74" t="n">
         <v>193.1</v>
       </c>
     </row>
@@ -5808,63 +6704,75 @@
         </is>
       </c>
       <c r="C75" t="n">
+        <v>0.5489422421269007</v>
+      </c>
+      <c r="D75" t="n">
         <v>2.76469599516618</v>
       </c>
-      <c r="D75" t="n">
+      <c r="E75" t="n">
         <v>1.878509211585439</v>
       </c>
-      <c r="E75" t="n">
+      <c r="F75" t="n">
         <v>15.07422918196824</v>
       </c>
-      <c r="F75" t="n">
-        <v>0</v>
-      </c>
       <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
         <v>31.88572694548295</v>
       </c>
-      <c r="H75" t="n">
+      <c r="I75" t="n">
         <v>1.86590614961199</v>
       </c>
-      <c r="I75" t="n">
+      <c r="J75" t="n">
         <v>0.0032767961130966</v>
       </c>
-      <c r="J75" t="n">
+      <c r="K75" t="n">
+        <v>0.2884438977053123</v>
+      </c>
+      <c r="L75" t="n">
         <v>45.69026958023989</v>
       </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" t="n">
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>5.871638763696845</v>
+      </c>
+      <c r="O75" t="n">
         <v>5.192289989047339</v>
       </c>
-      <c r="M75" t="n">
+      <c r="P75" t="n">
         <v>6.95789695225662</v>
       </c>
-      <c r="N75" t="n">
+      <c r="Q75" t="n">
         <v>6.399143897121919</v>
       </c>
-      <c r="O75" t="n">
+      <c r="R75" t="n">
         <v>5.661083690397482</v>
       </c>
-      <c r="P75" t="n">
+      <c r="S75" t="n">
         <v>5.954515226996685</v>
       </c>
-      <c r="Q75" t="n">
+      <c r="T75" t="n">
         <v>7.062876957661498</v>
       </c>
-      <c r="R75" t="n">
+      <c r="U75" t="n">
         <v>6.364750756851911</v>
       </c>
-      <c r="S75" t="n">
+      <c r="V75" t="n">
+        <v>5.377082332363082</v>
+      </c>
+      <c r="W75" t="n">
         <v>7.517575183684538</v>
       </c>
-      <c r="T75" t="n">
+      <c r="X75" t="n">
         <v>5.65934280344663</v>
       </c>
-      <c r="U75" t="n">
+      <c r="Y75" t="n">
         <v>201538325000</v>
       </c>
-      <c r="V75" t="n">
+      <c r="Z75" t="n">
         <v>191.2</v>
       </c>
     </row>
@@ -5880,63 +6788,75 @@
         </is>
       </c>
       <c r="C76" t="n">
+        <v>0.3645612804613256</v>
+      </c>
+      <c r="D76" t="n">
         <v>4.151880384681693</v>
       </c>
-      <c r="D76" t="n">
+      <c r="E76" t="n">
         <v>2.000441401837552</v>
       </c>
-      <c r="E76" t="n">
+      <c r="F76" t="n">
         <v>12.94940955587905</v>
       </c>
-      <c r="F76" t="n">
+      <c r="G76" t="n">
         <v>1.356722443836332</v>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>26.58164444750853</v>
       </c>
-      <c r="H76" t="n">
+      <c r="I76" t="n">
         <v>3.989033121336908</v>
       </c>
-      <c r="I76" t="n">
+      <c r="J76" t="n">
         <v>0.004212785308842</v>
       </c>
-      <c r="J76" t="n">
+      <c r="K76" t="n">
+        <v>0.2850410207732877</v>
+      </c>
+      <c r="L76" t="n">
         <v>48.31705355837649</v>
       </c>
-      <c r="K76" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" t="n">
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>5.991489571208939</v>
+      </c>
+      <c r="O76" t="n">
         <v>5.275509255321492</v>
       </c>
-      <c r="M76" t="n">
+      <c r="P76" t="n">
         <v>7.0964646745278</v>
       </c>
-      <c r="N76" t="n">
+      <c r="Q76" t="n">
         <v>6.490935977258828</v>
       </c>
-      <c r="O76" t="n">
+      <c r="R76" t="n">
         <v>5.427106305527791</v>
       </c>
-      <c r="P76" t="n">
+      <c r="S76" t="n">
         <v>5.992164299172632</v>
       </c>
-      <c r="Q76" t="n">
+      <c r="T76" t="n">
         <v>7.115598388872077</v>
       </c>
-      <c r="R76" t="n">
+      <c r="U76" t="n">
         <v>6.478017958642</v>
       </c>
-      <c r="S76" t="n">
+      <c r="V76" t="n">
+        <v>5.388843379309258</v>
+      </c>
+      <c r="W76" t="n">
         <v>7.627817020601843</v>
       </c>
-      <c r="T76" t="n">
+      <c r="X76" t="n">
         <v>5.709963285204025</v>
       </c>
-      <c r="U76" t="n">
+      <c r="Y76" t="n">
         <v>234951446000</v>
       </c>
-      <c r="V76" t="n">
+      <c r="Z76" t="n">
         <v>195.5</v>
       </c>
     </row>
@@ -5952,63 +6872,75 @@
         </is>
       </c>
       <c r="C77" t="n">
+        <v>0.249022494875492</v>
+      </c>
+      <c r="D77" t="n">
         <v>6.059163275017065</v>
       </c>
-      <c r="D77" t="n">
+      <c r="E77" t="n">
         <v>2.05997800461006</v>
       </c>
-      <c r="E77" t="n">
+      <c r="F77" t="n">
         <v>12.7986671000023</v>
       </c>
-      <c r="F77" t="n">
+      <c r="G77" t="n">
         <v>1.525378932964562</v>
       </c>
-      <c r="G77" t="n">
+      <c r="H77" t="n">
         <v>27.00682458936293</v>
       </c>
-      <c r="H77" t="n">
+      <c r="I77" t="n">
         <v>4.473123932508614</v>
       </c>
-      <c r="I77" t="n">
+      <c r="J77" t="n">
         <v>0.0037254251776955</v>
       </c>
-      <c r="J77" t="n">
+      <c r="K77" t="n">
+        <v>0.3089786377982651</v>
+      </c>
+      <c r="L77" t="n">
         <v>45.51513760768301</v>
       </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="n">
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>6.121856623539852</v>
+      </c>
+      <c r="O77" t="n">
         <v>5.402316948315554</v>
       </c>
-      <c r="M77" t="n">
+      <c r="P77" t="n">
         <v>7.172086882809199</v>
       </c>
-      <c r="N77" t="n">
+      <c r="Q77" t="n">
         <v>6.545809335305935</v>
       </c>
-      <c r="O77" t="n">
+      <c r="R77" t="n">
         <v>5.65648125273144</v>
       </c>
-      <c r="P77" t="n">
+      <c r="S77" t="n">
         <v>6.195282542368022</v>
       </c>
-      <c r="Q77" t="n">
+      <c r="T77" t="n">
         <v>7.188420296714315</v>
       </c>
-      <c r="R77" t="n">
+      <c r="U77" t="n">
         <v>6.619459655716335</v>
       </c>
-      <c r="S77" t="n">
+      <c r="V77" t="n">
+        <v>5.428906909470086</v>
+      </c>
+      <c r="W77" t="n">
         <v>7.736865905144136</v>
       </c>
-      <c r="T77" t="n">
+      <c r="X77" t="n">
         <v>5.765410537403918</v>
       </c>
-      <c r="U77" t="n">
+      <c r="Y77" t="n">
         <v>268506265000</v>
       </c>
-      <c r="V77" t="n">
+      <c r="Z77" t="n">
         <v>200.5</v>
       </c>
     </row>
@@ -6024,63 +6956,75 @@
         </is>
       </c>
       <c r="C78" t="n">
+        <v>0.1522641978193933</v>
+      </c>
+      <c r="D78" t="n">
         <v>6.027253089248414</v>
       </c>
-      <c r="D78" t="n">
+      <c r="E78" t="n">
         <v>2.427081208727431</v>
       </c>
-      <c r="E78" t="n">
+      <c r="F78" t="n">
         <v>13.35293211136427</v>
       </c>
-      <c r="F78" t="n">
+      <c r="G78" t="n">
         <v>0.9194948076755384</v>
       </c>
-      <c r="G78" t="n">
+      <c r="H78" t="n">
         <v>31.31589588088164</v>
       </c>
-      <c r="H78" t="n">
+      <c r="I78" t="n">
         <v>3.866056627347963</v>
       </c>
-      <c r="I78" t="n">
+      <c r="J78" t="n">
         <v>0.003742673324056</v>
       </c>
-      <c r="J78" t="n">
+      <c r="K78" t="n">
+        <v>0.3031758141829601</v>
+      </c>
+      <c r="L78" t="n">
         <v>41.63210358942833</v>
       </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>6.203971715028045</v>
+      </c>
+      <c r="O78" t="n">
         <v>5.477634409220125</v>
       </c>
-      <c r="M78" t="n">
+      <c r="P78" t="n">
         <v>7.201103792425386</v>
       </c>
-      <c r="N78" t="n">
+      <c r="Q78" t="n">
         <v>6.550308640181583</v>
       </c>
-      <c r="O78" t="n">
+      <c r="R78" t="n">
         <v>5.913205703741515</v>
       </c>
-      <c r="P78" t="n">
+      <c r="S78" t="n">
         <v>6.338099204365416</v>
       </c>
-      <c r="Q78" t="n">
+      <c r="T78" t="n">
         <v>7.215489922359463</v>
       </c>
-      <c r="R78" t="n">
+      <c r="U78" t="n">
         <v>6.723808378595117</v>
       </c>
-      <c r="S78" t="n">
+      <c r="V78" t="n">
+        <v>5.509388336627977</v>
+      </c>
+      <c r="W78" t="n">
         <v>7.754078403866325</v>
       </c>
-      <c r="T78" t="n">
+      <c r="X78" t="n">
         <v>5.784624892524359</v>
       </c>
-      <c r="U78" t="n">
+      <c r="Y78" t="n">
         <v>269780425000</v>
       </c>
-      <c r="V78" t="n">
+      <c r="Z78" t="n">
         <v>215</v>
       </c>
     </row>
@@ -6096,63 +7040,75 @@
         </is>
       </c>
       <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
         <v>5.647111628757074</v>
       </c>
-      <c r="D79" t="n">
+      <c r="E79" t="n">
         <v>2.258448012601855</v>
       </c>
-      <c r="E79" t="n">
+      <c r="F79" t="n">
         <v>12.78424241294252</v>
       </c>
-      <c r="F79" t="n">
+      <c r="G79" t="n">
         <v>0.8285829062625858</v>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>31.8151646984536</v>
       </c>
-      <c r="H79" t="n">
+      <c r="I79" t="n">
         <v>3.302292536242178</v>
       </c>
-      <c r="I79" t="n">
+      <c r="J79" t="n">
         <v>0.0042260482523162</v>
       </c>
-      <c r="J79" t="n">
+      <c r="K79" t="n">
+        <v>0.2882484436054079</v>
+      </c>
+      <c r="L79" t="n">
         <v>43.07168331288246</v>
       </c>
-      <c r="K79" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" t="n">
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>6.248081596256315</v>
+      </c>
+      <c r="O79" t="n">
         <v>5.577274005770226</v>
       </c>
-      <c r="M79" t="n">
+      <c r="P79" t="n">
         <v>7.266701603783519</v>
       </c>
-      <c r="N79" t="n">
+      <c r="Q79" t="n">
         <v>6.581498677784121</v>
       </c>
-      <c r="O79" t="n">
+      <c r="R79" t="n">
         <v>6.009721851392627</v>
       </c>
-      <c r="P79" t="n">
+      <c r="S79" t="n">
         <v>6.414442040317051</v>
       </c>
-      <c r="Q79" t="n">
+      <c r="T79" t="n">
         <v>7.292296291339635</v>
       </c>
-      <c r="R79" t="n">
+      <c r="U79" t="n">
         <v>6.764161995152357</v>
       </c>
-      <c r="S79" t="n">
+      <c r="V79" t="n">
+        <v>5.625496569458729</v>
+      </c>
+      <c r="W79" t="n">
         <v>7.861141382635704</v>
       </c>
-      <c r="T79" t="n">
+      <c r="X79" t="n">
         <v>5.773246304560763</v>
       </c>
-      <c r="U79" t="n">
+      <c r="Y79" t="n">
         <v>292306175000</v>
       </c>
-      <c r="V79" t="n">
+      <c r="Z79" t="n">
         <v>228.9</v>
       </c>
     </row>
@@ -6168,63 +7124,75 @@
         </is>
       </c>
       <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
         <v>5.2456261432548</v>
       </c>
-      <c r="D80" t="n">
+      <c r="E80" t="n">
         <v>2.118310778091467</v>
       </c>
-      <c r="E80" t="n">
+      <c r="F80" t="n">
         <v>12.13121251376405</v>
       </c>
-      <c r="F80" t="n">
+      <c r="G80" t="n">
         <v>0.9935891354296202</v>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>32.15114003626724</v>
       </c>
-      <c r="H80" t="n">
+      <c r="I80" t="n">
         <v>2.729271268277648</v>
       </c>
-      <c r="I80" t="n">
+      <c r="J80" t="n">
         <v>0.0036908506256042</v>
       </c>
-      <c r="J80" t="n">
+      <c r="K80" t="n">
+        <v>0.2668310644849609</v>
+      </c>
+      <c r="L80" t="n">
         <v>44.36032820980461</v>
       </c>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="n">
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>6.207865447049881</v>
+      </c>
+      <c r="O80" t="n">
         <v>5.591136254984248</v>
       </c>
-      <c r="M80" t="n">
+      <c r="P80" t="n">
         <v>7.265212875552756</v>
       </c>
-      <c r="N80" t="n">
+      <c r="Q80" t="n">
         <v>6.571694981428156</v>
       </c>
-      <c r="O80" t="n">
+      <c r="R80" t="n">
         <v>5.981111147362562</v>
       </c>
-      <c r="P80" t="n">
+      <c r="S80" t="n">
         <v>6.437111405761462</v>
       </c>
-      <c r="Q80" t="n">
+      <c r="T80" t="n">
         <v>7.302489678579493</v>
       </c>
-      <c r="R80" t="n">
+      <c r="U80" t="n">
         <v>6.717599132288709</v>
       </c>
-      <c r="S80" t="n">
+      <c r="V80" t="n">
+        <v>5.627944789136227</v>
+      </c>
+      <c r="W80" t="n">
         <v>7.872390391155048</v>
       </c>
-      <c r="T80" t="n">
+      <c r="X80" t="n">
         <v>5.782531997518167</v>
       </c>
-      <c r="U80" t="n">
+      <c r="Y80" t="n">
         <v>293076071000</v>
       </c>
-      <c r="V80" t="n">
+      <c r="Z80" t="n">
         <v>235.678</v>
       </c>
     </row>
@@ -6240,63 +7208,75 @@
         </is>
       </c>
       <c r="C81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="n">
         <v>4.771862610830884</v>
       </c>
-      <c r="D81" t="n">
+      <c r="E81" t="n">
         <v>1.934470068127518</v>
       </c>
-      <c r="E81" t="n">
+      <c r="F81" t="n">
         <v>11.59718453259322</v>
       </c>
-      <c r="F81" t="n">
+      <c r="G81" t="n">
         <v>1.360975019909853</v>
       </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>29.10214093939634</v>
       </c>
-      <c r="H81" t="n">
+      <c r="I81" t="n">
         <v>1.589589942311651</v>
       </c>
-      <c r="I81" t="n">
+      <c r="J81" t="n">
         <v>0.0038609005356423</v>
       </c>
-      <c r="J81" t="n">
+      <c r="K81" t="n">
+        <v>0.2546890405023841</v>
+      </c>
+      <c r="L81" t="n">
         <v>49.38522694579251</v>
       </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>6.344987035822055</v>
+      </c>
+      <c r="O81" t="n">
         <v>5.589044838259233</v>
       </c>
-      <c r="M81" t="n">
+      <c r="P81" t="n">
         <v>7.384461402350289</v>
       </c>
-      <c r="N81" t="n">
+      <c r="Q81" t="n">
         <v>6.690345229172582</v>
       </c>
-      <c r="O81" t="n">
+      <c r="R81" t="n">
         <v>6.046757309755908</v>
       </c>
-      <c r="P81" t="n">
+      <c r="S81" t="n">
         <v>6.477033865655801</v>
       </c>
-      <c r="Q81" t="n">
+      <c r="T81" t="n">
         <v>7.404838939363641</v>
       </c>
-      <c r="R81" t="n">
+      <c r="U81" t="n">
         <v>6.796779049090226</v>
       </c>
-      <c r="S81" t="n">
+      <c r="V81" t="n">
+        <v>5.783055655550709</v>
+      </c>
+      <c r="W81" t="n">
         <v>8.024682144286524</v>
       </c>
-      <c r="T81" t="n">
+      <c r="X81" t="n">
         <v>5.896356823309522</v>
       </c>
-      <c r="U81" t="n">
+      <c r="Y81" t="n">
         <v>329767625000</v>
       </c>
-      <c r="V81" t="n">
+      <c r="Z81" t="n">
         <v>241.338</v>
       </c>
     </row>
@@ -6312,63 +7292,75 @@
         </is>
       </c>
       <c r="C82" t="n">
+        <v>0.3105222223286139</v>
+      </c>
+      <c r="D82" t="n">
         <v>3.879703461947794</v>
       </c>
-      <c r="D82" t="n">
+      <c r="E82" t="n">
         <v>1.529837345591892</v>
       </c>
-      <c r="E82" t="n">
+      <c r="F82" t="n">
         <v>11.31761937040821</v>
       </c>
-      <c r="F82" t="n">
+      <c r="G82" t="n">
         <v>9.2820311152446</v>
       </c>
-      <c r="G82" t="n">
+      <c r="H82" t="n">
         <v>27.03164094578956</v>
       </c>
-      <c r="H82" t="n">
+      <c r="I82" t="n">
         <v>1.404722834182802</v>
       </c>
-      <c r="I82" t="n">
+      <c r="J82" t="n">
         <v>0.0035132239304167</v>
       </c>
-      <c r="J82" t="n">
+      <c r="K82" t="n">
+        <v>0.1189413420505486</v>
+      </c>
+      <c r="L82" t="n">
         <v>45.12146813852556</v>
       </c>
-      <c r="K82" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" t="n">
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>6.316171435887882</v>
+      </c>
+      <c r="O82" t="n">
         <v>5.459968403972453</v>
       </c>
-      <c r="M82" t="n">
+      <c r="P82" t="n">
         <v>7.288032445138866</v>
       </c>
-      <c r="N82" t="n">
+      <c r="Q82" t="n">
         <v>6.673891938870605</v>
       </c>
-      <c r="O82" t="n">
+      <c r="R82" t="n">
         <v>6.366350152997659</v>
       </c>
-      <c r="P82" t="n">
+      <c r="S82" t="n">
         <v>6.457726788193342</v>
       </c>
-      <c r="Q82" t="n">
+      <c r="T82" t="n">
         <v>7.374509922606541</v>
       </c>
-      <c r="R82" t="n">
+      <c r="U82" t="n">
         <v>6.76902183279196</v>
       </c>
-      <c r="S82" t="n">
+      <c r="V82" t="n">
+        <v>5.711816824085469</v>
+      </c>
+      <c r="W82" t="n">
         <v>7.935258200152438</v>
       </c>
-      <c r="T82" t="n">
+      <c r="X82" t="n">
         <v>5.93521159264379</v>
       </c>
-      <c r="U82" t="n">
+      <c r="Y82" t="n">
         <v>362601424000</v>
       </c>
-      <c r="V82" t="n">
+      <c r="Z82" t="n">
         <v>260.014</v>
       </c>
     </row>
@@ -6384,63 +7376,75 @@
         </is>
       </c>
       <c r="C83" t="n">
+        <v>0.3593959392185478</v>
+      </c>
+      <c r="D83" t="n">
         <v>4.193925432983249</v>
       </c>
-      <c r="D83" t="n">
+      <c r="E83" t="n">
         <v>1.192658542290682</v>
       </c>
-      <c r="E83" t="n">
+      <c r="F83" t="n">
         <v>13.39799923038312</v>
       </c>
-      <c r="F83" t="n">
+      <c r="G83" t="n">
         <v>10.91571930916908</v>
       </c>
-      <c r="G83" t="n">
+      <c r="H83" t="n">
         <v>25.57572916947865</v>
       </c>
-      <c r="H83" t="n">
+      <c r="I83" t="n">
         <v>1.330761344869975</v>
       </c>
-      <c r="I83" t="n">
+      <c r="J83" t="n">
         <v>0.0036185816326035</v>
       </c>
-      <c r="J83" t="n">
+      <c r="K83" t="n">
+        <v>0.0603017957152115</v>
+      </c>
+      <c r="L83" t="n">
         <v>42.96989065425888</v>
       </c>
-      <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="n">
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>6.138072574650863</v>
+      </c>
+      <c r="O83" t="n">
         <v>5.225907944468035</v>
       </c>
-      <c r="M83" t="n">
+      <c r="P83" t="n">
         <v>6.98265867619141</v>
       </c>
-      <c r="N83" t="n">
+      <c r="Q83" t="n">
         <v>6.620139854699943</v>
       </c>
-      <c r="O83" t="n">
+      <c r="R83" t="n">
         <v>6.303058421728174</v>
       </c>
-      <c r="P83" t="n">
+      <c r="S83" t="n">
         <v>6.260250409651302</v>
       </c>
-      <c r="Q83" t="n">
+      <c r="T83" t="n">
         <v>7.30941988003283</v>
       </c>
-      <c r="R83" t="n">
+      <c r="U83" t="n">
         <v>6.604499189522853</v>
       </c>
-      <c r="S83" t="n">
+      <c r="V83" t="n">
+        <v>5.544278619847001</v>
+      </c>
+      <c r="W83" t="n">
         <v>7.706594902527812</v>
       </c>
-      <c r="T83" t="n">
+      <c r="X83" t="n">
         <v>5.876194011809762</v>
       </c>
-      <c r="U83" t="n">
+      <c r="Y83" t="n">
         <v>299647793000</v>
       </c>
-      <c r="V83" t="n">
+      <c r="Z83" t="n">
         <v>280.251</v>
       </c>
     </row>
@@ -6456,63 +7460,75 @@
         </is>
       </c>
       <c r="C84" t="n">
+        <v>0.3010302323790157</v>
+      </c>
+      <c r="D84" t="n">
         <v>3.756679842974199</v>
       </c>
-      <c r="D84" t="n">
+      <c r="E84" t="n">
         <v>1.278741660485849</v>
       </c>
-      <c r="E84" t="n">
+      <c r="F84" t="n">
         <v>12.19560954582155</v>
       </c>
-      <c r="F84" t="n">
+      <c r="G84" t="n">
         <v>12.25099317320979</v>
       </c>
-      <c r="G84" t="n">
+      <c r="H84" t="n">
         <v>24.24434649277434</v>
       </c>
-      <c r="H84" t="n">
+      <c r="I84" t="n">
         <v>1.416611687458391</v>
       </c>
-      <c r="I84" t="n">
+      <c r="J84" t="n">
         <v>0.1051067598680279</v>
       </c>
-      <c r="J84" t="n">
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
         <v>44.45088060502883</v>
       </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" t="n">
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>6.058585642279344</v>
+      </c>
+      <c r="O84" t="n">
         <v>5.087658027816</v>
       </c>
-      <c r="M84" t="n">
+      <c r="P84" t="n">
         <v>7.023144392464227</v>
       </c>
-      <c r="N84" t="n">
+      <c r="Q84" t="n">
         <v>6.545033560519325</v>
       </c>
-      <c r="O84" t="n">
+      <c r="R84" t="n">
         <v>6.314562020362362</v>
       </c>
-      <c r="P84" t="n">
+      <c r="S84" t="n">
         <v>6.223349807400833</v>
       </c>
-      <c r="Q84" t="n">
+      <c r="T84" t="n">
         <v>7.252309047131505</v>
       </c>
-      <c r="R84" t="n">
+      <c r="U84" t="n">
         <v>6.551937075916022</v>
       </c>
-      <c r="S84" t="n">
+      <c r="V84" t="n">
+        <v>5.420269488104334</v>
+      </c>
+      <c r="W84" t="n">
         <v>7.640051101663814</v>
       </c>
-      <c r="T84" t="n">
+      <c r="X84" t="n">
         <v>5.806699975623286</v>
       </c>
-      <c r="U84" t="n">
+      <c r="Y84" t="n">
         <v>291405615000</v>
       </c>
-      <c r="V84" t="n">
+      <c r="Z84" t="n">
         <v>267.898</v>
       </c>
     </row>
@@ -6528,63 +7544,75 @@
         </is>
       </c>
       <c r="C85" t="n">
+        <v>0.3320213387754024</v>
+      </c>
+      <c r="D85" t="n">
         <v>3.553314969600192</v>
       </c>
-      <c r="D85" t="n">
+      <c r="E85" t="n">
         <v>1.184365727837736</v>
       </c>
-      <c r="E85" t="n">
+      <c r="F85" t="n">
         <v>13.71734903422507</v>
       </c>
-      <c r="F85" t="n">
+      <c r="G85" t="n">
         <v>13.87748288051526</v>
       </c>
-      <c r="G85" t="n">
+      <c r="H85" t="n">
         <v>24.66275323732427</v>
       </c>
-      <c r="H85" t="n">
+      <c r="I85" t="n">
         <v>1.27896366383531</v>
       </c>
-      <c r="I85" t="n">
+      <c r="J85" t="n">
         <v>0.1429343860772579</v>
       </c>
-      <c r="J85" t="n">
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
         <v>41.25081476180949</v>
       </c>
-      <c r="K85" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" t="n">
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>6.193486576864871</v>
+      </c>
+      <c r="O85" t="n">
         <v>5.071228512233326</v>
       </c>
-      <c r="M85" t="n">
+      <c r="P85" t="n">
         <v>6.913220298988393</v>
       </c>
-      <c r="N85" t="n">
+      <c r="Q85" t="n">
         <v>6.658177918830908</v>
       </c>
-      <c r="O85" t="n">
+      <c r="R85" t="n">
         <v>6.510764204896637</v>
       </c>
-      <c r="P85" t="n">
+      <c r="S85" t="n">
         <v>6.345180099273568</v>
       </c>
-      <c r="Q85" t="n">
+      <c r="T85" t="n">
         <v>7.368680346931382</v>
       </c>
-      <c r="R85" t="n">
+      <c r="U85" t="n">
         <v>6.723111056183538</v>
       </c>
-      <c r="S85" t="n">
+      <c r="V85" t="n">
+        <v>5.474033816609901</v>
+      </c>
+      <c r="W85" t="n">
         <v>7.68348191090125</v>
       </c>
-      <c r="T85" t="n">
+      <c r="X85" t="n">
         <v>5.891257356209997</v>
       </c>
-      <c r="U85" t="n">
+      <c r="Y85" t="n">
         <v>299007622119</v>
       </c>
-      <c r="V85" t="n">
+      <c r="Z85" t="n">
         <v>257.897</v>
       </c>
     </row>
@@ -6600,63 +7628,75 @@
         </is>
       </c>
       <c r="C86" t="n">
+        <v>0.2953788983066128</v>
+      </c>
+      <c r="D86" t="n">
         <v>3.333832257745519</v>
       </c>
-      <c r="D86" t="n">
+      <c r="E86" t="n">
         <v>0.9309206119305056</v>
       </c>
-      <c r="E86" t="n">
+      <c r="F86" t="n">
         <v>12.30396192374931</v>
       </c>
-      <c r="F86" t="n">
+      <c r="G86" t="n">
         <v>10.71071429965129</v>
       </c>
-      <c r="G86" t="n">
+      <c r="H86" t="n">
         <v>22.45161886710291</v>
       </c>
-      <c r="H86" t="n">
+      <c r="I86" t="n">
         <v>1.166907451302634</v>
       </c>
-      <c r="I86" t="n">
+      <c r="J86" t="n">
         <v>0.1210141282700941</v>
       </c>
-      <c r="J86" t="n">
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
         <v>48.68565156194112</v>
       </c>
-      <c r="K86" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" t="n">
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>6.230323981298906</v>
+      </c>
+      <c r="O86" t="n">
         <v>5.255044447941139</v>
       </c>
-      <c r="M86" t="n">
+      <c r="P86" t="n">
         <v>7.059600429233472</v>
       </c>
-      <c r="N86" t="n">
+      <c r="Q86" t="n">
         <v>6.659780986794387</v>
       </c>
-      <c r="O86" t="n">
+      <c r="R86" t="n">
         <v>6.453467544629802</v>
       </c>
-      <c r="P86" t="n">
+      <c r="S86" t="n">
         <v>6.28279002920643</v>
       </c>
-      <c r="Q86" t="n">
+      <c r="T86" t="n">
         <v>7.320348243767967</v>
       </c>
-      <c r="R86" t="n">
+      <c r="U86" t="n">
         <v>6.752959422404492</v>
       </c>
-      <c r="S86" t="n">
+      <c r="V86" t="n">
+        <v>5.460053492328909</v>
+      </c>
+      <c r="W86" t="n">
         <v>7.878147750445278</v>
       </c>
-      <c r="T86" t="n">
+      <c r="X86" t="n">
         <v>5.840670755105942</v>
       </c>
-      <c r="U86" t="n">
+      <c r="Y86" t="n">
         <v>325108752692</v>
       </c>
-      <c r="V86" t="n">
+      <c r="Z86" t="n">
         <v>257.062</v>
       </c>
     </row>
@@ -6672,63 +7712,75 @@
         </is>
       </c>
       <c r="C87" t="n">
+        <v>0.1782104955859393</v>
+      </c>
+      <c r="D87" t="n">
         <v>2.16957937292293</v>
       </c>
-      <c r="D87" t="n">
+      <c r="E87" t="n">
         <v>1.015220470779142</v>
       </c>
-      <c r="E87" t="n">
+      <c r="F87" t="n">
         <v>10.95009050759224</v>
       </c>
-      <c r="F87" t="n">
+      <c r="G87" t="n">
         <v>9.348737249805994</v>
       </c>
-      <c r="G87" t="n">
+      <c r="H87" t="n">
         <v>21.87560250683966</v>
       </c>
-      <c r="H87" t="n">
+      <c r="I87" t="n">
         <v>1.057072471890699</v>
       </c>
-      <c r="I87" t="n">
+      <c r="J87" t="n">
         <v>0.154762758986712</v>
       </c>
-      <c r="J87" t="n">
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
         <v>53.25072416559669</v>
       </c>
-      <c r="K87" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" t="n">
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>6.25753346524067</v>
+      </c>
+      <c r="O87" t="n">
         <v>5.375648717958327</v>
       </c>
-      <c r="M87" t="n">
+      <c r="P87" t="n">
         <v>7.193340183209972</v>
       </c>
-      <c r="N87" t="n">
+      <c r="Q87" t="n">
         <v>6.657779963106711</v>
       </c>
-      <c r="O87" t="n">
+      <c r="R87" t="n">
         <v>6.435444987529209</v>
       </c>
-      <c r="P87" t="n">
+      <c r="S87" t="n">
         <v>6.329916938627028</v>
       </c>
-      <c r="Q87" t="n">
+      <c r="T87" t="n">
         <v>7.345119487607087</v>
       </c>
-      <c r="R87" t="n">
+      <c r="U87" t="n">
         <v>6.811343522205642</v>
       </c>
-      <c r="S87" t="n">
+      <c r="V87" t="n">
+        <v>5.463407960540311</v>
+      </c>
+      <c r="W87" t="n">
         <v>8.034579213009714</v>
       </c>
-      <c r="T87" t="n">
+      <c r="X87" t="n">
         <v>5.807541672267272</v>
       </c>
-      <c r="U87" t="n">
+      <c r="Y87" t="n">
         <v>348194055552</v>
       </c>
-      <c r="V87" t="n">
+      <c r="Z87" t="n">
         <v>253.86</v>
       </c>
     </row>
@@ -6744,63 +7796,75 @@
         </is>
       </c>
       <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="n">
         <v>2.008273759093116</v>
       </c>
-      <c r="D88" t="n">
+      <c r="E88" t="n">
         <v>0.770660909349661</v>
       </c>
-      <c r="E88" t="n">
+      <c r="F88" t="n">
         <v>11.3089486566038</v>
       </c>
-      <c r="F88" t="n">
+      <c r="G88" t="n">
         <v>10.51954024026382</v>
       </c>
-      <c r="G88" t="n">
+      <c r="H88" t="n">
         <v>22.42119477117303</v>
       </c>
-      <c r="H88" t="n">
+      <c r="I88" t="n">
         <v>1.083373792054814</v>
       </c>
-      <c r="I88" t="n">
+      <c r="J88" t="n">
         <v>0.1236287889217485</v>
       </c>
-      <c r="J88" t="n">
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
         <v>51.76437908254</v>
       </c>
-      <c r="K88" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" t="n">
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>6.199372630737188</v>
+      </c>
+      <c r="O88" t="n">
         <v>5.403622910907371</v>
       </c>
-      <c r="M88" t="n">
+      <c r="P88" t="n">
         <v>7.142036574706803</v>
       </c>
-      <c r="N88" t="n">
+      <c r="Q88" t="n">
         <v>6.589421520524994</v>
       </c>
-      <c r="O88" t="n">
+      <c r="R88" t="n">
         <v>6.542745701770261</v>
       </c>
-      <c r="P88" t="n">
+      <c r="S88" t="n">
         <v>6.313837810712578</v>
       </c>
-      <c r="Q88" t="n">
+      <c r="T88" t="n">
         <v>7.314033370331935</v>
       </c>
-      <c r="R88" t="n">
+      <c r="U88" t="n">
         <v>6.754102816902058</v>
       </c>
-      <c r="S88" t="n">
+      <c r="V88" t="n">
+        <v>5.33729765151348</v>
+      </c>
+      <c r="W88" t="n">
         <v>7.974381441958469</v>
       </c>
-      <c r="T88" t="n">
+      <c r="X88" t="n">
         <v>5.663550630364894</v>
       </c>
-      <c r="U88" t="n">
+      <c r="Y88" t="n">
         <v>314952628264</v>
       </c>
-      <c r="V88" t="n">
+      <c r="Z88" t="n">
         <v>258.934</v>
       </c>
     </row>
@@ -6816,63 +7880,75 @@
         </is>
       </c>
       <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
         <v>1.828804763121656</v>
       </c>
-      <c r="D89" t="n">
+      <c r="E89" t="n">
         <v>0.6112230618183646</v>
       </c>
-      <c r="E89" t="n">
+      <c r="F89" t="n">
         <v>10.77936258380316</v>
       </c>
-      <c r="F89" t="n">
+      <c r="G89" t="n">
         <v>9.480047520254816</v>
       </c>
-      <c r="G89" t="n">
+      <c r="H89" t="n">
         <v>25.24782827884198</v>
       </c>
-      <c r="H89" t="n">
+      <c r="I89" t="n">
         <v>1.074556597196598</v>
       </c>
-      <c r="I89" t="n">
+      <c r="J89" t="n">
         <v>0.1417987915948997</v>
       </c>
-      <c r="J89" t="n">
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
         <v>50.83637840336853</v>
       </c>
-      <c r="K89" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" t="n">
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>6.274422994521283</v>
+      </c>
+      <c r="O89" t="n">
         <v>5.49618411214232</v>
       </c>
-      <c r="M89" t="n">
+      <c r="P89" t="n">
         <v>7.247799706130813</v>
       </c>
-      <c r="N89" t="n">
+      <c r="Q89" t="n">
         <v>6.647714338895812</v>
       </c>
-      <c r="O89" t="n">
+      <c r="R89" t="n">
         <v>6.473381280989824</v>
       </c>
-      <c r="P89" t="n">
+      <c r="S89" t="n">
         <v>6.443797302736302</v>
       </c>
-      <c r="Q89" t="n">
+      <c r="T89" t="n">
         <v>7.389193300938843</v>
       </c>
-      <c r="R89" t="n">
+      <c r="U89" t="n">
         <v>6.862318503857793</v>
       </c>
-      <c r="S89" t="n">
+      <c r="V89" t="n">
+        <v>5.511329753398925</v>
+      </c>
+      <c r="W89" t="n">
         <v>8.104549374999145</v>
       </c>
-      <c r="T89" t="n">
+      <c r="X89" t="n">
         <v>5.788674900557945</v>
       </c>
-      <c r="U89" t="n">
+      <c r="Y89" t="n">
         <v>351900674461</v>
       </c>
-      <c r="V89" t="n">
+      <c r="Z89" t="n">
         <v>249.866</v>
       </c>
     </row>
@@ -6888,63 +7964,75 @@
         </is>
       </c>
       <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
         <v>1.918183192477047</v>
       </c>
-      <c r="D90" t="n">
+      <c r="E90" t="n">
         <v>0.7648669799507667</v>
       </c>
-      <c r="E90" t="n">
+      <c r="F90" t="n">
         <v>11.87236254154361</v>
       </c>
-      <c r="F90" t="n">
+      <c r="G90" t="n">
         <v>10.70837930548366</v>
       </c>
-      <c r="G90" t="n">
+      <c r="H90" t="n">
         <v>31.22562556388421</v>
       </c>
-      <c r="H90" t="n">
+      <c r="I90" t="n">
         <v>1.502347845356956</v>
       </c>
-      <c r="I90" t="n">
+      <c r="J90" t="n">
         <v>0.1669178288589748</v>
       </c>
-      <c r="J90" t="n">
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
         <v>41.84131674244478</v>
       </c>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="n">
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>6.361319765447091</v>
+      </c>
+      <c r="O90" t="n">
         <v>5.66445239679886</v>
       </c>
-      <c r="M90" t="n">
+      <c r="P90" t="n">
         <v>7.297409362814692</v>
       </c>
-      <c r="N90" t="n">
+      <c r="Q90" t="n">
         <v>6.694549670120566</v>
       </c>
-      <c r="O90" t="n">
+      <c r="R90" t="n">
         <v>6.588857716169554</v>
       </c>
-      <c r="P90" t="n">
+      <c r="S90" t="n">
         <v>6.546699327344415</v>
       </c>
-      <c r="Q90" t="n">
+      <c r="T90" t="n">
         <v>7.443575894350589</v>
       </c>
-      <c r="R90" t="n">
+      <c r="U90" t="n">
         <v>6.964428630536936</v>
       </c>
-      <c r="S90" t="n">
+      <c r="V90" t="n">
+        <v>5.468987985746999</v>
+      </c>
+      <c r="W90" t="n">
         <v>8.250531282438216</v>
       </c>
-      <c r="T90" t="n">
+      <c r="X90" t="n">
         <v>5.798668277611961</v>
       </c>
-      <c r="U90" t="n">
+      <c r="Y90" t="n">
         <v>331680406332</v>
       </c>
-      <c r="V90" t="n">
+      <c r="Z90" t="n">
         <v>255.095</v>
       </c>
     </row>
@@ -6960,63 +8048,75 @@
         </is>
       </c>
       <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
         <v>2.100414319634924</v>
       </c>
-      <c r="D91" t="n">
+      <c r="E91" t="n">
         <v>0.9643309976487132</v>
       </c>
-      <c r="E91" t="n">
+      <c r="F91" t="n">
         <v>13.7433644399824</v>
       </c>
-      <c r="F91" t="n">
+      <c r="G91" t="n">
         <v>12.37402943599428</v>
       </c>
-      <c r="G91" t="n">
+      <c r="H91" t="n">
         <v>37.88392389122557</v>
       </c>
-      <c r="H91" t="n">
+      <c r="I91" t="n">
         <v>1.786541374658091</v>
       </c>
-      <c r="I91" t="n">
+      <c r="J91" t="n">
         <v>0.2416178567513473</v>
       </c>
-      <c r="J91" t="n">
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
         <v>30.90577768410467</v>
       </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="n">
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>6.31579188610481</v>
+      </c>
+      <c r="O91" t="n">
         <v>5.738151663283441</v>
       </c>
-      <c r="M91" t="n">
+      <c r="P91" t="n">
         <v>7.315264926453933</v>
       </c>
-      <c r="N91" t="n">
+      <c r="Q91" t="n">
         <v>6.702378002190073</v>
       </c>
-      <c r="O91" t="n">
+      <c r="R91" t="n">
         <v>6.548734708141091</v>
       </c>
-      <c r="P91" t="n">
+      <c r="S91" t="n">
         <v>6.530527726525799</v>
       </c>
-      <c r="Q91" t="n">
+      <c r="T91" t="n">
         <v>7.43296301768946</v>
       </c>
-      <c r="R91" t="n">
+      <c r="U91" t="n">
         <v>6.928165559969595</v>
       </c>
-      <c r="S91" t="n">
+      <c r="V91" t="n">
+        <v>5.481263702695403</v>
+      </c>
+      <c r="W91" t="n">
         <v>8.388793697331248</v>
       </c>
-      <c r="T91" t="n">
+      <c r="X91" t="n">
         <v>5.851138709812049</v>
       </c>
-      <c r="U91" t="n">
+      <c r="Y91" t="n">
         <v>279969062343</v>
       </c>
-      <c r="V91" t="n">
+      <c r="Z91" t="n">
         <v>255.914</v>
       </c>
     </row>
@@ -7032,63 +8132,75 @@
         </is>
       </c>
       <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
         <v>2.183758996307775</v>
       </c>
-      <c r="D92" t="n">
+      <c r="E92" t="n">
         <v>0.9601103113537316</v>
       </c>
-      <c r="E92" t="n">
+      <c r="F92" t="n">
         <v>16.17019997216893</v>
       </c>
-      <c r="F92" t="n">
+      <c r="G92" t="n">
         <v>11.49677509411264</v>
       </c>
-      <c r="G92" t="n">
+      <c r="H92" t="n">
         <v>39.43503094000381</v>
       </c>
-      <c r="H92" t="n">
+      <c r="I92" t="n">
         <v>2.221327131701019</v>
       </c>
-      <c r="I92" t="n">
+      <c r="J92" t="n">
         <v>0.3780740723451772</v>
       </c>
-      <c r="J92" t="n">
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
         <v>27.15472348200693</v>
       </c>
-      <c r="K92" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" t="n">
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>6.409681359228575</v>
+      </c>
+      <c r="O92" t="n">
         <v>5.751302010025054</v>
       </c>
-      <c r="M92" t="n">
+      <c r="P92" t="n">
         <v>7.381134475945595</v>
       </c>
-      <c r="N92" t="n">
+      <c r="Q92" t="n">
         <v>6.788723997550031</v>
       </c>
-      <c r="O92" t="n">
+      <c r="R92" t="n">
         <v>6.516888057421068</v>
       </c>
-      <c r="P92" t="n">
+      <c r="S92" t="n">
         <v>6.625604511478119</v>
       </c>
-      <c r="Q92" t="n">
+      <c r="T92" t="n">
         <v>7.493584462861508</v>
       </c>
-      <c r="R92" t="n">
+      <c r="U92" t="n">
         <v>7.044957477217799</v>
       </c>
-      <c r="S92" t="n">
+      <c r="V92" t="n">
+        <v>5.636502460342662</v>
+      </c>
+      <c r="W92" t="n">
         <v>8.390204966043303</v>
       </c>
-      <c r="T92" t="n">
+      <c r="X92" t="n">
         <v>6.016839850463917</v>
       </c>
-      <c r="U92" t="n">
+      <c r="Y92" t="n">
         <v>266378900503</v>
       </c>
-      <c r="V92" t="n">
+      <c r="Z92" t="n">
         <v>252.682</v>
       </c>
     </row>
@@ -7104,63 +8216,75 @@
         </is>
       </c>
       <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="n">
         <v>2.26809018231683</v>
       </c>
-      <c r="D93" t="n">
+      <c r="E93" t="n">
         <v>1.236945365696256</v>
       </c>
-      <c r="E93" t="n">
+      <c r="F93" t="n">
         <v>14.68460936928489</v>
       </c>
-      <c r="F93" t="n">
+      <c r="G93" t="n">
         <v>11.31563638690281</v>
       </c>
-      <c r="G93" t="n">
+      <c r="H93" t="n">
         <v>38.9585960143157</v>
       </c>
-      <c r="H93" t="n">
+      <c r="I93" t="n">
         <v>2.020429647658875</v>
       </c>
-      <c r="I93" t="n">
+      <c r="J93" t="n">
         <v>0.3690578646006429</v>
       </c>
-      <c r="J93" t="n">
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
         <v>29.14663516922398</v>
       </c>
-      <c r="K93" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" t="n">
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>6.272442986960556</v>
+      </c>
+      <c r="O93" t="n">
         <v>5.833816101237489</v>
       </c>
-      <c r="M93" t="n">
+      <c r="P93" t="n">
         <v>7.512704943465549</v>
       </c>
-      <c r="N93" t="n">
+      <c r="Q93" t="n">
         <v>6.749521302316858</v>
       </c>
-      <c r="O93" t="n">
+      <c r="R93" t="n">
         <v>6.484406164493495</v>
       </c>
-      <c r="P93" t="n">
+      <c r="S93" t="n">
         <v>6.690146386201316</v>
       </c>
-      <c r="Q93" t="n">
+      <c r="T93" t="n">
         <v>7.380723260191887</v>
       </c>
-      <c r="R93" t="n">
+      <c r="U93" t="n">
         <v>7.017192495563775</v>
       </c>
-      <c r="S93" t="n">
+      <c r="V93" t="n">
+        <v>5.538318034928669</v>
+      </c>
+      <c r="W93" t="n">
         <v>8.435879013331778</v>
       </c>
-      <c r="T93" t="n">
+      <c r="X93" t="n">
         <v>5.953113487434751</v>
       </c>
-      <c r="U93" t="n">
+      <c r="Y93" t="n">
         <v>267175474249</v>
       </c>
-      <c r="V93" t="n">
+      <c r="Z93" t="n">
         <v>253.434</v>
       </c>
     </row>
